--- a/documents/job-applications.xlsx
+++ b/documents/job-applications.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\LARRY\Documents\Scripts\auto-job-app-sender\documents\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{58406C11-9C6C-4319-B24D-AC1D54432407}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2FA896E1-3CC7-4BE1-AABC-808091CDF630}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="17" uniqueCount="12">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="63" uniqueCount="36">
   <si>
     <t>company</t>
   </si>
@@ -51,9 +51,6 @@
     <t>Software AI Engineer</t>
   </si>
   <si>
-    <t>Artificial Intelligence Engineer (Intern) at Baz.AI</t>
-  </si>
-  <si>
     <t>AI Engineer Intern</t>
   </si>
   <si>
@@ -61,13 +58,88 @@
   </si>
   <si>
     <t>Wellfound</t>
+  </si>
+  <si>
+    <t>Replied</t>
+  </si>
+  <si>
+    <t>BetterPic.io</t>
+  </si>
+  <si>
+    <t>Baz.AI</t>
+  </si>
+  <si>
+    <t>Moksh.io</t>
+  </si>
+  <si>
+    <t>Data Science Engineer Intern</t>
+  </si>
+  <si>
+    <t>Machine Learning (Data Gathering + NLP + GPT4) Intern</t>
+  </si>
+  <si>
+    <t>Harpresearch.ai</t>
+  </si>
+  <si>
+    <t>Applied Mathematics - Quantum Machine Learning Internship</t>
+  </si>
+  <si>
+    <t>Hybrid ML-LLM Workflow Engineering Intern</t>
+  </si>
+  <si>
+    <t>website</t>
+  </si>
+  <si>
+    <t>https://www.betterpic.io/careers</t>
+  </si>
+  <si>
+    <t>https://www.dnamicro.com/</t>
+  </si>
+  <si>
+    <t>https://zania.ai/</t>
+  </si>
+  <si>
+    <t>https://www.harpresearch.ai/</t>
+  </si>
+  <si>
+    <t>Zania.ai</t>
+  </si>
+  <si>
+    <t>Lead AI Engineer / Data Scientist</t>
+  </si>
+  <si>
+    <t>Real</t>
+  </si>
+  <si>
+    <t>AI/ML Engineer</t>
+  </si>
+  <si>
+    <t>https://onereal.com/pages/careers</t>
+  </si>
+  <si>
+    <t>https://www.trexsolutionsllc.com/</t>
+  </si>
+  <si>
+    <t>Data Science &amp; AI Platform Engineer</t>
+  </si>
+  <si>
+    <t>T-Rex Solutions</t>
+  </si>
+  <si>
+    <t>Sprouts AI</t>
+  </si>
+  <si>
+    <t>Chief NLP Scientist</t>
+  </si>
+  <si>
+    <t>https://www.sproutsai.com/company</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -76,8 +148,18 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <u/>
       <sz val="11"/>
-      <name val="Calibri "/>
+      <color theme="10"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="2">
@@ -97,16 +179,26 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="2">
+    <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
@@ -385,75 +477,249 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:E4"/>
-  <sheetFormatPr defaultRowHeight="14.4"/>
+  <dimension ref="A1:F13"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="45.109375" customWidth="1"/>
     <col min="2" max="2" width="36.44140625" customWidth="1"/>
-    <col min="3" max="3" width="27.77734375" customWidth="1"/>
+    <col min="3" max="3" width="46.44140625" customWidth="1"/>
     <col min="4" max="4" width="25.44140625" customWidth="1"/>
+    <col min="6" max="6" width="39.77734375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5">
-      <c r="A1" t="s">
+    <row r="1" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="B1" t="s">
+      <c r="B1" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="C1" t="s">
+      <c r="C1" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="D1" t="s">
+      <c r="D1" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="E1" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="2" spans="1:5">
-      <c r="A2" t="s">
+      <c r="E1" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="F1" s="2" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A2" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="C2" t="s">
+      <c r="B2" s="2"/>
+      <c r="C2" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="D2" t="s">
-        <v>6</v>
-      </c>
-      <c r="E2" t="s">
+      <c r="D2" s="2" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="3" spans="1:5">
-      <c r="A3" t="s">
+      <c r="E2" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="F2" s="2" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A3" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="C3" t="s">
+      <c r="B3" s="2"/>
+      <c r="C3" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="D3" t="s">
-        <v>6</v>
-      </c>
-      <c r="E3" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="4" spans="1:5">
+      <c r="D3" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="E3" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="F3" s="2" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A4" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="B4" s="2"/>
+      <c r="C4" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="C4" t="s">
-        <v>9</v>
-      </c>
-      <c r="D4" t="s">
-        <v>6</v>
-      </c>
-      <c r="E4" t="s">
-        <v>11</v>
+      <c r="D4" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="E4" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="F4" s="2"/>
+    </row>
+    <row r="5" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A5" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="B5" s="2"/>
+      <c r="C5" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D5" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="E5" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="F5" s="4" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A6" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="B6" s="2"/>
+      <c r="C6" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="D6" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="E6" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="F6" s="2"/>
+    </row>
+    <row r="7" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A7" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="B7" s="2"/>
+      <c r="C7" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="D7" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="E7" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="F7" s="2"/>
+    </row>
+    <row r="8" spans="1:6" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A8" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="B8" s="2"/>
+      <c r="C8" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="D8" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="E8" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="F8" s="2" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A9" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="B9" s="2"/>
+      <c r="C9" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="D9" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="E9" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="F9" s="2" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A10" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="B10" s="2"/>
+      <c r="C10" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="D10" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="E10" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="F10" s="2" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A11" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="C11" t="s">
+        <v>28</v>
+      </c>
+      <c r="D11" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="E11" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="F11" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A12" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="C12" t="s">
+        <v>31</v>
+      </c>
+      <c r="D12" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="E12" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="F12" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A13" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="C13" t="s">
+        <v>34</v>
+      </c>
+      <c r="D13" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="E13" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="F13" t="s">
+        <v>35</v>
       </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink ref="C8" r:id="rId1" display="https://wellfound.com/jobs/3070300-applied-mathematics-quantum-machine-learning-internship" xr:uid="{A79CCC78-B95C-437E-B419-A129E2100236}"/>
+    <hyperlink ref="C9" r:id="rId2" display="https://wellfound.com/jobs/3070295-hybrid-ml-llm-workflow-engineering-intern" xr:uid="{8F71FAD4-89FC-4EEF-B534-BF32621064A2}"/>
+    <hyperlink ref="F5" r:id="rId3" xr:uid="{2243349C-D0C1-47D7-B85B-F61D37610D38}"/>
+  </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
--- a/documents/job-applications.xlsx
+++ b/documents/job-applications.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\LARRY\Documents\Scripts\auto-job-app-sender\documents\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2FA896E1-3CC7-4BE1-AABC-808091CDF630}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3306FC64-5818-4EEB-AAC4-42CAB78997B4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="63" uniqueCount="36">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="92" uniqueCount="52">
   <si>
     <t>company</t>
   </si>
@@ -133,6 +133,54 @@
   </si>
   <si>
     <t>https://www.sproutsai.com/company</t>
+  </si>
+  <si>
+    <t>Rejected</t>
+  </si>
+  <si>
+    <t>Kalibrr</t>
+  </si>
+  <si>
+    <t>LENA - Lately Everything Needs Analytics</t>
+  </si>
+  <si>
+    <t>Likha-iT Inc.</t>
+  </si>
+  <si>
+    <t>LeapFroggr Inc.</t>
+  </si>
+  <si>
+    <t>https://www.lena.com.ph/</t>
+  </si>
+  <si>
+    <t>https://seriousmd.com/</t>
+  </si>
+  <si>
+    <t>https://likhait.com/</t>
+  </si>
+  <si>
+    <t>Power BI | Data Visualization Engineer</t>
+  </si>
+  <si>
+    <t>Data Scientist</t>
+  </si>
+  <si>
+    <t>Software Engineer</t>
+  </si>
+  <si>
+    <t>Senior Data Scientist</t>
+  </si>
+  <si>
+    <t>Senior Python Developer</t>
+  </si>
+  <si>
+    <t>https://www.itvt.de/</t>
+  </si>
+  <si>
+    <t>ITVT Philippines Inc.</t>
+  </si>
+  <si>
+    <t>Medgrocer</t>
   </si>
 </sst>
 </file>
@@ -183,7 +231,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
@@ -196,6 +244,7 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
@@ -477,7 +526,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:F13"/>
+  <dimension ref="A1:F19"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="45.109375" customWidth="1"/>
@@ -654,7 +703,7 @@
         <v>26</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>6</v>
+        <v>36</v>
       </c>
       <c r="E10" s="2" t="s">
         <v>10</v>
@@ -667,7 +716,8 @@
       <c r="A11" s="2" t="s">
         <v>27</v>
       </c>
-      <c r="C11" t="s">
+      <c r="B11" s="2"/>
+      <c r="C11" s="2" t="s">
         <v>28</v>
       </c>
       <c r="D11" s="2" t="s">
@@ -676,7 +726,7 @@
       <c r="E11" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="F11" t="s">
+      <c r="F11" s="2" t="s">
         <v>29</v>
       </c>
     </row>
@@ -684,7 +734,8 @@
       <c r="A12" s="2" t="s">
         <v>32</v>
       </c>
-      <c r="C12" t="s">
+      <c r="B12" s="2"/>
+      <c r="C12" s="2" t="s">
         <v>31</v>
       </c>
       <c r="D12" s="2" t="s">
@@ -693,7 +744,7 @@
       <c r="E12" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="F12" t="s">
+      <c r="F12" s="2" t="s">
         <v>30</v>
       </c>
     </row>
@@ -701,7 +752,8 @@
       <c r="A13" s="2" t="s">
         <v>33</v>
       </c>
-      <c r="C13" t="s">
+      <c r="B13" s="2"/>
+      <c r="C13" s="2" t="s">
         <v>34</v>
       </c>
       <c r="D13" s="2" t="s">
@@ -710,15 +762,122 @@
       <c r="E13" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="F13" t="s">
+      <c r="F13" s="2" t="s">
         <v>35</v>
       </c>
+    </row>
+    <row r="14" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A14" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="B14" s="2"/>
+      <c r="C14" s="4" t="s">
+        <v>44</v>
+      </c>
+      <c r="D14" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="E14" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="F14" s="2" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="15" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A15" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="B15" s="2"/>
+      <c r="C15" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="D15" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="E15" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="F15" s="2" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="16" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A16" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="B16" s="2"/>
+      <c r="C16" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="D16" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="E16" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="F16" s="2" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="17" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A17" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="B17" s="2"/>
+      <c r="C17" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="D17" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="E17" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="F17" s="2" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="18" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A18" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="B18" s="2"/>
+      <c r="C18" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="D18" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="E18" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="F18" s="2" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="19" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A19" s="6" t="s">
+        <v>51</v>
+      </c>
+      <c r="B19" s="6"/>
+      <c r="C19" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="D19" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="E19" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="F19" s="6"/>
     </row>
   </sheetData>
   <hyperlinks>
     <hyperlink ref="C8" r:id="rId1" display="https://wellfound.com/jobs/3070300-applied-mathematics-quantum-machine-learning-internship" xr:uid="{A79CCC78-B95C-437E-B419-A129E2100236}"/>
     <hyperlink ref="C9" r:id="rId2" display="https://wellfound.com/jobs/3070295-hybrid-ml-llm-workflow-engineering-intern" xr:uid="{8F71FAD4-89FC-4EEF-B534-BF32621064A2}"/>
     <hyperlink ref="F5" r:id="rId3" xr:uid="{2243349C-D0C1-47D7-B85B-F61D37610D38}"/>
+    <hyperlink ref="C14" r:id="rId4" display="https://jobseeker.kalibrr.com/c/twelve-baskets-analytics/jobs/215162/power-bi-data-visualization-engineer" xr:uid="{C2ED8803-7684-4369-855C-4B2A1CB460F4}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/documents/job-applications.xlsx
+++ b/documents/job-applications.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\LARRY\Documents\Scripts\auto-job-app-sender\documents\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3306FC64-5818-4EEB-AAC4-42CAB78997B4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{32F6B0AC-77E5-4F9A-9FD4-893E99BBE71D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -231,7 +231,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
@@ -244,7 +244,6 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
@@ -811,7 +810,7 @@
         <v>46</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>6</v>
+        <v>36</v>
       </c>
       <c r="E16" s="2" t="s">
         <v>37</v>
@@ -857,20 +856,18 @@
       </c>
     </row>
     <row r="19" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A19" s="6" t="s">
+      <c r="A19" t="s">
         <v>51</v>
       </c>
-      <c r="B19" s="6"/>
       <c r="C19" s="2" t="s">
         <v>46</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="E19" s="2" t="s">
         <v>37</v>
       </c>
-      <c r="F19" s="6"/>
     </row>
   </sheetData>
   <hyperlinks>

--- a/documents/job-applications.xlsx
+++ b/documents/job-applications.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\LARRY\Documents\Scripts\auto-job-app-sender\documents\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{32F6B0AC-77E5-4F9A-9FD4-893E99BBE71D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A8EEDBF8-85A6-404A-8AB7-B865A7E59FEC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="92" uniqueCount="52">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="155" uniqueCount="79">
   <si>
     <t>company</t>
   </si>
@@ -181,13 +181,94 @@
   </si>
   <si>
     <t>Medgrocer</t>
+  </si>
+  <si>
+    <t>Jr. Data Engineer</t>
+  </si>
+  <si>
+    <t>Software Engineer Cloud Vertex AI Infrastructure</t>
+  </si>
+  <si>
+    <t>https://www.accenture.com/ph-en/careers</t>
+  </si>
+  <si>
+    <t>Accenture</t>
+  </si>
+  <si>
+    <t>M2.0 Communications Inc. Media Meter</t>
+  </si>
+  <si>
+    <t>https://media-meter.net/</t>
+  </si>
+  <si>
+    <t>http://www.medgrocer.com/</t>
+  </si>
+  <si>
+    <t>Software IT Associate</t>
+  </si>
+  <si>
+    <t>AI Engineering Manager</t>
+  </si>
+  <si>
+    <t>https://questronix.com.ph/</t>
+  </si>
+  <si>
+    <t>API Developer</t>
+  </si>
+  <si>
+    <t>Questronix</t>
+  </si>
+  <si>
+    <t>Nomura Research Institute Indonesia</t>
+  </si>
+  <si>
+    <t>Machine Learning Engineer</t>
+  </si>
+  <si>
+    <t>https://www.nri.co.id/</t>
+  </si>
+  <si>
+    <t>Data Engineer</t>
+  </si>
+  <si>
+    <t>Sr Full Stack Developepr</t>
+  </si>
+  <si>
+    <t>Blue Spark Solutions, Inc.</t>
+  </si>
+  <si>
+    <t>Data Analyst</t>
+  </si>
+  <si>
+    <t>http://bluesparkph.com/</t>
+  </si>
+  <si>
+    <t>https://www.airflip.com/</t>
+  </si>
+  <si>
+    <t>Applied AI Engineer</t>
+  </si>
+  <si>
+    <t>Airflip</t>
+  </si>
+  <si>
+    <t>Thinking Machines</t>
+  </si>
+  <si>
+    <t>https://thinkingmachin.es/</t>
+  </si>
+  <si>
+    <t>Machine Learning (GenAI, LLMs)</t>
+  </si>
+  <si>
+    <t>careers@thinkingmachines.freshteam.com</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="3" x14ac:knownFonts="1">
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -205,6 +286,13 @@
     </font>
     <font>
       <sz val="11"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF222222"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -231,7 +319,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
@@ -244,6 +332,7 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
@@ -525,7 +614,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:F19"/>
+  <dimension ref="A1:F31"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="45.109375" customWidth="1"/>
@@ -856,9 +945,10 @@
       </c>
     </row>
     <row r="19" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A19" t="s">
+      <c r="A19" s="2" t="s">
         <v>51</v>
       </c>
+      <c r="B19" s="2"/>
       <c r="C19" s="2" t="s">
         <v>46</v>
       </c>
@@ -867,6 +957,229 @@
       </c>
       <c r="E19" s="2" t="s">
         <v>37</v>
+      </c>
+      <c r="F19" s="2" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="20" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A20" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="B20" s="2"/>
+      <c r="C20" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="D20" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="E20" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="F20" s="2" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="21" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A21" s="2" t="s">
+        <v>55</v>
+      </c>
+      <c r="B21" s="2"/>
+      <c r="C21" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="D21" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="E21" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="F21" s="2" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="22" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A22" s="2" t="s">
+        <v>55</v>
+      </c>
+      <c r="B22" s="2"/>
+      <c r="C22" s="2" t="s">
+        <v>59</v>
+      </c>
+      <c r="D22" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="E22" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="F22" s="2" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="23" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A23" s="2" t="s">
+        <v>55</v>
+      </c>
+      <c r="B23" s="2"/>
+      <c r="C23" s="2" t="s">
+        <v>60</v>
+      </c>
+      <c r="D23" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="E23" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="F23" s="2" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="24" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A24" s="2" t="s">
+        <v>63</v>
+      </c>
+      <c r="B24" s="2"/>
+      <c r="C24" s="2" t="s">
+        <v>62</v>
+      </c>
+      <c r="D24" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="E24" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="F24" s="2" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="25" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A25" s="2" t="s">
+        <v>64</v>
+      </c>
+      <c r="B25" s="2"/>
+      <c r="C25" s="2" t="s">
+        <v>65</v>
+      </c>
+      <c r="D25" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="E25" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="F25" s="2" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="26" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A26" s="2" t="s">
+        <v>63</v>
+      </c>
+      <c r="B26" s="2"/>
+      <c r="C26" s="2" t="s">
+        <v>67</v>
+      </c>
+      <c r="D26" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="E26" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="F26" s="2" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="27" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A27" s="2" t="s">
+        <v>63</v>
+      </c>
+      <c r="B27" s="2"/>
+      <c r="C27" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="D27" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="E27" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="F27" s="2" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="28" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A28" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="B28" s="2"/>
+      <c r="C28" s="2" t="s">
+        <v>70</v>
+      </c>
+      <c r="D28" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="E28" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="F28" s="2" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="29" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A29" s="2" t="s">
+        <v>74</v>
+      </c>
+      <c r="B29" s="2"/>
+      <c r="C29" s="2" t="s">
+        <v>73</v>
+      </c>
+      <c r="D29" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="E29" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="F29" s="2" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="30" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A30" s="2" t="s">
+        <v>75</v>
+      </c>
+      <c r="B30" s="6" t="s">
+        <v>78</v>
+      </c>
+      <c r="C30" s="2" t="s">
+        <v>67</v>
+      </c>
+      <c r="D30" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="E30" s="2" t="s">
+        <v>75</v>
+      </c>
+      <c r="F30" s="4" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="31" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A31" s="2" t="s">
+        <v>75</v>
+      </c>
+      <c r="B31" s="6" t="s">
+        <v>78</v>
+      </c>
+      <c r="C31" s="2" t="s">
+        <v>77</v>
+      </c>
+      <c r="D31" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="E31" s="2" t="s">
+        <v>75</v>
+      </c>
+      <c r="F31" s="4" t="s">
+        <v>76</v>
       </c>
     </row>
   </sheetData>
@@ -875,6 +1188,8 @@
     <hyperlink ref="C9" r:id="rId2" display="https://wellfound.com/jobs/3070295-hybrid-ml-llm-workflow-engineering-intern" xr:uid="{8F71FAD4-89FC-4EEF-B534-BF32621064A2}"/>
     <hyperlink ref="F5" r:id="rId3" xr:uid="{2243349C-D0C1-47D7-B85B-F61D37610D38}"/>
     <hyperlink ref="C14" r:id="rId4" display="https://jobseeker.kalibrr.com/c/twelve-baskets-analytics/jobs/215162/power-bi-data-visualization-engineer" xr:uid="{C2ED8803-7684-4369-855C-4B2A1CB460F4}"/>
+    <hyperlink ref="F30" r:id="rId5" xr:uid="{FAB250DC-3878-40A9-9C88-7B946B625FA9}"/>
+    <hyperlink ref="F31" r:id="rId6" xr:uid="{3141AFC0-D998-4026-86A8-ED9E9752D6FA}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/documents/job-applications.xlsx
+++ b/documents/job-applications.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="28129"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="28227"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\LARRY\Documents\Scripts\auto-job-app-sender\documents\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A8EEDBF8-85A6-404A-8AB7-B865A7E59FEC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{66D5628A-170C-4353-884B-8296412F642F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="155" uniqueCount="79">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="169" uniqueCount="87">
   <si>
     <t>company</t>
   </si>
@@ -262,6 +262,30 @@
   </si>
   <si>
     <t>careers@thinkingmachines.freshteam.com</t>
+  </si>
+  <si>
+    <t>Interview Pending</t>
+  </si>
+  <si>
+    <t>Shortlisted</t>
+  </si>
+  <si>
+    <t>https://careers.snap.com/job?id=R0037568&amp;ref=peerlist</t>
+  </si>
+  <si>
+    <t>Snap Inc.</t>
+  </si>
+  <si>
+    <t>Machine Learning Engineer - GenAI</t>
+  </si>
+  <si>
+    <t>https://jobs.lever.co/factored/088fd469-0abf-4bc8-a23d-91c1d64c1dc4/apply</t>
+  </si>
+  <si>
+    <t>Factored</t>
+  </si>
+  <si>
+    <t>Full Stack Engineer</t>
   </si>
 </sst>
 </file>
@@ -614,7 +638,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:F31"/>
+  <dimension ref="A1:F34"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="45.109375" customWidth="1"/>
@@ -971,7 +995,7 @@
         <v>52</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>6</v>
+        <v>79</v>
       </c>
       <c r="E20" s="2" t="s">
         <v>37</v>
@@ -1007,7 +1031,7 @@
         <v>59</v>
       </c>
       <c r="D22" s="2" t="s">
-        <v>6</v>
+        <v>80</v>
       </c>
       <c r="E22" s="2" t="s">
         <v>37</v>
@@ -1153,7 +1177,7 @@
         <v>67</v>
       </c>
       <c r="D30" s="2" t="s">
-        <v>6</v>
+        <v>36</v>
       </c>
       <c r="E30" s="2" t="s">
         <v>75</v>
@@ -1173,13 +1197,61 @@
         <v>77</v>
       </c>
       <c r="D31" s="2" t="s">
-        <v>6</v>
+        <v>36</v>
       </c>
       <c r="E31" s="2" t="s">
         <v>75</v>
       </c>
       <c r="F31" s="4" t="s">
         <v>76</v>
+      </c>
+    </row>
+    <row r="32" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A32" s="2" t="s">
+        <v>82</v>
+      </c>
+      <c r="C32" s="2" t="s">
+        <v>83</v>
+      </c>
+      <c r="D32" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="E32" s="2" t="s">
+        <v>82</v>
+      </c>
+      <c r="F32" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="33" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A33" s="2" t="s">
+        <v>85</v>
+      </c>
+      <c r="C33" s="2" t="s">
+        <v>67</v>
+      </c>
+      <c r="D33" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="E33" s="2" t="s">
+        <v>85</v>
+      </c>
+      <c r="F33" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="34" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A34" s="2" t="s">
+        <v>85</v>
+      </c>
+      <c r="C34" s="2" t="s">
+        <v>86</v>
+      </c>
+      <c r="D34" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="E34" s="2" t="s">
+        <v>85</v>
       </c>
     </row>
   </sheetData>

--- a/documents/job-applications.xlsx
+++ b/documents/job-applications.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\LARRY\Documents\Scripts\auto-job-app-sender\documents\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{66D5628A-170C-4353-884B-8296412F642F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C64EBBE4-F638-4976-9586-176BDC735CFD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="169" uniqueCount="87">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="218" uniqueCount="106">
   <si>
     <t>company</t>
   </si>
@@ -286,13 +286,70 @@
   </si>
   <si>
     <t>Full Stack Engineer</t>
+  </si>
+  <si>
+    <t>Avensys Consulting, Inc.</t>
+  </si>
+  <si>
+    <t>Jobstreet</t>
+  </si>
+  <si>
+    <t>Globe Telecom</t>
+  </si>
+  <si>
+    <t>AI Application Engineer</t>
+  </si>
+  <si>
+    <t>Jollibee Foods Corps.</t>
+  </si>
+  <si>
+    <t>https://globe.wd3.myworkdayjobs.com/en-US/GLB_Careers/userHome</t>
+  </si>
+  <si>
+    <t>Workday</t>
+  </si>
+  <si>
+    <t>https://career44.sapsf.com/portalcareer?_s.crb=WdTlZwrjLvKJ1a3ELEhYl4s8XneOF2cXwbcEyqtJOhU%253d</t>
+  </si>
+  <si>
+    <t>Insight</t>
+  </si>
+  <si>
+    <t>Q2 HR Solutions Inc.</t>
+  </si>
+  <si>
+    <t>TQA</t>
+  </si>
+  <si>
+    <t>Manulife</t>
+  </si>
+  <si>
+    <t>https://manulife.wd3.myworkdayjobs.com/</t>
+  </si>
+  <si>
+    <t>Okada</t>
+  </si>
+  <si>
+    <t>Gcash</t>
+  </si>
+  <si>
+    <t>Senior Machine Learning Researcher</t>
+  </si>
+  <si>
+    <t>https://globe.wd3.myworkdayjobs.com/en-US/Mynt/userHome</t>
+  </si>
+  <si>
+    <t>Machine Learning Operations Engineer</t>
+  </si>
+  <si>
+    <t>Cardinal Health International Philippines Inc.</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="4" x14ac:knownFonts="1">
+  <fonts count="5" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -321,6 +378,13 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF2E3849"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
   <fills count="2">
     <fill>
@@ -343,7 +407,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
@@ -357,6 +421,8 @@
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
@@ -638,7 +704,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:F34"/>
+  <dimension ref="A1:F45"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="45.109375" customWidth="1"/>
@@ -1210,6 +1276,7 @@
       <c r="A32" s="2" t="s">
         <v>82</v>
       </c>
+      <c r="B32" s="7"/>
       <c r="C32" s="2" t="s">
         <v>83</v>
       </c>
@@ -1219,7 +1286,7 @@
       <c r="E32" s="2" t="s">
         <v>82</v>
       </c>
-      <c r="F32" t="s">
+      <c r="F32" s="7" t="s">
         <v>81</v>
       </c>
     </row>
@@ -1227,6 +1294,7 @@
       <c r="A33" s="2" t="s">
         <v>85</v>
       </c>
+      <c r="B33" s="7"/>
       <c r="C33" s="2" t="s">
         <v>67</v>
       </c>
@@ -1236,7 +1304,7 @@
       <c r="E33" s="2" t="s">
         <v>85</v>
       </c>
-      <c r="F33" t="s">
+      <c r="F33" s="7" t="s">
         <v>84</v>
       </c>
     </row>
@@ -1244,6 +1312,7 @@
       <c r="A34" s="2" t="s">
         <v>85</v>
       </c>
+      <c r="B34" s="7"/>
       <c r="C34" s="2" t="s">
         <v>86</v>
       </c>
@@ -1253,6 +1322,193 @@
       <c r="E34" s="2" t="s">
         <v>85</v>
       </c>
+      <c r="F34" s="7"/>
+    </row>
+    <row r="35" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A35" s="2" t="s">
+        <v>87</v>
+      </c>
+      <c r="B35" s="7"/>
+      <c r="C35" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="D35" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="E35" s="2" t="s">
+        <v>88</v>
+      </c>
+      <c r="F35" s="7"/>
+    </row>
+    <row r="36" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A36" s="2" t="s">
+        <v>89</v>
+      </c>
+      <c r="B36" s="7"/>
+      <c r="C36" s="2" t="s">
+        <v>90</v>
+      </c>
+      <c r="D36" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="E36" s="2" t="s">
+        <v>93</v>
+      </c>
+      <c r="F36" s="7" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="37" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A37" s="2" t="s">
+        <v>91</v>
+      </c>
+      <c r="B37" s="7"/>
+      <c r="C37" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="D37" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="E37" s="2" t="s">
+        <v>93</v>
+      </c>
+      <c r="F37" s="7" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="38" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A38" s="2" t="s">
+        <v>95</v>
+      </c>
+      <c r="B38" s="7"/>
+      <c r="C38" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="D38" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="E38" s="2" t="s">
+        <v>88</v>
+      </c>
+      <c r="F38" s="7"/>
+    </row>
+    <row r="39" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A39" s="8" t="s">
+        <v>96</v>
+      </c>
+      <c r="B39" s="7"/>
+      <c r="C39" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="D39" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="E39" s="2" t="s">
+        <v>88</v>
+      </c>
+      <c r="F39" s="7"/>
+    </row>
+    <row r="40" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A40" s="2" t="s">
+        <v>97</v>
+      </c>
+      <c r="B40" s="7"/>
+      <c r="C40" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="D40" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="E40" s="2" t="s">
+        <v>88</v>
+      </c>
+      <c r="F40" s="7"/>
+    </row>
+    <row r="41" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A41" s="2" t="s">
+        <v>98</v>
+      </c>
+      <c r="B41" s="7"/>
+      <c r="C41" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="D41" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="E41" s="2" t="s">
+        <v>88</v>
+      </c>
+      <c r="F41" s="7" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="42" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A42" s="2" t="s">
+        <v>100</v>
+      </c>
+      <c r="B42" s="7"/>
+      <c r="C42" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="D42" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="E42" s="2" t="s">
+        <v>88</v>
+      </c>
+      <c r="F42" s="7"/>
+    </row>
+    <row r="43" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A43" s="2" t="s">
+        <v>101</v>
+      </c>
+      <c r="B43" s="7"/>
+      <c r="C43" s="2" t="s">
+        <v>102</v>
+      </c>
+      <c r="D43" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="E43" s="2" t="s">
+        <v>88</v>
+      </c>
+      <c r="F43" s="7" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="44" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A44" s="2" t="s">
+        <v>101</v>
+      </c>
+      <c r="B44" s="7"/>
+      <c r="C44" s="2" t="s">
+        <v>104</v>
+      </c>
+      <c r="D44" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="E44" s="2" t="s">
+        <v>88</v>
+      </c>
+      <c r="F44" s="7" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="45" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A45" s="7" t="s">
+        <v>105</v>
+      </c>
+      <c r="B45" s="7"/>
+      <c r="C45" s="2" t="s">
+        <v>67</v>
+      </c>
+      <c r="D45" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="E45" s="2" t="s">
+        <v>88</v>
+      </c>
+      <c r="F45" s="7"/>
     </row>
   </sheetData>
   <hyperlinks>
@@ -1264,5 +1520,6 @@
     <hyperlink ref="F31" r:id="rId6" xr:uid="{3141AFC0-D998-4026-86A8-ED9E9752D6FA}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" r:id="rId7"/>
 </worksheet>
 </file>
--- a/documents/job-applications.xlsx
+++ b/documents/job-applications.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\LARRY\Documents\Scripts\auto-job-app-sender\documents\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C64EBBE4-F638-4976-9586-176BDC735CFD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C34E9C1F-35A1-46D9-A053-FA95C64FD242}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -264,9 +264,6 @@
     <t>careers@thinkingmachines.freshteam.com</t>
   </si>
   <si>
-    <t>Interview Pending</t>
-  </si>
-  <si>
     <t>Shortlisted</t>
   </si>
   <si>
@@ -343,6 +340,9 @@
   </si>
   <si>
     <t>Cardinal Health International Philippines Inc.</t>
+  </si>
+  <si>
+    <t>Tech Interiew Done</t>
   </si>
 </sst>
 </file>
@@ -407,7 +407,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
@@ -421,7 +421,6 @@
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="2">
@@ -1061,7 +1060,7 @@
         <v>52</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>79</v>
+        <v>105</v>
       </c>
       <c r="E20" s="2" t="s">
         <v>37</v>
@@ -1097,7 +1096,7 @@
         <v>59</v>
       </c>
       <c r="D22" s="2" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="E22" s="2" t="s">
         <v>37</v>
@@ -1274,27 +1273,25 @@
     </row>
     <row r="32" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A32" s="2" t="s">
+        <v>81</v>
+      </c>
+      <c r="C32" s="2" t="s">
         <v>82</v>
       </c>
-      <c r="B32" s="7"/>
-      <c r="C32" s="2" t="s">
-        <v>83</v>
-      </c>
       <c r="D32" s="2" t="s">
         <v>6</v>
       </c>
       <c r="E32" s="2" t="s">
-        <v>82</v>
-      </c>
-      <c r="F32" s="7" t="s">
         <v>81</v>
+      </c>
+      <c r="F32" t="s">
+        <v>80</v>
       </c>
     </row>
     <row r="33" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A33" s="2" t="s">
-        <v>85</v>
-      </c>
-      <c r="B33" s="7"/>
+        <v>84</v>
+      </c>
       <c r="C33" s="2" t="s">
         <v>67</v>
       </c>
@@ -1302,33 +1299,30 @@
         <v>6</v>
       </c>
       <c r="E33" s="2" t="s">
-        <v>85</v>
-      </c>
-      <c r="F33" s="7" t="s">
         <v>84</v>
+      </c>
+      <c r="F33" t="s">
+        <v>83</v>
       </c>
     </row>
     <row r="34" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A34" s="2" t="s">
+        <v>84</v>
+      </c>
+      <c r="C34" s="2" t="s">
         <v>85</v>
       </c>
-      <c r="B34" s="7"/>
-      <c r="C34" s="2" t="s">
-        <v>86</v>
-      </c>
       <c r="D34" s="2" t="s">
         <v>6</v>
       </c>
       <c r="E34" s="2" t="s">
-        <v>85</v>
-      </c>
-      <c r="F34" s="7"/>
+        <v>84</v>
+      </c>
     </row>
     <row r="35" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A35" s="2" t="s">
-        <v>87</v>
-      </c>
-      <c r="B35" s="7"/>
+        <v>86</v>
+      </c>
       <c r="C35" s="2" t="s">
         <v>47</v>
       </c>
@@ -1336,33 +1330,30 @@
         <v>6</v>
       </c>
       <c r="E35" s="2" t="s">
-        <v>88</v>
-      </c>
-      <c r="F35" s="7"/>
+        <v>87</v>
+      </c>
     </row>
     <row r="36" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A36" s="2" t="s">
+        <v>88</v>
+      </c>
+      <c r="C36" s="2" t="s">
         <v>89</v>
       </c>
-      <c r="B36" s="7"/>
-      <c r="C36" s="2" t="s">
-        <v>90</v>
-      </c>
       <c r="D36" s="2" t="s">
         <v>6</v>
       </c>
       <c r="E36" s="2" t="s">
-        <v>93</v>
-      </c>
-      <c r="F36" s="7" t="s">
         <v>92</v>
+      </c>
+      <c r="F36" t="s">
+        <v>91</v>
       </c>
     </row>
     <row r="37" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A37" s="2" t="s">
-        <v>91</v>
-      </c>
-      <c r="B37" s="7"/>
+        <v>90</v>
+      </c>
       <c r="C37" s="2" t="s">
         <v>45</v>
       </c>
@@ -1370,17 +1361,16 @@
         <v>6</v>
       </c>
       <c r="E37" s="2" t="s">
+        <v>92</v>
+      </c>
+      <c r="F37" t="s">
         <v>93</v>
-      </c>
-      <c r="F37" s="7" t="s">
-        <v>94</v>
       </c>
     </row>
     <row r="38" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A38" s="2" t="s">
-        <v>95</v>
-      </c>
-      <c r="B38" s="7"/>
+        <v>94</v>
+      </c>
       <c r="C38" s="2" t="s">
         <v>48</v>
       </c>
@@ -1388,15 +1378,13 @@
         <v>6</v>
       </c>
       <c r="E38" s="2" t="s">
-        <v>88</v>
-      </c>
-      <c r="F38" s="7"/>
+        <v>87</v>
+      </c>
     </row>
     <row r="39" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A39" s="8" t="s">
-        <v>96</v>
-      </c>
-      <c r="B39" s="7"/>
+      <c r="A39" s="7" t="s">
+        <v>95</v>
+      </c>
       <c r="C39" s="2" t="s">
         <v>45</v>
       </c>
@@ -1404,15 +1392,13 @@
         <v>6</v>
       </c>
       <c r="E39" s="2" t="s">
-        <v>88</v>
-      </c>
-      <c r="F39" s="7"/>
+        <v>87</v>
+      </c>
     </row>
     <row r="40" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A40" s="2" t="s">
-        <v>97</v>
-      </c>
-      <c r="B40" s="7"/>
+        <v>96</v>
+      </c>
       <c r="C40" s="2" t="s">
         <v>45</v>
       </c>
@@ -1420,15 +1406,13 @@
         <v>6</v>
       </c>
       <c r="E40" s="2" t="s">
-        <v>88</v>
-      </c>
-      <c r="F40" s="7"/>
+        <v>87</v>
+      </c>
     </row>
     <row r="41" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A41" s="2" t="s">
-        <v>98</v>
-      </c>
-      <c r="B41" s="7"/>
+        <v>97</v>
+      </c>
       <c r="C41" s="2" t="s">
         <v>45</v>
       </c>
@@ -1436,17 +1420,16 @@
         <v>6</v>
       </c>
       <c r="E41" s="2" t="s">
-        <v>88</v>
-      </c>
-      <c r="F41" s="7" t="s">
-        <v>99</v>
+        <v>87</v>
+      </c>
+      <c r="F41" t="s">
+        <v>98</v>
       </c>
     </row>
     <row r="42" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A42" s="2" t="s">
-        <v>100</v>
-      </c>
-      <c r="B42" s="7"/>
+        <v>99</v>
+      </c>
       <c r="C42" s="2" t="s">
         <v>45</v>
       </c>
@@ -1454,51 +1437,47 @@
         <v>6</v>
       </c>
       <c r="E42" s="2" t="s">
-        <v>88</v>
-      </c>
-      <c r="F42" s="7"/>
+        <v>87</v>
+      </c>
     </row>
     <row r="43" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A43" s="2" t="s">
+        <v>100</v>
+      </c>
+      <c r="C43" s="2" t="s">
         <v>101</v>
       </c>
-      <c r="B43" s="7"/>
-      <c r="C43" s="2" t="s">
+      <c r="D43" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="E43" s="2" t="s">
+        <v>87</v>
+      </c>
+      <c r="F43" t="s">
         <v>102</v>
-      </c>
-      <c r="D43" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="E43" s="2" t="s">
-        <v>88</v>
-      </c>
-      <c r="F43" s="7" t="s">
-        <v>103</v>
       </c>
     </row>
     <row r="44" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A44" s="2" t="s">
-        <v>101</v>
-      </c>
-      <c r="B44" s="7"/>
+        <v>100</v>
+      </c>
       <c r="C44" s="2" t="s">
+        <v>103</v>
+      </c>
+      <c r="D44" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="E44" s="2" t="s">
+        <v>87</v>
+      </c>
+      <c r="F44" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="45" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A45" t="s">
         <v>104</v>
       </c>
-      <c r="D44" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="E44" s="2" t="s">
-        <v>88</v>
-      </c>
-      <c r="F44" s="7" t="s">
-        <v>103</v>
-      </c>
-    </row>
-    <row r="45" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A45" s="7" t="s">
-        <v>105</v>
-      </c>
-      <c r="B45" s="7"/>
       <c r="C45" s="2" t="s">
         <v>67</v>
       </c>
@@ -1506,9 +1485,8 @@
         <v>6</v>
       </c>
       <c r="E45" s="2" t="s">
-        <v>88</v>
-      </c>
-      <c r="F45" s="7"/>
+        <v>87</v>
+      </c>
     </row>
   </sheetData>
   <hyperlinks>

--- a/documents/job-applications.xlsx
+++ b/documents/job-applications.xlsx
@@ -1,20 +1,26 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <fileVersion rupBuild="9303" lowestEdited="5" lastEdited="5" appName="xl"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="28324"/>
   <workbookPr/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\LARRY\Documents\Scripts\auto-job-app-sender\documents\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{42DD6FC9-2256-4FD2-92DC-8F3C27ADA0AF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="480" yWindow="60" windowWidth="18195" windowHeight="8505" activeTab="0"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet r:id="rId1" sheetId="1" name="Sheet1"/>
+    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr fullCalcOnLoad="1"/>
+  <calcPr calcId="0"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="218" uniqueCount="106">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="322" uniqueCount="147">
   <si>
     <t>company</t>
   </si>
@@ -332,14 +338,136 @@
   </si>
   <si>
     <t>Cardinal Health International Philippines Inc.</t>
+  </si>
+  <si>
+    <t>Philippine Airlines</t>
+  </si>
+  <si>
+    <t>Inquired</t>
+  </si>
+  <si>
+    <t>recruiter</t>
+  </si>
+  <si>
+    <t>catherine_alhambra@pal.com.ph</t>
+  </si>
+  <si>
+    <t>qramos@netflix.com</t>
+  </si>
+  <si>
+    <t>Netflix</t>
+  </si>
+  <si>
+    <t>Zendesk</t>
+  </si>
+  <si>
+    <t>giannedeniseduenas@gmail.com</t>
+  </si>
+  <si>
+    <t>restil.vss@gmail.com</t>
+  </si>
+  <si>
+    <t>Virtual Staffing Solutions</t>
+  </si>
+  <si>
+    <t>jayson@blissgrowth.com</t>
+  </si>
+  <si>
+    <t>Stashed</t>
+  </si>
+  <si>
+    <t>Blissgrowth</t>
+  </si>
+  <si>
+    <t>angeliqu.misa@vxi.com</t>
+  </si>
+  <si>
+    <t>joymariedeguzman.817@gmail.com</t>
+  </si>
+  <si>
+    <t>VXI</t>
+  </si>
+  <si>
+    <t>daniella.mae.m.bisda@accenture.com. </t>
+  </si>
+  <si>
+    <t>NCS Group</t>
+  </si>
+  <si>
+    <t>LinkedIn</t>
+  </si>
+  <si>
+    <t>Manpower Ph</t>
+  </si>
+  <si>
+    <t>Azeus Systems Limited</t>
+  </si>
+  <si>
+    <t>AI Developer</t>
+  </si>
+  <si>
+    <t>GoTyme</t>
+  </si>
+  <si>
+    <t>https://gotyme.bamboohr.com/careers/262</t>
+  </si>
+  <si>
+    <t>Socium</t>
+  </si>
+  <si>
+    <t>Maya</t>
+  </si>
+  <si>
+    <t>Emerson</t>
+  </si>
+  <si>
+    <t>Software Developer</t>
+  </si>
+  <si>
+    <t>Code and Theory</t>
+  </si>
+  <si>
+    <t>https://www.codeandtheory.com/careers/</t>
+  </si>
+  <si>
+    <t>https://manulife.wd3.myworkdayjobs.com/en-US/MFCJH_Jobs/</t>
+  </si>
+  <si>
+    <t>Wimmer Solutions</t>
+  </si>
+  <si>
+    <t>Trend Micro</t>
+  </si>
+  <si>
+    <t>Concentrix</t>
+  </si>
+  <si>
+    <t>Data Engineer w/ Salesforce Expertise</t>
+  </si>
+  <si>
+    <t>Senior Data Engineer</t>
+  </si>
+  <si>
+    <t>Universal Access and Systems Solutions, Inc.</t>
+  </si>
+  <si>
+    <t>Lead Software Engineer</t>
+  </si>
+  <si>
+    <t>ING</t>
+  </si>
+  <si>
+    <t>Required</t>
+  </si>
+  <si>
+    <t>Rejected but keep in touch for possible internship</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" mc:Ignorable="x14ac">
-  <numFmts count="0"/>
-  <fonts count="4" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -348,30 +476,32 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <u/>
       <sz val="11"/>
-      <color theme="1"/>
+      <color theme="10"/>
       <name val="Calibri"/>
       <family val="2"/>
+      <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF222222"/>
       <name val="Calibri"/>
       <family val="2"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF2e3849"/>
-      <name val="Calibri"/>
-      <family val="2"/>
+      <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="2">
+  <fills count="3">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFFF"/>
+        <bgColor indexed="64"/>
+      </patternFill>
     </fill>
   </fills>
   <borders count="2">
@@ -390,38 +520,36 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
-    <xf xfId="0" numFmtId="0" borderId="0" fontId="0" fillId="0"/>
-    <xf xfId="0" numFmtId="0" borderId="1" applyBorder="1" fontId="1" applyFont="1" fillId="0" applyAlignment="1">
+  <cellXfs count="6">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf xfId="0" numFmtId="0" borderId="1" applyBorder="1" fontId="1" applyFont="1" fillId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
-    <xf xfId="0" numFmtId="0" borderId="1" applyBorder="1" fontId="2" applyFont="1" fillId="0" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf xfId="0" numFmtId="0" borderId="0" fontId="0" fillId="0" applyAlignment="1">
-      <alignment horizontal="general"/>
-    </xf>
-    <xf xfId="0" numFmtId="0" borderId="1" applyBorder="1" fontId="3" applyFont="1" fillId="0" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf xfId="0" numFmtId="0" borderId="0" fontId="0" fillId="0" applyAlignment="1">
-      <alignment horizontal="general"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
-  <cellStyles count="1">
-    <cellStyle xfId="0" builtinId="0" name="Normal"/>
+  <cellStyles count="2">
+    <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
-    <ext uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
-      <x14ac:slicerStyles xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" defaultSlicerStyle="SlicerStyleLight1"/>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
     </ext>
   </extLst>
 </styleSheet>
@@ -432,10 +560,10 @@
   <a:themeElements>
     <a:clrScheme name="Office">
       <a:dk1>
-        <a:sysClr lastClr="000000" val="windowText"/>
+        <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
       <a:lt1>
-        <a:sysClr lastClr="FFFFFF" val="window"/>
+        <a:sysClr val="window" lastClr="FFFFFF"/>
       </a:lt1>
       <a:dk2>
         <a:srgbClr val="44546A"/>
@@ -473,71 +601,71 @@
         <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
-        <a:font typeface="ＭＳ Ｐゴシック" script="Jpan"/>
-        <a:font typeface="맑은 고딕" script="Hang"/>
-        <a:font typeface="宋体" script="Hans"/>
-        <a:font typeface="新細明體" script="Hant"/>
-        <a:font typeface="Times New Roman" script="Arab"/>
-        <a:font typeface="Times New Roman" script="Hebr"/>
-        <a:font typeface="Tahoma" script="Thai"/>
-        <a:font typeface="Nyala" script="Ethi"/>
-        <a:font typeface="Vrinda" script="Beng"/>
-        <a:font typeface="Shruti" script="Gujr"/>
-        <a:font typeface="MoolBoran" script="Khmr"/>
-        <a:font typeface="Tunga" script="Knda"/>
-        <a:font typeface="Raavi" script="Guru"/>
-        <a:font typeface="Euphemia" script="Cans"/>
-        <a:font typeface="Plantagenet Cherokee" script="Cher"/>
-        <a:font typeface="Microsoft Yi Baiti" script="Yiii"/>
-        <a:font typeface="Microsoft Himalaya" script="Tibt"/>
-        <a:font typeface="MV Boli" script="Thaa"/>
-        <a:font typeface="Mangal" script="Deva"/>
-        <a:font typeface="Gautami" script="Telu"/>
-        <a:font typeface="Latha" script="Taml"/>
-        <a:font typeface="Estrangelo Edessa" script="Syrc"/>
-        <a:font typeface="Kalinga" script="Orya"/>
-        <a:font typeface="Kartika" script="Mlym"/>
-        <a:font typeface="DokChampa" script="Laoo"/>
-        <a:font typeface="Iskoola Pota" script="Sinh"/>
-        <a:font typeface="Mongolian Baiti" script="Mong"/>
-        <a:font typeface="Times New Roman" script="Viet"/>
-        <a:font typeface="Microsoft Uighur" script="Uigh"/>
-        <a:font typeface="Sylfaen" script="Geor"/>
+        <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
+        <a:font script="Hang" typeface="맑은 고딕"/>
+        <a:font script="Hans" typeface="宋体"/>
+        <a:font script="Hant" typeface="新細明體"/>
+        <a:font script="Arab" typeface="Times New Roman"/>
+        <a:font script="Hebr" typeface="Times New Roman"/>
+        <a:font script="Thai" typeface="Tahoma"/>
+        <a:font script="Ethi" typeface="Nyala"/>
+        <a:font script="Beng" typeface="Vrinda"/>
+        <a:font script="Gujr" typeface="Shruti"/>
+        <a:font script="Khmr" typeface="MoolBoran"/>
+        <a:font script="Knda" typeface="Tunga"/>
+        <a:font script="Guru" typeface="Raavi"/>
+        <a:font script="Cans" typeface="Euphemia"/>
+        <a:font script="Cher" typeface="Plantagenet Cherokee"/>
+        <a:font script="Yiii" typeface="Microsoft Yi Baiti"/>
+        <a:font script="Tibt" typeface="Microsoft Himalaya"/>
+        <a:font script="Thaa" typeface="MV Boli"/>
+        <a:font script="Deva" typeface="Mangal"/>
+        <a:font script="Telu" typeface="Gautami"/>
+        <a:font script="Taml" typeface="Latha"/>
+        <a:font script="Syrc" typeface="Estrangelo Edessa"/>
+        <a:font script="Orya" typeface="Kalinga"/>
+        <a:font script="Mlym" typeface="Kartika"/>
+        <a:font script="Laoo" typeface="DokChampa"/>
+        <a:font script="Sinh" typeface="Iskoola Pota"/>
+        <a:font script="Mong" typeface="Mongolian Baiti"/>
+        <a:font script="Viet" typeface="Times New Roman"/>
+        <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
         <a:latin typeface="Calibri"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
-        <a:font typeface="ＭＳ Ｐゴシック" script="Jpan"/>
-        <a:font typeface="맑은 고딕" script="Hang"/>
-        <a:font typeface="宋体" script="Hans"/>
-        <a:font typeface="新細明體" script="Hant"/>
-        <a:font typeface="Arial" script="Arab"/>
-        <a:font typeface="Arial" script="Hebr"/>
-        <a:font typeface="Tahoma" script="Thai"/>
-        <a:font typeface="Nyala" script="Ethi"/>
-        <a:font typeface="Vrinda" script="Beng"/>
-        <a:font typeface="Shruti" script="Gujr"/>
-        <a:font typeface="DaunPenh" script="Khmr"/>
-        <a:font typeface="Tunga" script="Knda"/>
-        <a:font typeface="Raavi" script="Guru"/>
-        <a:font typeface="Euphemia" script="Cans"/>
-        <a:font typeface="Plantagenet Cherokee" script="Cher"/>
-        <a:font typeface="Microsoft Yi Baiti" script="Yiii"/>
-        <a:font typeface="Microsoft Himalaya" script="Tibt"/>
-        <a:font typeface="MV Boli" script="Thaa"/>
-        <a:font typeface="Mangal" script="Deva"/>
-        <a:font typeface="Gautami" script="Telu"/>
-        <a:font typeface="Latha" script="Taml"/>
-        <a:font typeface="Estrangelo Edessa" script="Syrc"/>
-        <a:font typeface="Kalinga" script="Orya"/>
-        <a:font typeface="Kartika" script="Mlym"/>
-        <a:font typeface="DokChampa" script="Laoo"/>
-        <a:font typeface="Iskoola Pota" script="Sinh"/>
-        <a:font typeface="Mongolian Baiti" script="Mong"/>
-        <a:font typeface="Arial" script="Viet"/>
-        <a:font typeface="Microsoft Uighur" script="Uigh"/>
-        <a:font typeface="Sylfaen" script="Geor"/>
+        <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
+        <a:font script="Hang" typeface="맑은 고딕"/>
+        <a:font script="Hans" typeface="宋体"/>
+        <a:font script="Hant" typeface="新細明體"/>
+        <a:font script="Arab" typeface="Arial"/>
+        <a:font script="Hebr" typeface="Arial"/>
+        <a:font script="Thai" typeface="Tahoma"/>
+        <a:font script="Ethi" typeface="Nyala"/>
+        <a:font script="Beng" typeface="Vrinda"/>
+        <a:font script="Gujr" typeface="Shruti"/>
+        <a:font script="Khmr" typeface="DaunPenh"/>
+        <a:font script="Knda" typeface="Tunga"/>
+        <a:font script="Guru" typeface="Raavi"/>
+        <a:font script="Cans" typeface="Euphemia"/>
+        <a:font script="Cher" typeface="Plantagenet Cherokee"/>
+        <a:font script="Yiii" typeface="Microsoft Yi Baiti"/>
+        <a:font script="Tibt" typeface="Microsoft Himalaya"/>
+        <a:font script="Thaa" typeface="MV Boli"/>
+        <a:font script="Deva" typeface="Mangal"/>
+        <a:font script="Telu" typeface="Gautami"/>
+        <a:font script="Taml" typeface="Latha"/>
+        <a:font script="Syrc" typeface="Estrangelo Edessa"/>
+        <a:font script="Orya" typeface="Kalinga"/>
+        <a:font script="Mlym" typeface="Kartika"/>
+        <a:font script="Laoo" typeface="DokChampa"/>
+        <a:font script="Sinh" typeface="Iskoola Pota"/>
+        <a:font script="Mong" typeface="Mongolian Baiti"/>
+        <a:font script="Viet" typeface="Arial"/>
+        <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
       </a:minorFont>
     </a:fontScheme>
     <a:fmtScheme name="Office">
@@ -565,7 +693,7 @@
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
-          <a:lin scaled="1" ang="16200000"/>
+          <a:lin ang="16200000" scaled="1"/>
         </a:gradFill>
         <a:gradFill rotWithShape="1">
           <a:gsLst>
@@ -588,11 +716,11 @@
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
-          <a:lin scaled="1" ang="16200000"/>
+          <a:lin ang="16200000" scaled="1"/>
         </a:gradFill>
       </a:fillStyleLst>
       <a:lnStyleLst>
-        <a:ln algn="ctr" cmpd="sng" cap="flat" w="9525">
+        <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
           <a:solidFill>
             <a:schemeClr val="phClr">
               <a:shade val="9500"/>
@@ -601,13 +729,13 @@
           </a:solidFill>
           <a:prstDash val="solid"/>
         </a:ln>
-        <a:ln algn="ctr" cmpd="sng" cap="flat" w="25400">
+        <a:ln w="25400" cap="flat" cmpd="sng" algn="ctr">
           <a:solidFill>
             <a:schemeClr val="phClr"/>
           </a:solidFill>
           <a:prstDash val="solid"/>
         </a:ln>
-        <a:ln algn="ctr" cmpd="sng" cap="flat" w="38100">
+        <a:ln w="38100" cap="flat" cmpd="sng" algn="ctr">
           <a:solidFill>
             <a:schemeClr val="phClr"/>
           </a:solidFill>
@@ -617,7 +745,7 @@
       <a:effectStyleLst>
         <a:effectStyle>
           <a:effectLst>
-            <a:outerShdw dir="5400000" rotWithShape="0" dist="23000" blurRad="40000">
+            <a:outerShdw blurRad="40000" dist="23000" dir="5400000" rotWithShape="0">
               <a:srgbClr val="000000">
                 <a:alpha val="38000"/>
               </a:srgbClr>
@@ -626,7 +754,7 @@
         </a:effectStyle>
         <a:effectStyle>
           <a:effectLst>
-            <a:outerShdw dir="5400000" rotWithShape="0" dist="23000" blurRad="40000">
+            <a:outerShdw blurRad="40000" dist="23000" dir="5400000" rotWithShape="0">
               <a:srgbClr val="000000">
                 <a:alpha val="35000"/>
               </a:srgbClr>
@@ -635,7 +763,7 @@
         </a:effectStyle>
         <a:effectStyle>
           <a:effectLst>
-            <a:outerShdw dir="5400000" rotWithShape="0" dist="23000" blurRad="40000">
+            <a:outerShdw blurRad="40000" dist="23000" dir="5400000" rotWithShape="0">
               <a:srgbClr val="000000">
                 <a:alpha val="35000"/>
               </a:srgbClr>
@@ -643,10 +771,10 @@
           </a:effectLst>
           <a:scene3d>
             <a:camera prst="orthographicFront">
-              <a:rot rev="0" lon="0" lat="0"/>
+              <a:rot lat="0" lon="0" rev="0"/>
             </a:camera>
-            <a:lightRig dir="t" rig="threePt">
-              <a:rot rev="1200000" lon="0" lat="0"/>
+            <a:lightRig rig="threePt" dir="t">
+              <a:rot lat="0" lon="0" rev="1200000"/>
             </a:lightRig>
           </a:scene3d>
           <a:sp3d>
@@ -711,22 +839,24 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <sheetPr>
     <outlinePr summaryBelow="0"/>
   </sheetPr>
-  <dimension ref="A1:F45"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <dimension ref="A1:H70"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" style="6" width="45.14785714285715" customWidth="1" bestFit="1"/>
-    <col min="2" max="2" style="6" width="36.43357142857143" customWidth="1" bestFit="1"/>
-    <col min="3" max="3" style="6" width="46.43357142857143" customWidth="1" bestFit="1"/>
-    <col min="4" max="4" style="6" width="25.433571428571426" customWidth="1" bestFit="1"/>
-    <col min="5" max="5" style="6" width="13.576428571428572" customWidth="1" bestFit="1"/>
-    <col min="6" max="6" style="6" width="39.71928571428572" customWidth="1" bestFit="1"/>
+    <col min="1" max="1" width="45.109375" style="2" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="36.44140625" style="2" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="46.44140625" style="2" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="25.44140625" style="2" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="13.5546875" style="2" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="53.109375" style="2" customWidth="1"/>
+    <col min="7" max="7" width="22.6640625" style="2" customWidth="1"/>
+    <col min="8" max="16384" width="8.88671875" style="2"/>
   </cols>
   <sheetData>
-    <row x14ac:dyDescent="0.25" r="1" customHeight="1" ht="19.5">
+    <row r="1" spans="1:7" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -745,8 +875,11 @@
       <c r="F1" s="1" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row x14ac:dyDescent="0.25" r="2" customHeight="1" ht="19.5">
+      <c r="G1" s="1" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="2" spans="1:7" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="1" t="s">
         <v>6</v>
       </c>
@@ -764,7 +897,7 @@
         <v>10</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="3" customHeight="1" ht="19.5">
+    <row r="3" spans="1:7" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3" s="1" t="s">
         <v>6</v>
       </c>
@@ -782,7 +915,7 @@
         <v>10</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="4" customHeight="1" ht="19.5">
+    <row r="4" spans="1:7" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A4" s="1" t="s">
         <v>13</v>
       </c>
@@ -798,7 +931,7 @@
       </c>
       <c r="F4" s="1"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="5" customHeight="1" ht="19.5">
+    <row r="5" spans="1:7" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A5" s="1" t="s">
         <v>15</v>
       </c>
@@ -816,7 +949,7 @@
         <v>16</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="6" customHeight="1" ht="19.5">
+    <row r="6" spans="1:7" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A6" s="1" t="s">
         <v>17</v>
       </c>
@@ -832,7 +965,7 @@
       </c>
       <c r="F6" s="1"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="7" customHeight="1" ht="19.5">
+    <row r="7" spans="1:7" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A7" s="1" t="s">
         <v>17</v>
       </c>
@@ -848,12 +981,12 @@
       </c>
       <c r="F7" s="1"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="8" customHeight="1" ht="33">
+    <row r="8" spans="1:7" ht="33" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A8" s="1" t="s">
         <v>20</v>
       </c>
       <c r="B8" s="1"/>
-      <c r="C8" s="2" t="s">
+      <c r="C8" s="3" t="s">
         <v>21</v>
       </c>
       <c r="D8" s="1" t="s">
@@ -866,12 +999,12 @@
         <v>22</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="9" customHeight="1" ht="19.5">
+    <row r="9" spans="1:7" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A9" s="1" t="s">
         <v>20</v>
       </c>
       <c r="B9" s="1"/>
-      <c r="C9" s="2" t="s">
+      <c r="C9" s="3" t="s">
         <v>23</v>
       </c>
       <c r="D9" s="1" t="s">
@@ -884,12 +1017,12 @@
         <v>22</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="10" customHeight="1" ht="19.5">
+    <row r="10" spans="1:7" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A10" s="1" t="s">
         <v>24</v>
       </c>
       <c r="B10" s="1"/>
-      <c r="C10" s="2" t="s">
+      <c r="C10" s="3" t="s">
         <v>25</v>
       </c>
       <c r="D10" s="1" t="s">
@@ -902,7 +1035,7 @@
         <v>27</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="11" customHeight="1" ht="19.5">
+    <row r="11" spans="1:7" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A11" s="1" t="s">
         <v>28</v>
       </c>
@@ -920,7 +1053,7 @@
         <v>30</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="12" customHeight="1" ht="19.5">
+    <row r="12" spans="1:7" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A12" s="1" t="s">
         <v>31</v>
       </c>
@@ -938,7 +1071,7 @@
         <v>33</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="13" customHeight="1" ht="19.5">
+    <row r="13" spans="1:7" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A13" s="1" t="s">
         <v>34</v>
       </c>
@@ -956,7 +1089,7 @@
         <v>36</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="14" customHeight="1" ht="19.5">
+    <row r="14" spans="1:7" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A14" s="1" t="s">
         <v>37</v>
       </c>
@@ -974,7 +1107,7 @@
         <v>40</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="15" customHeight="1" ht="19.5">
+    <row r="15" spans="1:7" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A15" s="1" t="s">
         <v>37</v>
       </c>
@@ -992,7 +1125,7 @@
         <v>40</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="16" customHeight="1" ht="19.5">
+    <row r="16" spans="1:7" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A16" s="1" t="s">
         <v>42</v>
       </c>
@@ -1010,7 +1143,7 @@
         <v>44</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="17" customHeight="1" ht="19.5">
+    <row r="17" spans="1:6" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A17" s="1" t="s">
         <v>45</v>
       </c>
@@ -1028,8 +1161,8 @@
         <v>47</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="18" customHeight="1" ht="19.5">
-      <c r="A18" s="2" t="s">
+    <row r="18" spans="1:6" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A18" s="3" t="s">
         <v>48</v>
       </c>
       <c r="B18" s="1"/>
@@ -1046,7 +1179,7 @@
         <v>50</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="19" customHeight="1" ht="19.5">
+    <row r="19" spans="1:6" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A19" s="1" t="s">
         <v>51</v>
       </c>
@@ -1064,7 +1197,7 @@
         <v>52</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="20" customHeight="1" ht="19.5">
+    <row r="20" spans="1:6" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A20" s="1" t="s">
         <v>53</v>
       </c>
@@ -1082,7 +1215,7 @@
         <v>56</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="21" customHeight="1" ht="19.5">
+    <row r="21" spans="1:6" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A21" s="1" t="s">
         <v>57</v>
       </c>
@@ -1100,7 +1233,7 @@
         <v>59</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="22" customHeight="1" ht="19.5">
+    <row r="22" spans="1:6" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A22" s="1" t="s">
         <v>57</v>
       </c>
@@ -1118,7 +1251,7 @@
         <v>59</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="23" customHeight="1" ht="19.5">
+    <row r="23" spans="1:6" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A23" s="1" t="s">
         <v>57</v>
       </c>
@@ -1136,7 +1269,7 @@
         <v>59</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="24" customHeight="1" ht="19.5">
+    <row r="24" spans="1:6" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A24" s="1" t="s">
         <v>63</v>
       </c>
@@ -1154,7 +1287,7 @@
         <v>65</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="25" customHeight="1" ht="19.5">
+    <row r="25" spans="1:6" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A25" s="1" t="s">
         <v>66</v>
       </c>
@@ -1172,7 +1305,7 @@
         <v>68</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="26" customHeight="1" ht="19.5">
+    <row r="26" spans="1:6" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A26" s="1" t="s">
         <v>63</v>
       </c>
@@ -1190,7 +1323,7 @@
         <v>65</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="27" customHeight="1" ht="19.5">
+    <row r="27" spans="1:6" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A27" s="1" t="s">
         <v>63</v>
       </c>
@@ -1208,7 +1341,7 @@
         <v>65</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="28" customHeight="1" ht="19.5">
+    <row r="28" spans="1:6" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A28" s="1" t="s">
         <v>71</v>
       </c>
@@ -1226,7 +1359,7 @@
         <v>73</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="29" customHeight="1" ht="19.5">
+    <row r="29" spans="1:6" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A29" s="1" t="s">
         <v>74</v>
       </c>
@@ -1244,11 +1377,11 @@
         <v>76</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="30" customHeight="1" ht="19.5">
+    <row r="30" spans="1:6" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A30" s="1" t="s">
         <v>77</v>
       </c>
-      <c r="B30" s="3" t="s">
+      <c r="B30" s="1" t="s">
         <v>78</v>
       </c>
       <c r="C30" s="1" t="s">
@@ -1264,11 +1397,11 @@
         <v>79</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="31" customHeight="1" ht="19.5">
+    <row r="31" spans="1:6" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A31" s="1" t="s">
         <v>77</v>
       </c>
-      <c r="B31" s="3" t="s">
+      <c r="B31" s="1" t="s">
         <v>78</v>
       </c>
       <c r="C31" s="1" t="s">
@@ -1284,11 +1417,10 @@
         <v>79</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="32" customHeight="1" ht="19.5">
+    <row r="32" spans="1:6" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A32" s="1" t="s">
         <v>81</v>
       </c>
-      <c r="B32" s="4"/>
       <c r="C32" s="1" t="s">
         <v>82</v>
       </c>
@@ -1298,15 +1430,14 @@
       <c r="E32" s="1" t="s">
         <v>81</v>
       </c>
-      <c r="F32" s="4" t="s">
+      <c r="F32" s="2" t="s">
         <v>83</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="33" customHeight="1" ht="19.5">
+    <row r="33" spans="1:8" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A33" s="1" t="s">
         <v>84</v>
       </c>
-      <c r="B33" s="4"/>
       <c r="C33" s="1" t="s">
         <v>69</v>
       </c>
@@ -1316,15 +1447,14 @@
       <c r="E33" s="1" t="s">
         <v>84</v>
       </c>
-      <c r="F33" s="4" t="s">
+      <c r="F33" s="2" t="s">
         <v>85</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="34" customHeight="1" ht="19.5">
+    <row r="34" spans="1:8" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A34" s="1" t="s">
         <v>84</v>
       </c>
-      <c r="B34" s="4"/>
       <c r="C34" s="1" t="s">
         <v>86</v>
       </c>
@@ -1334,13 +1464,11 @@
       <c r="E34" s="1" t="s">
         <v>84</v>
       </c>
-      <c r="F34" s="4"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="35" customHeight="1" ht="19.5">
+    </row>
+    <row r="35" spans="1:8" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A35" s="1" t="s">
         <v>87</v>
       </c>
-      <c r="B35" s="4"/>
       <c r="C35" s="1" t="s">
         <v>46</v>
       </c>
@@ -1350,13 +1478,11 @@
       <c r="E35" s="1" t="s">
         <v>88</v>
       </c>
-      <c r="F35" s="4"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="36" customHeight="1" ht="18.75">
+    </row>
+    <row r="36" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A36" s="1" t="s">
         <v>89</v>
       </c>
-      <c r="B36" s="4"/>
       <c r="C36" s="1" t="s">
         <v>90</v>
       </c>
@@ -1366,15 +1492,14 @@
       <c r="E36" s="1" t="s">
         <v>91</v>
       </c>
-      <c r="F36" s="4" t="s">
+      <c r="F36" s="2" t="s">
         <v>92</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="37" customHeight="1" ht="18.75">
+    <row r="37" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A37" s="1" t="s">
         <v>93</v>
       </c>
-      <c r="B37" s="4"/>
       <c r="C37" s="1" t="s">
         <v>41</v>
       </c>
@@ -1384,15 +1509,14 @@
       <c r="E37" s="1" t="s">
         <v>91</v>
       </c>
-      <c r="F37" s="4" t="s">
+      <c r="F37" s="2" t="s">
         <v>94</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="38" customHeight="1" ht="18.75">
+    <row r="38" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A38" s="1" t="s">
         <v>95</v>
       </c>
-      <c r="B38" s="4"/>
       <c r="C38" s="1" t="s">
         <v>49</v>
       </c>
@@ -1402,13 +1526,11 @@
       <c r="E38" s="1" t="s">
         <v>88</v>
       </c>
-      <c r="F38" s="4"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="39" customHeight="1" ht="18.75">
-      <c r="A39" s="5" t="s">
+    </row>
+    <row r="39" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A39" s="1" t="s">
         <v>96</v>
       </c>
-      <c r="B39" s="4"/>
       <c r="C39" s="1" t="s">
         <v>41</v>
       </c>
@@ -1418,13 +1540,11 @@
       <c r="E39" s="1" t="s">
         <v>88</v>
       </c>
-      <c r="F39" s="4"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="40" customHeight="1" ht="18.75">
+    </row>
+    <row r="40" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A40" s="1" t="s">
         <v>97</v>
       </c>
-      <c r="B40" s="4"/>
       <c r="C40" s="1" t="s">
         <v>41</v>
       </c>
@@ -1434,13 +1554,11 @@
       <c r="E40" s="1" t="s">
         <v>88</v>
       </c>
-      <c r="F40" s="4"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="41" customHeight="1" ht="18.75">
+    </row>
+    <row r="41" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A41" s="1" t="s">
         <v>98</v>
       </c>
-      <c r="B41" s="4"/>
       <c r="C41" s="1" t="s">
         <v>41</v>
       </c>
@@ -1450,15 +1568,14 @@
       <c r="E41" s="1" t="s">
         <v>88</v>
       </c>
-      <c r="F41" s="4" t="s">
+      <c r="F41" s="2" t="s">
         <v>99</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="42" customHeight="1" ht="18.75">
+    <row r="42" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A42" s="1" t="s">
         <v>100</v>
       </c>
-      <c r="B42" s="4"/>
       <c r="C42" s="1" t="s">
         <v>41</v>
       </c>
@@ -1468,31 +1585,28 @@
       <c r="E42" s="1" t="s">
         <v>88</v>
       </c>
-      <c r="F42" s="4"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="43" customHeight="1" ht="18.75">
+    </row>
+    <row r="43" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A43" s="1" t="s">
         <v>101</v>
       </c>
-      <c r="B43" s="4"/>
       <c r="C43" s="1" t="s">
         <v>102</v>
       </c>
       <c r="D43" s="1" t="s">
-        <v>12</v>
+        <v>146</v>
       </c>
       <c r="E43" s="1" t="s">
         <v>88</v>
       </c>
-      <c r="F43" s="4" t="s">
+      <c r="F43" s="2" t="s">
         <v>103</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="44" customHeight="1" ht="18.75">
+    <row r="44" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A44" s="1" t="s">
         <v>101</v>
       </c>
-      <c r="B44" s="4"/>
       <c r="C44" s="1" t="s">
         <v>104</v>
       </c>
@@ -1502,15 +1616,14 @@
       <c r="E44" s="1" t="s">
         <v>88</v>
       </c>
-      <c r="F44" s="4" t="s">
+      <c r="F44" s="2" t="s">
         <v>103</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="45" customHeight="1" ht="18.75">
-      <c r="A45" s="4" t="s">
+    <row r="45" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A45" s="2" t="s">
         <v>105</v>
       </c>
-      <c r="B45" s="4"/>
       <c r="C45" s="1" t="s">
         <v>69</v>
       </c>
@@ -1520,9 +1633,377 @@
       <c r="E45" s="1" t="s">
         <v>88</v>
       </c>
-      <c r="F45" s="4"/>
+    </row>
+    <row r="46" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A46" s="1" t="s">
+        <v>106</v>
+      </c>
+      <c r="C46" s="1" t="s">
+        <v>69</v>
+      </c>
+      <c r="D46" s="1" t="s">
+        <v>107</v>
+      </c>
+      <c r="G46" s="5" t="s">
+        <v>109</v>
+      </c>
+      <c r="H46" s="5"/>
+    </row>
+    <row r="47" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A47" s="1" t="s">
+        <v>111</v>
+      </c>
+      <c r="C47" s="1" t="s">
+        <v>69</v>
+      </c>
+      <c r="D47" s="1" t="s">
+        <v>107</v>
+      </c>
+      <c r="G47" s="2" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="48" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A48" s="1" t="s">
+        <v>112</v>
+      </c>
+      <c r="C48" s="1" t="s">
+        <v>69</v>
+      </c>
+      <c r="D48" s="1" t="s">
+        <v>107</v>
+      </c>
+      <c r="G48" s="2" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="49" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A49" s="1" t="s">
+        <v>115</v>
+      </c>
+      <c r="C49" s="1" t="s">
+        <v>69</v>
+      </c>
+      <c r="D49" s="1" t="s">
+        <v>145</v>
+      </c>
+      <c r="G49" s="2" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="50" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A50" s="1" t="s">
+        <v>118</v>
+      </c>
+      <c r="C50" s="1" t="s">
+        <v>69</v>
+      </c>
+      <c r="D50" s="1" t="s">
+        <v>117</v>
+      </c>
+      <c r="G50" s="5" t="s">
+        <v>116</v>
+      </c>
+      <c r="H50" s="5"/>
+    </row>
+    <row r="51" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A51" s="1" t="s">
+        <v>121</v>
+      </c>
+      <c r="C51" s="1" t="s">
+        <v>69</v>
+      </c>
+      <c r="D51" s="1" t="s">
+        <v>107</v>
+      </c>
+      <c r="G51" s="4" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="52" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A52" s="1" t="s">
+        <v>121</v>
+      </c>
+      <c r="C52" s="1" t="s">
+        <v>69</v>
+      </c>
+      <c r="D52" s="1" t="s">
+        <v>107</v>
+      </c>
+      <c r="G52" s="2" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="53" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A53" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="C53" s="1" t="s">
+        <v>69</v>
+      </c>
+      <c r="D53" s="1" t="s">
+        <v>107</v>
+      </c>
+      <c r="G53" s="4" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="54" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A54" s="2" t="s">
+        <v>123</v>
+      </c>
+      <c r="C54" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="D54" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="E54" s="2" t="s">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="55" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A55" s="2" t="s">
+        <v>125</v>
+      </c>
+      <c r="C55" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="D55" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="E55" s="2" t="s">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="56" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A56" s="2" t="s">
+        <v>126</v>
+      </c>
+      <c r="C56" s="2" t="s">
+        <v>127</v>
+      </c>
+      <c r="D56" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="E56" s="2" t="s">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="57" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A57" s="2" t="s">
+        <v>128</v>
+      </c>
+      <c r="C57" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="D57" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="E57" s="2" t="s">
+        <v>124</v>
+      </c>
+      <c r="F57" s="2" t="s">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="58" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A58" s="2" t="s">
+        <v>130</v>
+      </c>
+      <c r="C58" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="D58" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="E58" s="2" t="s">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="59" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A59" s="2" t="s">
+        <v>131</v>
+      </c>
+      <c r="C59" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="D59" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="E59" s="2" t="s">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="60" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A60" s="2" t="s">
+        <v>132</v>
+      </c>
+      <c r="C60" s="2" t="s">
+        <v>133</v>
+      </c>
+      <c r="D60" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="E60" s="2" t="s">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="61" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A61" s="2" t="s">
+        <v>134</v>
+      </c>
+      <c r="C61" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="D61" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="E61" s="2" t="s">
+        <v>124</v>
+      </c>
+      <c r="F61" s="2" t="s">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="62" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A62" s="2" t="s">
+        <v>132</v>
+      </c>
+      <c r="C62" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="D62" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="E62" s="2" t="s">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="63" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A63" s="2" t="s">
+        <v>98</v>
+      </c>
+      <c r="C63" s="2" t="s">
+        <v>67</v>
+      </c>
+      <c r="D63" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="E63" s="2" t="s">
+        <v>124</v>
+      </c>
+      <c r="F63" s="2" t="s">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="64" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A64" s="2" t="s">
+        <v>137</v>
+      </c>
+      <c r="C64" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="D64" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="E64" s="2" t="s">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="65" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A65" s="2" t="s">
+        <v>138</v>
+      </c>
+      <c r="C65" s="2" t="s">
+        <v>86</v>
+      </c>
+      <c r="D65" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="E65" s="2" t="s">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="66" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A66" s="2" t="s">
+        <v>139</v>
+      </c>
+      <c r="C66" s="2" t="s">
+        <v>140</v>
+      </c>
+      <c r="D66" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="E66" s="2" t="s">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="67" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A67" s="2" t="s">
+        <v>123</v>
+      </c>
+      <c r="C67" s="2" t="s">
+        <v>141</v>
+      </c>
+      <c r="D67" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="E67" s="2" t="s">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="68" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A68" s="2" t="s">
+        <v>142</v>
+      </c>
+      <c r="C68" s="2" t="s">
+        <v>143</v>
+      </c>
+      <c r="D68" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="E68" s="2" t="s">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="69" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A69" s="2" t="s">
+        <v>144</v>
+      </c>
+      <c r="C69" s="2" t="s">
+        <v>86</v>
+      </c>
+      <c r="D69" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="E69" s="2" t="s">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="70" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A70" s="2" t="s">
+        <v>131</v>
+      </c>
+      <c r="C70" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="D70" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="E70" s="2" t="s">
+        <v>124</v>
+      </c>
     </row>
   </sheetData>
+  <mergeCells count="2">
+    <mergeCell ref="G46:H46"/>
+    <mergeCell ref="G50:H50"/>
+  </mergeCells>
+  <hyperlinks>
+    <hyperlink ref="G51" r:id="rId1" display="mailto:angeliqu.misa@vxi.com" xr:uid="{F8822347-4DA6-4E1C-A199-2A7D94621AA7}"/>
+    <hyperlink ref="G53" r:id="rId2" display="mailto:daniella.mae.m.bisda@accenture.com" xr:uid="{5736F313-6CD2-4F50-B11A-CAF420139990}"/>
+  </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
--- a/documents/job-applications.xlsx
+++ b/documents/job-applications.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\LARRY\Documents\Scripts\auto-job-app-sender\documents\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{42DD6FC9-2256-4FD2-92DC-8F3C27ADA0AF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5298E0FF-F1C8-4679-8606-7039C2661216}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="322" uniqueCount="147">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="326" uniqueCount="149">
   <si>
     <t>company</t>
   </si>
@@ -461,6 +461,12 @@
   </si>
   <si>
     <t>Rejected but keep in touch for possible internship</t>
+  </si>
+  <si>
+    <t>Philippine Digital Assets Exchange</t>
+  </si>
+  <si>
+    <t>Senior Python Software Engineer</t>
   </si>
 </sst>
 </file>
@@ -843,7 +849,7 @@
   <sheetPr>
     <outlinePr summaryBelow="0"/>
   </sheetPr>
-  <dimension ref="A1:H70"/>
+  <dimension ref="A1:H71"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="45.109375" style="2" bestFit="1" customWidth="1"/>
@@ -1995,6 +2001,20 @@
         <v>124</v>
       </c>
     </row>
+    <row r="71" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A71" s="2" t="s">
+        <v>147</v>
+      </c>
+      <c r="C71" s="2" t="s">
+        <v>148</v>
+      </c>
+      <c r="D71" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="E71" s="2" t="s">
+        <v>124</v>
+      </c>
+    </row>
   </sheetData>
   <mergeCells count="2">
     <mergeCell ref="G46:H46"/>

--- a/documents/job-applications.xlsx
+++ b/documents/job-applications.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\LARRY\Documents\Scripts\auto-job-app-sender\documents\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5298E0FF-F1C8-4679-8606-7039C2661216}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{50E53D26-0E89-4BED-9F32-CBA4A2CF0514}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="326" uniqueCount="149">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="470" uniqueCount="206">
   <si>
     <t>company</t>
   </si>
@@ -346,9 +346,6 @@
     <t>Inquired</t>
   </si>
   <si>
-    <t>recruiter</t>
-  </si>
-  <si>
     <t>catherine_alhambra@pal.com.ph</t>
   </si>
   <si>
@@ -467,13 +464,187 @@
   </si>
   <si>
     <t>Senior Python Software Engineer</t>
+  </si>
+  <si>
+    <t>Foundever</t>
+  </si>
+  <si>
+    <t>enrisalara29@yahoo.com</t>
+  </si>
+  <si>
+    <t>DOXA Talent</t>
+  </si>
+  <si>
+    <t>angelohernandez25@gmail.com</t>
+  </si>
+  <si>
+    <t>anxious1491@gmail.com</t>
+  </si>
+  <si>
+    <t>Tata Consultancy Services</t>
+  </si>
+  <si>
+    <t>Software Engineer II</t>
+  </si>
+  <si>
+    <t>https://zendesk.wd1.myworkdayjobs.com/en-US/zendesk</t>
+  </si>
+  <si>
+    <t>vcvisda@unionbankph.com</t>
+  </si>
+  <si>
+    <t>Unionbank</t>
+  </si>
+  <si>
+    <t>mhelbert.paredes17@gmail.com</t>
+  </si>
+  <si>
+    <t>Everise</t>
+  </si>
+  <si>
+    <t>PSG Global Solutions</t>
+  </si>
+  <si>
+    <t>maricvid@amazon.com</t>
+  </si>
+  <si>
+    <t>ryan.rivera@telusinternational.com</t>
+  </si>
+  <si>
+    <t>Telus International Philippines</t>
+  </si>
+  <si>
+    <t>060290remfelguillenabelandres@gmail.com</t>
+  </si>
+  <si>
+    <t>Peoples Credit Network Finance Co. Inc.</t>
+  </si>
+  <si>
+    <t>cindydleon09@gmail.com</t>
+  </si>
+  <si>
+    <t>OC Ledgr</t>
+  </si>
+  <si>
+    <t>aprilchristine024@gmail.com</t>
+  </si>
+  <si>
+    <t>lyanatorrecampo@gmail.com</t>
+  </si>
+  <si>
+    <t>Stratpoint Technologies</t>
+  </si>
+  <si>
+    <t>AboitizPower</t>
+  </si>
+  <si>
+    <t>Yondu, Inc.</t>
+  </si>
+  <si>
+    <t>ljayme@yondu.com</t>
+  </si>
+  <si>
+    <t>miiraaa14@gmail.com</t>
+  </si>
+  <si>
+    <t>recruiter_email</t>
+  </si>
+  <si>
+    <t>recruiter_no</t>
+  </si>
+  <si>
+    <t>CTBC Bank Philippines</t>
+  </si>
+  <si>
+    <t>floriedelsanchez@gmail.com</t>
+  </si>
+  <si>
+    <t>iamchristinelopez@yahoo.com</t>
+  </si>
+  <si>
+    <t>TechTaxi, Inc.</t>
+  </si>
+  <si>
+    <t>donnatamayodlt@gmail.com</t>
+  </si>
+  <si>
+    <t>PwC Acceleration Center Manila</t>
+  </si>
+  <si>
+    <t>fatima.allona.bolano@pwc.com</t>
+  </si>
+  <si>
+    <t>jannachristina.liwanag@emerson.com</t>
+  </si>
+  <si>
+    <t>antuazon@hrnetworkph.com</t>
+  </si>
+  <si>
+    <t>HR Network Inc</t>
+  </si>
+  <si>
+    <t>Seven Seven</t>
+  </si>
+  <si>
+    <t>kqxmc2mcmr@privaterelay.appleid.com</t>
+  </si>
+  <si>
+    <t>Oracle</t>
+  </si>
+  <si>
+    <t>sheanasunga@gmail.com</t>
+  </si>
+  <si>
+    <t>gabatajohnmartin@gmail.com</t>
+  </si>
+  <si>
+    <t>Cognizant</t>
+  </si>
+  <si>
+    <t>ncorpuz@enshored.com</t>
+  </si>
+  <si>
+    <t>Enshore</t>
+  </si>
+  <si>
+    <t>krystel.dimalibot@gmail.com</t>
+  </si>
+  <si>
+    <t>emerson</t>
+  </si>
+  <si>
+    <t>alessandrian04@gmail.com</t>
+  </si>
+  <si>
+    <t>Find Human Resources Inc.</t>
+  </si>
+  <si>
+    <t>jgrojas1208@gmail.com</t>
+  </si>
+  <si>
+    <t>Infosys BPM</t>
+  </si>
+  <si>
+    <t>adrianejomeldupo.s@infosys.com</t>
+  </si>
+  <si>
+    <t>Arc.dev</t>
+  </si>
+  <si>
+    <t>KMC</t>
+  </si>
+  <si>
+    <t>Business Intelligence Dev</t>
+  </si>
+  <si>
+    <t>Senior Full Stack Software Engineer</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="3" x14ac:knownFonts="1">
+  <fonts count="6" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -494,6 +665,25 @@
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="8"/>
+      <color theme="1"/>
+      <name val="Segoe UI"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="8"/>
+      <color rgb="FF0A66C2"/>
+      <name val="Segoe UI"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="8"/>
+      <color rgb="FF0A66C2"/>
+      <name val="Segoe UI"/>
+      <family val="2"/>
     </font>
   </fonts>
   <fills count="3">
@@ -530,7 +720,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
@@ -540,9 +730,16 @@
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
@@ -849,7 +1046,7 @@
   <sheetPr>
     <outlinePr summaryBelow="0"/>
   </sheetPr>
-  <dimension ref="A1:H71"/>
+  <dimension ref="A1:H107"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="45.109375" style="2" bestFit="1" customWidth="1"/>
@@ -859,10 +1056,11 @@
     <col min="5" max="5" width="13.5546875" style="2" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="53.109375" style="2" customWidth="1"/>
     <col min="7" max="7" width="22.6640625" style="2" customWidth="1"/>
-    <col min="8" max="16384" width="8.88671875" style="2"/>
+    <col min="8" max="8" width="23.44140625" style="2" customWidth="1"/>
+    <col min="9" max="16384" width="8.88671875" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:8" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -882,10 +1080,13 @@
         <v>5</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>108</v>
-      </c>
-    </row>
-    <row r="2" spans="1:7" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
+        <v>175</v>
+      </c>
+      <c r="H1" s="2" t="s">
+        <v>176</v>
+      </c>
+    </row>
+    <row r="2" spans="1:8" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="1" t="s">
         <v>6</v>
       </c>
@@ -903,7 +1104,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="3" spans="1:7" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:8" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3" s="1" t="s">
         <v>6</v>
       </c>
@@ -921,7 +1122,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="4" spans="1:7" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:8" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A4" s="1" t="s">
         <v>13</v>
       </c>
@@ -937,7 +1138,7 @@
       </c>
       <c r="F4" s="1"/>
     </row>
-    <row r="5" spans="1:7" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:8" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A5" s="1" t="s">
         <v>15</v>
       </c>
@@ -955,7 +1156,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="6" spans="1:7" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:8" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A6" s="1" t="s">
         <v>17</v>
       </c>
@@ -971,7 +1172,7 @@
       </c>
       <c r="F6" s="1"/>
     </row>
-    <row r="7" spans="1:7" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:8" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A7" s="1" t="s">
         <v>17</v>
       </c>
@@ -987,7 +1188,7 @@
       </c>
       <c r="F7" s="1"/>
     </row>
-    <row r="8" spans="1:7" ht="33" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:8" ht="33" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A8" s="1" t="s">
         <v>20</v>
       </c>
@@ -1005,7 +1206,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="9" spans="1:7" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:8" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A9" s="1" t="s">
         <v>20</v>
       </c>
@@ -1023,7 +1224,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="10" spans="1:7" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:8" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A10" s="1" t="s">
         <v>24</v>
       </c>
@@ -1041,7 +1242,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="11" spans="1:7" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:8" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A11" s="1" t="s">
         <v>28</v>
       </c>
@@ -1059,7 +1260,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="12" spans="1:7" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:8" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A12" s="1" t="s">
         <v>31</v>
       </c>
@@ -1077,7 +1278,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="13" spans="1:7" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:8" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A13" s="1" t="s">
         <v>34</v>
       </c>
@@ -1095,7 +1296,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="14" spans="1:7" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:8" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A14" s="1" t="s">
         <v>37</v>
       </c>
@@ -1113,7 +1314,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="15" spans="1:7" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:8" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A15" s="1" t="s">
         <v>37</v>
       </c>
@@ -1131,7 +1332,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="16" spans="1:7" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:8" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A16" s="1" t="s">
         <v>42</v>
       </c>
@@ -1600,7 +1801,7 @@
         <v>102</v>
       </c>
       <c r="D43" s="1" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="E43" s="1" t="s">
         <v>88</v>
@@ -1650,14 +1851,14 @@
       <c r="D46" s="1" t="s">
         <v>107</v>
       </c>
-      <c r="G46" s="5" t="s">
-        <v>109</v>
-      </c>
-      <c r="H46" s="5"/>
+      <c r="G46" s="9" t="s">
+        <v>108</v>
+      </c>
+      <c r="H46" s="9"/>
     </row>
     <row r="47" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A47" s="1" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="C47" s="1" t="s">
         <v>69</v>
@@ -1666,55 +1867,55 @@
         <v>107</v>
       </c>
       <c r="G47" s="2" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
     </row>
     <row r="48" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A48" s="1" t="s">
+        <v>111</v>
+      </c>
+      <c r="C48" s="1" t="s">
+        <v>69</v>
+      </c>
+      <c r="D48" s="1" t="s">
+        <v>107</v>
+      </c>
+      <c r="G48" s="2" t="s">
         <v>112</v>
-      </c>
-      <c r="C48" s="1" t="s">
-        <v>69</v>
-      </c>
-      <c r="D48" s="1" t="s">
-        <v>107</v>
-      </c>
-      <c r="G48" s="2" t="s">
-        <v>113</v>
       </c>
     </row>
     <row r="49" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A49" s="1" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="C49" s="1" t="s">
         <v>69</v>
       </c>
       <c r="D49" s="1" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="G49" s="2" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
     </row>
     <row r="50" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A50" s="1" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="C50" s="1" t="s">
         <v>69</v>
       </c>
       <c r="D50" s="1" t="s">
-        <v>117</v>
-      </c>
-      <c r="G50" s="5" t="s">
         <v>116</v>
       </c>
-      <c r="H50" s="5"/>
+      <c r="G50" s="9" t="s">
+        <v>115</v>
+      </c>
+      <c r="H50" s="9"/>
     </row>
     <row r="51" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A51" s="1" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="C51" s="1" t="s">
         <v>69</v>
@@ -1723,12 +1924,12 @@
         <v>107</v>
       </c>
       <c r="G51" s="4" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
     </row>
     <row r="52" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A52" s="1" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="C52" s="1" t="s">
         <v>69</v>
@@ -1737,7 +1938,7 @@
         <v>107</v>
       </c>
       <c r="G52" s="2" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
     </row>
     <row r="53" spans="1:8" x14ac:dyDescent="0.3">
@@ -1751,26 +1952,26 @@
         <v>107</v>
       </c>
       <c r="G53" s="4" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
     </row>
     <row r="54" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A54" s="2" t="s">
+        <v>122</v>
+      </c>
+      <c r="C54" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="D54" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="E54" s="2" t="s">
         <v>123</v>
-      </c>
-      <c r="C54" s="2" t="s">
-        <v>69</v>
-      </c>
-      <c r="D54" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="E54" s="2" t="s">
-        <v>124</v>
       </c>
     </row>
     <row r="55" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A55" s="2" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="C55" s="2" t="s">
         <v>69</v>
@@ -1779,43 +1980,43 @@
         <v>12</v>
       </c>
       <c r="E55" s="2" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
     </row>
     <row r="56" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A56" s="2" t="s">
+        <v>125</v>
+      </c>
+      <c r="C56" s="2" t="s">
         <v>126</v>
       </c>
-      <c r="C56" s="2" t="s">
-        <v>127</v>
-      </c>
       <c r="D56" s="2" t="s">
         <v>12</v>
       </c>
       <c r="E56" s="2" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
     </row>
     <row r="57" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A57" s="2" t="s">
+        <v>127</v>
+      </c>
+      <c r="C57" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="D57" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="E57" s="2" t="s">
+        <v>123</v>
+      </c>
+      <c r="F57" s="2" t="s">
         <v>128</v>
-      </c>
-      <c r="C57" s="2" t="s">
-        <v>69</v>
-      </c>
-      <c r="D57" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="E57" s="2" t="s">
-        <v>124</v>
-      </c>
-      <c r="F57" s="2" t="s">
-        <v>129</v>
       </c>
     </row>
     <row r="58" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A58" s="2" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="C58" s="2" t="s">
         <v>69</v>
@@ -1824,12 +2025,12 @@
         <v>12</v>
       </c>
       <c r="E58" s="2" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
     </row>
     <row r="59" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A59" s="2" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="C59" s="2" t="s">
         <v>46</v>
@@ -1838,26 +2039,26 @@
         <v>12</v>
       </c>
       <c r="E59" s="2" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
     </row>
     <row r="60" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A60" s="2" t="s">
+        <v>131</v>
+      </c>
+      <c r="C60" s="2" t="s">
         <v>132</v>
       </c>
-      <c r="C60" s="2" t="s">
-        <v>133</v>
-      </c>
       <c r="D60" s="2" t="s">
         <v>12</v>
       </c>
       <c r="E60" s="2" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
     </row>
     <row r="61" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A61" s="2" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="C61" s="2" t="s">
         <v>43</v>
@@ -1866,15 +2067,15 @@
         <v>12</v>
       </c>
       <c r="E61" s="2" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="F61" s="2" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
     </row>
     <row r="62" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A62" s="2" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="C62" s="2" t="s">
         <v>43</v>
@@ -1883,7 +2084,7 @@
         <v>12</v>
       </c>
       <c r="E62" s="2" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
     </row>
     <row r="63" spans="1:8" x14ac:dyDescent="0.3">
@@ -1897,15 +2098,15 @@
         <v>12</v>
       </c>
       <c r="E63" s="2" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="F63" s="2" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
     </row>
     <row r="64" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A64" s="2" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="C64" s="2" t="s">
         <v>43</v>
@@ -1914,12 +2115,12 @@
         <v>12</v>
       </c>
       <c r="E64" s="2" t="s">
-        <v>124</v>
-      </c>
-    </row>
-    <row r="65" spans="1:5" x14ac:dyDescent="0.3">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="65" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A65" s="2" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="C65" s="2" t="s">
         <v>86</v>
@@ -1928,54 +2129,54 @@
         <v>12</v>
       </c>
       <c r="E65" s="2" t="s">
-        <v>124</v>
-      </c>
-    </row>
-    <row r="66" spans="1:5" x14ac:dyDescent="0.3">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="66" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A66" s="2" t="s">
+        <v>138</v>
+      </c>
+      <c r="C66" s="2" t="s">
         <v>139</v>
       </c>
-      <c r="C66" s="2" t="s">
+      <c r="D66" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="E66" s="2" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="67" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A67" s="2" t="s">
+        <v>122</v>
+      </c>
+      <c r="C67" s="2" t="s">
         <v>140</v>
       </c>
-      <c r="D66" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="E66" s="2" t="s">
-        <v>124</v>
-      </c>
-    </row>
-    <row r="67" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A67" s="2" t="s">
+      <c r="D67" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="E67" s="2" t="s">
         <v>123</v>
       </c>
-      <c r="C67" s="2" t="s">
+    </row>
+    <row r="68" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A68" s="2" t="s">
         <v>141</v>
       </c>
-      <c r="D67" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="E67" s="2" t="s">
-        <v>124</v>
-      </c>
-    </row>
-    <row r="68" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A68" s="2" t="s">
+      <c r="C68" s="2" t="s">
         <v>142</v>
       </c>
-      <c r="C68" s="2" t="s">
+      <c r="D68" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="E68" s="2" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="69" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A69" s="2" t="s">
         <v>143</v>
-      </c>
-      <c r="D68" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="E68" s="2" t="s">
-        <v>124</v>
-      </c>
-    </row>
-    <row r="69" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A69" s="2" t="s">
-        <v>144</v>
       </c>
       <c r="C69" s="2" t="s">
         <v>86</v>
@@ -1984,12 +2185,12 @@
         <v>12</v>
       </c>
       <c r="E69" s="2" t="s">
-        <v>124</v>
-      </c>
-    </row>
-    <row r="70" spans="1:5" x14ac:dyDescent="0.3">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="70" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A70" s="2" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="C70" s="2" t="s">
         <v>41</v>
@@ -1998,21 +2199,534 @@
         <v>12</v>
       </c>
       <c r="E70" s="2" t="s">
-        <v>124</v>
-      </c>
-    </row>
-    <row r="71" spans="1:5" x14ac:dyDescent="0.3">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="71" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A71" s="2" t="s">
+        <v>146</v>
+      </c>
+      <c r="C71" s="2" t="s">
         <v>147</v>
       </c>
-      <c r="C71" s="2" t="s">
+      <c r="D71" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="E71" s="2" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="72" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A72" s="2" t="s">
         <v>148</v>
       </c>
-      <c r="D71" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="E71" s="2" t="s">
-        <v>124</v>
+      <c r="C72" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="D72" s="2" t="s">
+        <v>107</v>
+      </c>
+      <c r="G72" s="2" t="s">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="73" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A73" s="2" t="s">
+        <v>150</v>
+      </c>
+      <c r="C73" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="D73" s="2" t="s">
+        <v>107</v>
+      </c>
+      <c r="G73" s="2" t="s">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="74" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A74" s="2" t="s">
+        <v>153</v>
+      </c>
+      <c r="C74" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="D74" s="2" t="s">
+        <v>107</v>
+      </c>
+      <c r="G74" s="2" t="s">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="75" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A75" s="2" t="s">
+        <v>111</v>
+      </c>
+      <c r="C75" s="2" t="s">
+        <v>154</v>
+      </c>
+      <c r="D75" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="F75" s="5" t="s">
+        <v>155</v>
+      </c>
+      <c r="G75" s="2" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="76" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A76" s="2" t="s">
+        <v>157</v>
+      </c>
+      <c r="C76" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="D76" s="2" t="s">
+        <v>107</v>
+      </c>
+      <c r="G76" s="5" t="s">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="77" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A77" s="2" t="s">
+        <v>159</v>
+      </c>
+      <c r="C77" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="D77" s="2" t="s">
+        <v>107</v>
+      </c>
+      <c r="G77" s="7" t="s">
+        <v>158</v>
+      </c>
+    </row>
+    <row r="78" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A78" s="2" t="s">
+        <v>160</v>
+      </c>
+      <c r="C78" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="D78" s="2" t="s">
+        <v>107</v>
+      </c>
+      <c r="G78" s="5" t="s">
+        <v>161</v>
+      </c>
+    </row>
+    <row r="79" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A79" s="2" t="s">
+        <v>163</v>
+      </c>
+      <c r="C79" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="D79" s="2" t="s">
+        <v>107</v>
+      </c>
+      <c r="G79" s="5" t="s">
+        <v>162</v>
+      </c>
+    </row>
+    <row r="80" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A80" s="6" t="s">
+        <v>165</v>
+      </c>
+      <c r="C80" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="D80" s="2" t="s">
+        <v>107</v>
+      </c>
+      <c r="G80" s="5" t="s">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="81" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A81" s="2" t="s">
+        <v>167</v>
+      </c>
+      <c r="C81" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="D81" s="2" t="s">
+        <v>107</v>
+      </c>
+      <c r="G81" s="8" t="s">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="82" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A82" s="2" t="s">
+        <v>138</v>
+      </c>
+      <c r="C82" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="D82" s="2" t="s">
+        <v>107</v>
+      </c>
+      <c r="G82" s="5" t="s">
+        <v>168</v>
+      </c>
+    </row>
+    <row r="83" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A83" s="2" t="s">
+        <v>159</v>
+      </c>
+      <c r="C83" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="D83" s="2" t="s">
+        <v>107</v>
+      </c>
+      <c r="G83" s="5" t="s">
+        <v>169</v>
+      </c>
+    </row>
+    <row r="84" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A84" s="2" t="s">
+        <v>170</v>
+      </c>
+      <c r="C84" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="D84" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="E84" s="2" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="85" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A85" s="2" t="s">
+        <v>171</v>
+      </c>
+      <c r="C85" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="D85" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="E85" s="2" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="86" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A86" s="2" t="s">
+        <v>129</v>
+      </c>
+      <c r="C86" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="D86" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="E86" s="2" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="87" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A87" s="2" t="s">
+        <v>122</v>
+      </c>
+      <c r="C87" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="D87" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="E87" s="2" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="88" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A88" s="2" t="s">
+        <v>172</v>
+      </c>
+      <c r="C88" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="D88" s="2" t="s">
+        <v>107</v>
+      </c>
+      <c r="G88" s="5" t="s">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="89" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A89" s="2" t="s">
+        <v>177</v>
+      </c>
+      <c r="C89" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="D89" s="2" t="s">
+        <v>107</v>
+      </c>
+      <c r="G89" s="5" t="s">
+        <v>174</v>
+      </c>
+      <c r="H89" s="6">
+        <v>9394791981</v>
+      </c>
+    </row>
+    <row r="90" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A90" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="C90" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="D90" s="2" t="s">
+        <v>107</v>
+      </c>
+      <c r="G90" s="5" t="s">
+        <v>178</v>
+      </c>
+    </row>
+    <row r="91" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A91" s="2" t="s">
+        <v>143</v>
+      </c>
+      <c r="C91" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="D91" s="2" t="s">
+        <v>107</v>
+      </c>
+      <c r="G91" s="5" t="s">
+        <v>179</v>
+      </c>
+      <c r="H91" s="6">
+        <v>9270345867</v>
+      </c>
+    </row>
+    <row r="92" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A92" s="2" t="s">
+        <v>180</v>
+      </c>
+      <c r="C92" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="D92" s="2" t="s">
+        <v>107</v>
+      </c>
+      <c r="G92" s="5" t="s">
+        <v>181</v>
+      </c>
+      <c r="H92" s="6">
+        <v>639923742220</v>
+      </c>
+    </row>
+    <row r="93" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A93" s="2" t="s">
+        <v>182</v>
+      </c>
+      <c r="C93" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="D93" s="2" t="s">
+        <v>107</v>
+      </c>
+      <c r="G93" s="10" t="s">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="94" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A94" s="2" t="s">
+        <v>131</v>
+      </c>
+      <c r="C94" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="D94" s="2" t="s">
+        <v>107</v>
+      </c>
+      <c r="G94" s="5" t="s">
+        <v>184</v>
+      </c>
+    </row>
+    <row r="95" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A95" s="2" t="s">
+        <v>186</v>
+      </c>
+      <c r="C95" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="D95" s="2" t="s">
+        <v>107</v>
+      </c>
+      <c r="G95" s="5" t="s">
+        <v>185</v>
+      </c>
+    </row>
+    <row r="96" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A96" s="2" t="s">
+        <v>187</v>
+      </c>
+      <c r="C96" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="D96" s="2" t="s">
+        <v>107</v>
+      </c>
+      <c r="G96" s="5" t="s">
+        <v>188</v>
+      </c>
+    </row>
+    <row r="97" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A97" s="2" t="s">
+        <v>189</v>
+      </c>
+      <c r="C97" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="D97" s="2" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="98" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A98" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="C98" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="D98" s="2" t="s">
+        <v>107</v>
+      </c>
+      <c r="G98" s="5" t="s">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="99" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A99" s="2" t="s">
+        <v>192</v>
+      </c>
+      <c r="C99" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="D99" s="2" t="s">
+        <v>107</v>
+      </c>
+      <c r="G99" s="5" t="s">
+        <v>191</v>
+      </c>
+    </row>
+    <row r="100" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A100" s="2" t="s">
+        <v>194</v>
+      </c>
+      <c r="C100" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="D100" s="2" t="s">
+        <v>107</v>
+      </c>
+      <c r="G100" s="5" t="s">
+        <v>193</v>
+      </c>
+      <c r="H100" s="6">
+        <v>9695979091</v>
+      </c>
+    </row>
+    <row r="101" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A101" s="2" t="s">
+        <v>196</v>
+      </c>
+      <c r="C101" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="D101" s="2" t="s">
+        <v>107</v>
+      </c>
+      <c r="G101" s="5" t="s">
+        <v>195</v>
+      </c>
+    </row>
+    <row r="102" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A102" s="2" t="s">
+        <v>198</v>
+      </c>
+      <c r="C102" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="D102" s="2" t="s">
+        <v>107</v>
+      </c>
+      <c r="G102" s="5" t="s">
+        <v>197</v>
+      </c>
+    </row>
+    <row r="103" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A103" s="2" t="s">
+        <v>192</v>
+      </c>
+      <c r="C103" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="D103" s="2" t="s">
+        <v>107</v>
+      </c>
+      <c r="G103" s="5" t="s">
+        <v>199</v>
+      </c>
+    </row>
+    <row r="104" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A104" s="2" t="s">
+        <v>200</v>
+      </c>
+      <c r="C104" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="D104" s="2" t="s">
+        <v>107</v>
+      </c>
+      <c r="G104" s="5" t="s">
+        <v>201</v>
+      </c>
+    </row>
+    <row r="105" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A105" s="2" t="s">
+        <v>202</v>
+      </c>
+      <c r="C105" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="D105" s="2" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="106" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A106" s="2" t="s">
+        <v>203</v>
+      </c>
+      <c r="C106" s="2" t="s">
+        <v>204</v>
+      </c>
+      <c r="D106" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="E106" s="2" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="107" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A107" s="2" t="s">
+        <v>98</v>
+      </c>
+      <c r="C107" s="2" t="s">
+        <v>205</v>
+      </c>
+      <c r="D107" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="E107" s="2" t="s">
+        <v>123</v>
       </c>
     </row>
   </sheetData>
@@ -2023,6 +2737,29 @@
   <hyperlinks>
     <hyperlink ref="G51" r:id="rId1" display="mailto:angeliqu.misa@vxi.com" xr:uid="{F8822347-4DA6-4E1C-A199-2A7D94621AA7}"/>
     <hyperlink ref="G53" r:id="rId2" display="mailto:daniella.mae.m.bisda@accenture.com" xr:uid="{5736F313-6CD2-4F50-B11A-CAF420139990}"/>
+    <hyperlink ref="F75" r:id="rId3" xr:uid="{1F35D3D0-D2E4-44F7-A294-1D932740061B}"/>
+    <hyperlink ref="G76" r:id="rId4" display="mailto:vcvisda@unionbankph.com" xr:uid="{2B50802A-78DE-45BD-8487-7B04C5C69BCC}"/>
+    <hyperlink ref="G77" r:id="rId5" display="mailto:mhelbert.paredes17@gmail.com" xr:uid="{3A70F298-6A85-485F-B784-E721910E61AD}"/>
+    <hyperlink ref="G78" r:id="rId6" display="mailto:maricvid@amazon.com" xr:uid="{B0781B8C-DB3D-4E3B-BDC9-1B4BFFA4F80F}"/>
+    <hyperlink ref="G79" r:id="rId7" display="mailto:ryan.rivera@telusinternational.com" xr:uid="{6FB8D0A7-3746-4063-ADC1-39039DC75449}"/>
+    <hyperlink ref="G80" r:id="rId8" display="mailto:060290remfelguillenabelandres@gmail.com" xr:uid="{A4145F4D-D6B4-4735-9CFD-6E9D7170DCB7}"/>
+    <hyperlink ref="G82" r:id="rId9" display="mailto:aprilchristine024@gmail.com" xr:uid="{16F6E4B8-B4D2-49BF-98EE-3D097721E81B}"/>
+    <hyperlink ref="G83" r:id="rId10" display="mailto:lyanatorrecampo@gmail.com" xr:uid="{D51965BF-4764-4516-B002-98A2E111999F}"/>
+    <hyperlink ref="G88" r:id="rId11" display="mailto:ljayme@yondu.com" xr:uid="{B8D84DF7-0660-4ABB-B6B3-EC4399E9E1B6}"/>
+    <hyperlink ref="G89" r:id="rId12" display="mailto:miiraaa14@gmail.com" xr:uid="{152360AF-DCC6-4B5C-A953-BE4BE0336D85}"/>
+    <hyperlink ref="G90" r:id="rId13" display="mailto:floriedelsanchez@gmail.com" xr:uid="{7637E896-0CD3-4EB0-98B2-5F6E6BAD95D2}"/>
+    <hyperlink ref="G91" r:id="rId14" display="mailto:iamchristinelopez@yahoo.com" xr:uid="{A09DB61A-7FA6-4FEB-ACA9-712996ABCA45}"/>
+    <hyperlink ref="G92" r:id="rId15" display="mailto:donnatamayodlt@gmail.com" xr:uid="{F1BDD7F7-18B2-4C58-83B3-8C625C90694E}"/>
+    <hyperlink ref="G94" r:id="rId16" display="mailto:jannachristina.liwanag@emerson.com" xr:uid="{3A73A12A-16C8-476F-AFEF-1361A084559A}"/>
+    <hyperlink ref="G95" r:id="rId17" display="mailto:antuazon@hrnetworkph.com" xr:uid="{53C7618E-6977-4B29-BF35-86BAFD22CF7E}"/>
+    <hyperlink ref="G96" r:id="rId18" display="mailto:kqxmc2mcmr@privaterelay.appleid.com" xr:uid="{BCCB1F5B-FA73-43B1-993A-97328E59A748}"/>
+    <hyperlink ref="G98" r:id="rId19" display="mailto:sheanasunga@gmail.com" xr:uid="{696C44F2-33F8-4D1C-85E3-B23516398A3A}"/>
+    <hyperlink ref="G99" r:id="rId20" display="mailto:gabatajohnmartin@gmail.com" xr:uid="{08544EF3-D7EB-402E-AF77-ED725C298C68}"/>
+    <hyperlink ref="G100" r:id="rId21" display="mailto:ncorpuz@enshored.com" xr:uid="{035A0D76-EEC3-4B02-AB1B-9FA0BFEC1ED1}"/>
+    <hyperlink ref="G101" r:id="rId22" display="mailto:krystel.dimalibot@gmail.com" xr:uid="{0536CED5-725F-4C6D-A39D-AD0A28E0182A}"/>
+    <hyperlink ref="G102" r:id="rId23" display="mailto:alessandrian04@gmail.com" xr:uid="{EF7858F4-4749-49F3-832D-C20C07D0160C}"/>
+    <hyperlink ref="G103" r:id="rId24" display="mailto:jgrojas1208@gmail.com" xr:uid="{127D1963-A796-4043-B835-D4E9B5C4BF9E}"/>
+    <hyperlink ref="G104" r:id="rId25" display="mailto:adrianejomeldupo.s@infosys.com" xr:uid="{55DD9FC8-5D3B-4C7F-8283-365B41814C2C}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/documents/job-applications.xlsx
+++ b/documents/job-applications.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="28324"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="28429"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\LARRY\Documents\Scripts\auto-job-app-sender\documents\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{50E53D26-0E89-4BED-9F32-CBA4A2CF0514}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{37F88845-EA65-45FA-9BAD-9943BC002FE0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="470" uniqueCount="206">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="510" uniqueCount="219">
   <si>
     <t>company</t>
   </si>
@@ -638,13 +638,52 @@
   </si>
   <si>
     <t>Senior Full Stack Software Engineer</t>
+  </si>
+  <si>
+    <t>PDAX</t>
+  </si>
+  <si>
+    <t>Senior Associate Software Engineer</t>
+  </si>
+  <si>
+    <t>Junior Python Software Engineer</t>
+  </si>
+  <si>
+    <t>Xurpa, Enterprise Inc.</t>
+  </si>
+  <si>
+    <t>Junior Python Develoepr</t>
+  </si>
+  <si>
+    <t>Lancesoft, Inc.</t>
+  </si>
+  <si>
+    <t>Collabera Digital</t>
+  </si>
+  <si>
+    <t>Risewave Consulting, Inc.</t>
+  </si>
+  <si>
+    <t>AI Software Engineer</t>
+  </si>
+  <si>
+    <t>Comrise</t>
+  </si>
+  <si>
+    <t>Phitopolis</t>
+  </si>
+  <si>
+    <t>Machine Learning Researcher/Engineer</t>
+  </si>
+  <si>
+    <t>ETL Developer</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="6" x14ac:knownFonts="1">
+  <fonts count="5" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -667,23 +706,19 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="8"/>
-      <color theme="1"/>
-      <name val="Segoe UI"/>
+      <sz val="11"/>
+      <color rgb="FF0A66C2"/>
+      <name val="Calibri"/>
       <family val="2"/>
-    </font>
-    <font>
-      <sz val="8"/>
-      <color rgb="FF0A66C2"/>
-      <name val="Segoe UI"/>
-      <family val="2"/>
+      <scheme val="minor"/>
     </font>
     <font>
       <u/>
-      <sz val="8"/>
+      <sz val="11"/>
       <color rgb="FF0A66C2"/>
-      <name val="Segoe UI"/>
+      <name val="Calibri"/>
       <family val="2"/>
+      <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="3">
@@ -730,16 +765,16 @@
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
@@ -1046,7 +1081,7 @@
   <sheetPr>
     <outlinePr summaryBelow="0"/>
   </sheetPr>
-  <dimension ref="A1:H107"/>
+  <dimension ref="A1:H117"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="45.109375" style="2" bestFit="1" customWidth="1"/>
@@ -1851,10 +1886,10 @@
       <c r="D46" s="1" t="s">
         <v>107</v>
       </c>
-      <c r="G46" s="9" t="s">
+      <c r="G46" s="5" t="s">
         <v>108</v>
       </c>
-      <c r="H46" s="9"/>
+      <c r="H46" s="5"/>
     </row>
     <row r="47" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A47" s="1" t="s">
@@ -1908,10 +1943,10 @@
       <c r="D50" s="1" t="s">
         <v>116</v>
       </c>
-      <c r="G50" s="9" t="s">
+      <c r="G50" s="5" t="s">
         <v>115</v>
       </c>
-      <c r="H50" s="9"/>
+      <c r="H50" s="5"/>
     </row>
     <row r="51" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A51" s="1" t="s">
@@ -2268,7 +2303,7 @@
       <c r="D75" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="F75" s="5" t="s">
+      <c r="F75" s="6" t="s">
         <v>155</v>
       </c>
       <c r="G75" s="2" t="s">
@@ -2285,7 +2320,7 @@
       <c r="D76" s="2" t="s">
         <v>107</v>
       </c>
-      <c r="G76" s="5" t="s">
+      <c r="G76" s="6" t="s">
         <v>156</v>
       </c>
     </row>
@@ -2313,7 +2348,7 @@
       <c r="D78" s="2" t="s">
         <v>107</v>
       </c>
-      <c r="G78" s="5" t="s">
+      <c r="G78" s="6" t="s">
         <v>161</v>
       </c>
     </row>
@@ -2327,12 +2362,12 @@
       <c r="D79" s="2" t="s">
         <v>107</v>
       </c>
-      <c r="G79" s="5" t="s">
+      <c r="G79" s="6" t="s">
         <v>162</v>
       </c>
     </row>
     <row r="80" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A80" s="6" t="s">
+      <c r="A80" s="8" t="s">
         <v>165</v>
       </c>
       <c r="C80" s="2" t="s">
@@ -2341,7 +2376,7 @@
       <c r="D80" s="2" t="s">
         <v>107</v>
       </c>
-      <c r="G80" s="5" t="s">
+      <c r="G80" s="6" t="s">
         <v>164</v>
       </c>
     </row>
@@ -2355,7 +2390,7 @@
       <c r="D81" s="2" t="s">
         <v>107</v>
       </c>
-      <c r="G81" s="8" t="s">
+      <c r="G81" s="9" t="s">
         <v>166</v>
       </c>
     </row>
@@ -2369,7 +2404,7 @@
       <c r="D82" s="2" t="s">
         <v>107</v>
       </c>
-      <c r="G82" s="5" t="s">
+      <c r="G82" s="6" t="s">
         <v>168</v>
       </c>
     </row>
@@ -2383,7 +2418,7 @@
       <c r="D83" s="2" t="s">
         <v>107</v>
       </c>
-      <c r="G83" s="5" t="s">
+      <c r="G83" s="6" t="s">
         <v>169</v>
       </c>
     </row>
@@ -2453,7 +2488,7 @@
       <c r="D88" s="2" t="s">
         <v>107</v>
       </c>
-      <c r="G88" s="5" t="s">
+      <c r="G88" s="6" t="s">
         <v>173</v>
       </c>
     </row>
@@ -2467,10 +2502,10 @@
       <c r="D89" s="2" t="s">
         <v>107</v>
       </c>
-      <c r="G89" s="5" t="s">
+      <c r="G89" s="6" t="s">
         <v>174</v>
       </c>
-      <c r="H89" s="6">
+      <c r="H89" s="8">
         <v>9394791981</v>
       </c>
     </row>
@@ -2484,7 +2519,7 @@
       <c r="D90" s="2" t="s">
         <v>107</v>
       </c>
-      <c r="G90" s="5" t="s">
+      <c r="G90" s="6" t="s">
         <v>178</v>
       </c>
     </row>
@@ -2498,10 +2533,10 @@
       <c r="D91" s="2" t="s">
         <v>107</v>
       </c>
-      <c r="G91" s="5" t="s">
+      <c r="G91" s="6" t="s">
         <v>179</v>
       </c>
-      <c r="H91" s="6">
+      <c r="H91" s="8">
         <v>9270345867</v>
       </c>
     </row>
@@ -2515,10 +2550,10 @@
       <c r="D92" s="2" t="s">
         <v>107</v>
       </c>
-      <c r="G92" s="5" t="s">
+      <c r="G92" s="6" t="s">
         <v>181</v>
       </c>
-      <c r="H92" s="6">
+      <c r="H92" s="8">
         <v>639923742220</v>
       </c>
     </row>
@@ -2546,7 +2581,7 @@
       <c r="D94" s="2" t="s">
         <v>107</v>
       </c>
-      <c r="G94" s="5" t="s">
+      <c r="G94" s="6" t="s">
         <v>184</v>
       </c>
     </row>
@@ -2560,7 +2595,7 @@
       <c r="D95" s="2" t="s">
         <v>107</v>
       </c>
-      <c r="G95" s="5" t="s">
+      <c r="G95" s="6" t="s">
         <v>185</v>
       </c>
     </row>
@@ -2574,7 +2609,7 @@
       <c r="D96" s="2" t="s">
         <v>107</v>
       </c>
-      <c r="G96" s="5" t="s">
+      <c r="G96" s="6" t="s">
         <v>188</v>
       </c>
     </row>
@@ -2599,7 +2634,7 @@
       <c r="D98" s="2" t="s">
         <v>107</v>
       </c>
-      <c r="G98" s="5" t="s">
+      <c r="G98" s="6" t="s">
         <v>190</v>
       </c>
     </row>
@@ -2613,7 +2648,7 @@
       <c r="D99" s="2" t="s">
         <v>107</v>
       </c>
-      <c r="G99" s="5" t="s">
+      <c r="G99" s="6" t="s">
         <v>191</v>
       </c>
     </row>
@@ -2627,10 +2662,10 @@
       <c r="D100" s="2" t="s">
         <v>107</v>
       </c>
-      <c r="G100" s="5" t="s">
+      <c r="G100" s="6" t="s">
         <v>193</v>
       </c>
-      <c r="H100" s="6">
+      <c r="H100" s="8">
         <v>9695979091</v>
       </c>
     </row>
@@ -2644,7 +2679,7 @@
       <c r="D101" s="2" t="s">
         <v>107</v>
       </c>
-      <c r="G101" s="5" t="s">
+      <c r="G101" s="6" t="s">
         <v>195</v>
       </c>
     </row>
@@ -2658,7 +2693,7 @@
       <c r="D102" s="2" t="s">
         <v>107</v>
       </c>
-      <c r="G102" s="5" t="s">
+      <c r="G102" s="6" t="s">
         <v>197</v>
       </c>
     </row>
@@ -2672,7 +2707,7 @@
       <c r="D103" s="2" t="s">
         <v>107</v>
       </c>
-      <c r="G103" s="5" t="s">
+      <c r="G103" s="6" t="s">
         <v>199</v>
       </c>
     </row>
@@ -2686,7 +2721,7 @@
       <c r="D104" s="2" t="s">
         <v>107</v>
       </c>
-      <c r="G104" s="5" t="s">
+      <c r="G104" s="6" t="s">
         <v>201</v>
       </c>
     </row>
@@ -2726,6 +2761,146 @@
         <v>12</v>
       </c>
       <c r="E107" s="2" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="108" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A108" s="2" t="s">
+        <v>206</v>
+      </c>
+      <c r="C108" s="2" t="s">
+        <v>207</v>
+      </c>
+      <c r="D108" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="E108" s="2" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="109" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A109" s="2" t="s">
+        <v>206</v>
+      </c>
+      <c r="C109" s="2" t="s">
+        <v>208</v>
+      </c>
+      <c r="D109" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="E109" s="2" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="110" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A110" s="2" t="s">
+        <v>209</v>
+      </c>
+      <c r="C110" s="2" t="s">
+        <v>210</v>
+      </c>
+      <c r="D110" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="E110" s="2" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="111" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A111" s="2" t="s">
+        <v>211</v>
+      </c>
+      <c r="C111" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="D111" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="E111" s="2" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="112" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A112" s="2" t="s">
+        <v>137</v>
+      </c>
+      <c r="C112" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="D112" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="E112" s="2" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="113" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A113" s="2" t="s">
+        <v>212</v>
+      </c>
+      <c r="C113" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="D113" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="E113" s="2" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="114" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A114" s="2" t="s">
+        <v>213</v>
+      </c>
+      <c r="C114" s="2" t="s">
+        <v>214</v>
+      </c>
+      <c r="D114" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="E114" s="2" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="115" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A115" s="2" t="s">
+        <v>215</v>
+      </c>
+      <c r="C115" s="2" t="s">
+        <v>214</v>
+      </c>
+      <c r="D115" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="E115" s="2" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="116" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A116" s="2" t="s">
+        <v>216</v>
+      </c>
+      <c r="C116" s="2" t="s">
+        <v>217</v>
+      </c>
+      <c r="D116" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="E116" s="2" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="117" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A117" s="2" t="s">
+        <v>211</v>
+      </c>
+      <c r="C117" s="2" t="s">
+        <v>218</v>
+      </c>
+      <c r="D117" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="E117" s="2" t="s">
         <v>123</v>
       </c>
     </row>

--- a/documents/job-applications.xlsx
+++ b/documents/job-applications.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\LARRY\Documents\Scripts\auto-job-app-sender\documents\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{37F88845-EA65-45FA-9BAD-9943BC002FE0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CF7D83F4-AE1A-4643-A725-77717CBA7447}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="510" uniqueCount="219">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="587" uniqueCount="237">
   <si>
     <t>company</t>
   </si>
@@ -677,6 +677,60 @@
   </si>
   <si>
     <t>ETL Developer</t>
+  </si>
+  <si>
+    <t>zayd@stratpoint.com</t>
+  </si>
+  <si>
+    <t>Trinity Workforce Solutions, Inc.</t>
+  </si>
+  <si>
+    <t>Avaloq</t>
+  </si>
+  <si>
+    <t>APplied</t>
+  </si>
+  <si>
+    <t>Nicoll Curtin</t>
+  </si>
+  <si>
+    <t>Avance</t>
+  </si>
+  <si>
+    <t>Python Developer</t>
+  </si>
+  <si>
+    <t>Land Transportation Systems, Inc.</t>
+  </si>
+  <si>
+    <t>RGP</t>
+  </si>
+  <si>
+    <t>PLDT</t>
+  </si>
+  <si>
+    <t>KPMG</t>
+  </si>
+  <si>
+    <t>Lingaro</t>
+  </si>
+  <si>
+    <t>Hiraya Tech</t>
+  </si>
+  <si>
+    <t>Programmer</t>
+  </si>
+  <si>
+    <t>51Talk</t>
+  </si>
+  <si>
+    <t>TapTalent.ai</t>
+  </si>
+  <si>
+    <t>Macquarie</t>
+  </si>
+  <si>
+    <t>Erni</t>
   </si>
 </sst>
 </file>
@@ -755,7 +809,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="11">
+  <cellXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
@@ -765,16 +819,15 @@
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
@@ -1081,7 +1134,7 @@
   <sheetPr>
     <outlinePr summaryBelow="0"/>
   </sheetPr>
-  <dimension ref="A1:H117"/>
+  <dimension ref="A1:H136"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="45.109375" style="2" bestFit="1" customWidth="1"/>
@@ -1886,10 +1939,10 @@
       <c r="D46" s="1" t="s">
         <v>107</v>
       </c>
-      <c r="G46" s="5" t="s">
+      <c r="G46" s="9" t="s">
         <v>108</v>
       </c>
-      <c r="H46" s="5"/>
+      <c r="H46" s="9"/>
     </row>
     <row r="47" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A47" s="1" t="s">
@@ -1943,10 +1996,10 @@
       <c r="D50" s="1" t="s">
         <v>116</v>
       </c>
-      <c r="G50" s="5" t="s">
+      <c r="G50" s="9" t="s">
         <v>115</v>
       </c>
-      <c r="H50" s="5"/>
+      <c r="H50" s="9"/>
     </row>
     <row r="51" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A51" s="1" t="s">
@@ -2303,7 +2356,7 @@
       <c r="D75" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="F75" s="6" t="s">
+      <c r="F75" s="5" t="s">
         <v>155</v>
       </c>
       <c r="G75" s="2" t="s">
@@ -2320,7 +2373,7 @@
       <c r="D76" s="2" t="s">
         <v>107</v>
       </c>
-      <c r="G76" s="6" t="s">
+      <c r="G76" s="5" t="s">
         <v>156</v>
       </c>
     </row>
@@ -2334,7 +2387,7 @@
       <c r="D77" s="2" t="s">
         <v>107</v>
       </c>
-      <c r="G77" s="7" t="s">
+      <c r="G77" s="6" t="s">
         <v>158</v>
       </c>
     </row>
@@ -2348,7 +2401,7 @@
       <c r="D78" s="2" t="s">
         <v>107</v>
       </c>
-      <c r="G78" s="6" t="s">
+      <c r="G78" s="5" t="s">
         <v>161</v>
       </c>
     </row>
@@ -2362,12 +2415,12 @@
       <c r="D79" s="2" t="s">
         <v>107</v>
       </c>
-      <c r="G79" s="6" t="s">
+      <c r="G79" s="5" t="s">
         <v>162</v>
       </c>
     </row>
     <row r="80" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A80" s="8" t="s">
+      <c r="A80" t="s">
         <v>165</v>
       </c>
       <c r="C80" s="2" t="s">
@@ -2376,7 +2429,7 @@
       <c r="D80" s="2" t="s">
         <v>107</v>
       </c>
-      <c r="G80" s="6" t="s">
+      <c r="G80" s="5" t="s">
         <v>164</v>
       </c>
     </row>
@@ -2390,7 +2443,7 @@
       <c r="D81" s="2" t="s">
         <v>107</v>
       </c>
-      <c r="G81" s="9" t="s">
+      <c r="G81" s="7" t="s">
         <v>166</v>
       </c>
     </row>
@@ -2404,7 +2457,7 @@
       <c r="D82" s="2" t="s">
         <v>107</v>
       </c>
-      <c r="G82" s="6" t="s">
+      <c r="G82" s="5" t="s">
         <v>168</v>
       </c>
     </row>
@@ -2418,7 +2471,7 @@
       <c r="D83" s="2" t="s">
         <v>107</v>
       </c>
-      <c r="G83" s="6" t="s">
+      <c r="G83" s="5" t="s">
         <v>169</v>
       </c>
     </row>
@@ -2488,7 +2541,7 @@
       <c r="D88" s="2" t="s">
         <v>107</v>
       </c>
-      <c r="G88" s="6" t="s">
+      <c r="G88" s="5" t="s">
         <v>173</v>
       </c>
     </row>
@@ -2502,10 +2555,10 @@
       <c r="D89" s="2" t="s">
         <v>107</v>
       </c>
-      <c r="G89" s="6" t="s">
+      <c r="G89" s="5" t="s">
         <v>174</v>
       </c>
-      <c r="H89" s="8">
+      <c r="H89">
         <v>9394791981</v>
       </c>
     </row>
@@ -2519,7 +2572,7 @@
       <c r="D90" s="2" t="s">
         <v>107</v>
       </c>
-      <c r="G90" s="6" t="s">
+      <c r="G90" s="5" t="s">
         <v>178</v>
       </c>
     </row>
@@ -2533,10 +2586,10 @@
       <c r="D91" s="2" t="s">
         <v>107</v>
       </c>
-      <c r="G91" s="6" t="s">
+      <c r="G91" s="5" t="s">
         <v>179</v>
       </c>
-      <c r="H91" s="8">
+      <c r="H91">
         <v>9270345867</v>
       </c>
     </row>
@@ -2550,10 +2603,10 @@
       <c r="D92" s="2" t="s">
         <v>107</v>
       </c>
-      <c r="G92" s="6" t="s">
+      <c r="G92" s="5" t="s">
         <v>181</v>
       </c>
-      <c r="H92" s="8">
+      <c r="H92">
         <v>639923742220</v>
       </c>
     </row>
@@ -2567,7 +2620,7 @@
       <c r="D93" s="2" t="s">
         <v>107</v>
       </c>
-      <c r="G93" s="10" t="s">
+      <c r="G93" s="8" t="s">
         <v>183</v>
       </c>
     </row>
@@ -2581,7 +2634,7 @@
       <c r="D94" s="2" t="s">
         <v>107</v>
       </c>
-      <c r="G94" s="6" t="s">
+      <c r="G94" s="5" t="s">
         <v>184</v>
       </c>
     </row>
@@ -2595,7 +2648,7 @@
       <c r="D95" s="2" t="s">
         <v>107</v>
       </c>
-      <c r="G95" s="6" t="s">
+      <c r="G95" s="5" t="s">
         <v>185</v>
       </c>
     </row>
@@ -2609,7 +2662,7 @@
       <c r="D96" s="2" t="s">
         <v>107</v>
       </c>
-      <c r="G96" s="6" t="s">
+      <c r="G96" s="5" t="s">
         <v>188</v>
       </c>
     </row>
@@ -2634,7 +2687,7 @@
       <c r="D98" s="2" t="s">
         <v>107</v>
       </c>
-      <c r="G98" s="6" t="s">
+      <c r="G98" s="5" t="s">
         <v>190</v>
       </c>
     </row>
@@ -2648,7 +2701,7 @@
       <c r="D99" s="2" t="s">
         <v>107</v>
       </c>
-      <c r="G99" s="6" t="s">
+      <c r="G99" s="5" t="s">
         <v>191</v>
       </c>
     </row>
@@ -2662,10 +2715,10 @@
       <c r="D100" s="2" t="s">
         <v>107</v>
       </c>
-      <c r="G100" s="6" t="s">
+      <c r="G100" s="5" t="s">
         <v>193</v>
       </c>
-      <c r="H100" s="8">
+      <c r="H100">
         <v>9695979091</v>
       </c>
     </row>
@@ -2679,7 +2732,7 @@
       <c r="D101" s="2" t="s">
         <v>107</v>
       </c>
-      <c r="G101" s="6" t="s">
+      <c r="G101" s="5" t="s">
         <v>195</v>
       </c>
     </row>
@@ -2693,7 +2746,7 @@
       <c r="D102" s="2" t="s">
         <v>107</v>
       </c>
-      <c r="G102" s="6" t="s">
+      <c r="G102" s="5" t="s">
         <v>197</v>
       </c>
     </row>
@@ -2707,7 +2760,7 @@
       <c r="D103" s="2" t="s">
         <v>107</v>
       </c>
-      <c r="G103" s="6" t="s">
+      <c r="G103" s="5" t="s">
         <v>199</v>
       </c>
     </row>
@@ -2721,7 +2774,7 @@
       <c r="D104" s="2" t="s">
         <v>107</v>
       </c>
-      <c r="G104" s="6" t="s">
+      <c r="G104" s="5" t="s">
         <v>201</v>
       </c>
     </row>
@@ -2744,7 +2797,7 @@
         <v>204</v>
       </c>
       <c r="D106" s="2" t="s">
-        <v>12</v>
+        <v>26</v>
       </c>
       <c r="E106" s="2" t="s">
         <v>123</v>
@@ -2758,7 +2811,7 @@
         <v>205</v>
       </c>
       <c r="D107" s="2" t="s">
-        <v>12</v>
+        <v>26</v>
       </c>
       <c r="E107" s="2" t="s">
         <v>123</v>
@@ -2800,7 +2853,7 @@
         <v>210</v>
       </c>
       <c r="D110" s="2" t="s">
-        <v>12</v>
+        <v>26</v>
       </c>
       <c r="E110" s="2" t="s">
         <v>123</v>
@@ -2834,7 +2887,7 @@
         <v>123</v>
       </c>
     </row>
-    <row r="113" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="113" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A113" s="2" t="s">
         <v>212</v>
       </c>
@@ -2842,13 +2895,13 @@
         <v>69</v>
       </c>
       <c r="D113" s="2" t="s">
-        <v>12</v>
+        <v>26</v>
       </c>
       <c r="E113" s="2" t="s">
         <v>123</v>
       </c>
     </row>
-    <row r="114" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="114" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A114" s="2" t="s">
         <v>213</v>
       </c>
@@ -2856,13 +2909,13 @@
         <v>214</v>
       </c>
       <c r="D114" s="2" t="s">
-        <v>12</v>
+        <v>26</v>
       </c>
       <c r="E114" s="2" t="s">
         <v>123</v>
       </c>
     </row>
-    <row r="115" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="115" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A115" s="2" t="s">
         <v>215</v>
       </c>
@@ -2870,13 +2923,13 @@
         <v>214</v>
       </c>
       <c r="D115" s="2" t="s">
-        <v>12</v>
+        <v>26</v>
       </c>
       <c r="E115" s="2" t="s">
         <v>123</v>
       </c>
     </row>
-    <row r="116" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="116" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A116" s="2" t="s">
         <v>216</v>
       </c>
@@ -2890,7 +2943,7 @@
         <v>123</v>
       </c>
     </row>
-    <row r="117" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="117" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A117" s="2" t="s">
         <v>211</v>
       </c>
@@ -2898,9 +2951,278 @@
         <v>218</v>
       </c>
       <c r="D117" s="2" t="s">
-        <v>12</v>
+        <v>26</v>
       </c>
       <c r="E117" s="2" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="118" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A118" s="2" t="s">
+        <v>170</v>
+      </c>
+      <c r="C118" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="D118" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="E118" s="2" t="s">
+        <v>123</v>
+      </c>
+      <c r="G118" s="2" t="s">
+        <v>219</v>
+      </c>
+    </row>
+    <row r="119" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A119" s="2" t="s">
+        <v>220</v>
+      </c>
+      <c r="C119" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="D119" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="E119" s="2" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="120" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A120" s="2" t="s">
+        <v>221</v>
+      </c>
+      <c r="C120" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="D120" s="2" t="s">
+        <v>222</v>
+      </c>
+      <c r="E120" s="2" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="121" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A121" s="2" t="s">
+        <v>223</v>
+      </c>
+      <c r="C121" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="D121" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="E121" s="2" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="122" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A122" s="2" t="s">
+        <v>224</v>
+      </c>
+      <c r="C122" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="D122" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="E122" s="2" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="123" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A123" s="2" t="s">
+        <v>98</v>
+      </c>
+      <c r="C123" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="D123" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="E123" s="2" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="124" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A124" s="2" t="s">
+        <v>213</v>
+      </c>
+      <c r="C124" s="2" t="s">
+        <v>225</v>
+      </c>
+      <c r="D124" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="E124" s="2" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="125" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A125" s="2" t="s">
+        <v>226</v>
+      </c>
+      <c r="C125" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="D125" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="E125" s="2" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="126" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A126" s="2" t="s">
+        <v>141</v>
+      </c>
+      <c r="C126" s="2" t="s">
+        <v>67</v>
+      </c>
+      <c r="D126" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="E126" s="2" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="127" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A127" s="2" t="s">
+        <v>227</v>
+      </c>
+      <c r="C127" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="D127" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="E127" s="2" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="128" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A128" s="2" t="s">
+        <v>163</v>
+      </c>
+      <c r="C128" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="D128" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="E128" s="2" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="129" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A129" s="2" t="s">
+        <v>228</v>
+      </c>
+      <c r="C129" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="D129" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="E129" s="2" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="130" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A130" s="2" t="s">
+        <v>229</v>
+      </c>
+      <c r="C130" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="D130" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="E130" s="2" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="131" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A131" s="2" t="s">
+        <v>230</v>
+      </c>
+      <c r="C131" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="D131" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="E131" s="2" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="132" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A132" s="2" t="s">
+        <v>231</v>
+      </c>
+      <c r="C132" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="D132" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="E132" s="2" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="133" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A133" s="2" t="s">
+        <v>233</v>
+      </c>
+      <c r="C133" s="2" t="s">
+        <v>232</v>
+      </c>
+      <c r="D133" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="E133" s="2" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="134" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A134" s="2" t="s">
+        <v>234</v>
+      </c>
+      <c r="C134" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="D134" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="E134" s="2" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="135" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A135" s="2" t="s">
+        <v>235</v>
+      </c>
+      <c r="C135" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="D135" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="E135" s="2" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="136" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A136" s="2" t="s">
+        <v>236</v>
+      </c>
+      <c r="C136" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="D136" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="E136" s="2" t="s">
         <v>123</v>
       </c>
     </row>

--- a/documents/job-applications.xlsx
+++ b/documents/job-applications.xlsx
@@ -1,16 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="28429"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
+  <fileVersion appName="xl" lastEdited="6" lowestEdited="5" rupBuild="14420"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\LARRY\Documents\Scripts\auto-job-app-sender\documents\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Projects\To Github\auto-job-app-sender\documents\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CF7D83F4-AE1A-4643-A725-77717CBA7447}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-105" yWindow="-105" windowWidth="23250" windowHeight="12450"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -20,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="587" uniqueCount="237">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="622" uniqueCount="249">
   <si>
     <t>company</t>
   </si>
@@ -731,13 +730,49 @@
   </si>
   <si>
     <t>Erni</t>
+  </si>
+  <si>
+    <t>Sprout Solutions</t>
+  </si>
+  <si>
+    <t>jorgecrisan.botana@billease.ph</t>
+  </si>
+  <si>
+    <t>Billease</t>
+  </si>
+  <si>
+    <t>Bossjobs</t>
+  </si>
+  <si>
+    <t>denise@bossjob.ph</t>
+  </si>
+  <si>
+    <t>SBSI</t>
+  </si>
+  <si>
+    <t>harvey.gamboa@sbsi.com.ph</t>
+  </si>
+  <si>
+    <t>Pointwest Innovations Corp.</t>
+  </si>
+  <si>
+    <t>Media Meter</t>
+  </si>
+  <si>
+    <t>Gardenia</t>
+  </si>
+  <si>
+    <t>Jora</t>
+  </si>
+  <si>
+    <t>WHR Global Consulting</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="5" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
+  <fonts count="6" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -774,6 +809,12 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF222222"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
   </fonts>
   <fills count="3">
     <fill>
@@ -809,7 +850,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
@@ -828,6 +869,7 @@
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
@@ -1130,25 +1172,25 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr>
     <outlinePr summaryBelow="0"/>
   </sheetPr>
-  <dimension ref="A1:H136"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <dimension ref="A1:H145"/>
+  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="45.109375" style="2" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="36.44140625" style="2" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="46.44140625" style="2" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="25.44140625" style="2" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="13.5546875" style="2" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="53.109375" style="2" customWidth="1"/>
-    <col min="7" max="7" width="22.6640625" style="2" customWidth="1"/>
-    <col min="8" max="8" width="23.44140625" style="2" customWidth="1"/>
-    <col min="9" max="16384" width="8.88671875" style="2"/>
+    <col min="1" max="1" width="45.140625" style="2" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="36.42578125" style="2" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="46.42578125" style="2" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="25.42578125" style="2" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="13.5703125" style="2" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="53.140625" style="2" customWidth="1"/>
+    <col min="7" max="7" width="22.7109375" style="2" customWidth="1"/>
+    <col min="8" max="8" width="23.42578125" style="2" customWidth="1"/>
+    <col min="9" max="16384" width="8.85546875" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:8" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1174,7 +1216,7 @@
         <v>176</v>
       </c>
     </row>
-    <row r="2" spans="1:8" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:8" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
         <v>6</v>
       </c>
@@ -1192,7 +1234,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="3" spans="1:8" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:8" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
         <v>6</v>
       </c>
@@ -1210,7 +1252,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="4" spans="1:8" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:8" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
         <v>13</v>
       </c>
@@ -1226,7 +1268,7 @@
       </c>
       <c r="F4" s="1"/>
     </row>
-    <row r="5" spans="1:8" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:8" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="1" t="s">
         <v>15</v>
       </c>
@@ -1244,7 +1286,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="6" spans="1:8" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:8" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="1" t="s">
         <v>17</v>
       </c>
@@ -1260,7 +1302,7 @@
       </c>
       <c r="F6" s="1"/>
     </row>
-    <row r="7" spans="1:8" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:8" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="1" t="s">
         <v>17</v>
       </c>
@@ -1276,7 +1318,7 @@
       </c>
       <c r="F7" s="1"/>
     </row>
-    <row r="8" spans="1:8" ht="33" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:8" ht="33" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="1" t="s">
         <v>20</v>
       </c>
@@ -1294,7 +1336,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="9" spans="1:8" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:8" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="1" t="s">
         <v>20</v>
       </c>
@@ -1312,7 +1354,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="10" spans="1:8" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:8" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="1" t="s">
         <v>24</v>
       </c>
@@ -1330,7 +1372,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="11" spans="1:8" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:8" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="1" t="s">
         <v>28</v>
       </c>
@@ -1348,7 +1390,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="12" spans="1:8" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:8" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="1" t="s">
         <v>31</v>
       </c>
@@ -1366,7 +1408,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="13" spans="1:8" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:8" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="1" t="s">
         <v>34</v>
       </c>
@@ -1384,7 +1426,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="14" spans="1:8" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:8" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="1" t="s">
         <v>37</v>
       </c>
@@ -1402,7 +1444,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="15" spans="1:8" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:8" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="1" t="s">
         <v>37</v>
       </c>
@@ -1420,7 +1462,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="16" spans="1:8" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:8" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="1" t="s">
         <v>42</v>
       </c>
@@ -1438,7 +1480,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="17" spans="1:6" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:6" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="1" t="s">
         <v>45</v>
       </c>
@@ -1456,7 +1498,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="18" spans="1:6" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:6" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" s="3" t="s">
         <v>48</v>
       </c>
@@ -1474,7 +1516,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="19" spans="1:6" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:6" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19" s="1" t="s">
         <v>51</v>
       </c>
@@ -1492,7 +1534,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="20" spans="1:6" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:6" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" s="1" t="s">
         <v>53</v>
       </c>
@@ -1510,7 +1552,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="21" spans="1:6" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:6" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21" s="1" t="s">
         <v>57</v>
       </c>
@@ -1528,7 +1570,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="22" spans="1:6" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:6" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A22" s="1" t="s">
         <v>57</v>
       </c>
@@ -1546,7 +1588,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="23" spans="1:6" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:6" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A23" s="1" t="s">
         <v>57</v>
       </c>
@@ -1564,7 +1606,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="24" spans="1:6" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:6" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A24" s="1" t="s">
         <v>63</v>
       </c>
@@ -1582,7 +1624,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="25" spans="1:6" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:6" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A25" s="1" t="s">
         <v>66</v>
       </c>
@@ -1600,7 +1642,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="26" spans="1:6" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:6" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A26" s="1" t="s">
         <v>63</v>
       </c>
@@ -1618,7 +1660,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="27" spans="1:6" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:6" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A27" s="1" t="s">
         <v>63</v>
       </c>
@@ -1636,7 +1678,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="28" spans="1:6" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:6" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A28" s="1" t="s">
         <v>71</v>
       </c>
@@ -1654,7 +1696,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="29" spans="1:6" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:6" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A29" s="1" t="s">
         <v>74</v>
       </c>
@@ -1672,7 +1714,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="30" spans="1:6" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:6" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A30" s="1" t="s">
         <v>77</v>
       </c>
@@ -1692,7 +1734,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="31" spans="1:6" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:6" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A31" s="1" t="s">
         <v>77</v>
       </c>
@@ -1712,7 +1754,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="32" spans="1:6" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:6" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A32" s="1" t="s">
         <v>81</v>
       </c>
@@ -1729,7 +1771,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="33" spans="1:8" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:8" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A33" s="1" t="s">
         <v>84</v>
       </c>
@@ -1746,7 +1788,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="34" spans="1:8" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:8" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A34" s="1" t="s">
         <v>84</v>
       </c>
@@ -1760,7 +1802,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="35" spans="1:8" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:8" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A35" s="1" t="s">
         <v>87</v>
       </c>
@@ -1774,7 +1816,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="36" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A36" s="1" t="s">
         <v>89</v>
       </c>
@@ -1791,7 +1833,7 @@
         <v>92</v>
       </c>
     </row>
-    <row r="37" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A37" s="1" t="s">
         <v>93</v>
       </c>
@@ -1808,7 +1850,7 @@
         <v>94</v>
       </c>
     </row>
-    <row r="38" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A38" s="1" t="s">
         <v>95</v>
       </c>
@@ -1822,7 +1864,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="39" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A39" s="1" t="s">
         <v>96</v>
       </c>
@@ -1836,7 +1878,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="40" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A40" s="1" t="s">
         <v>97</v>
       </c>
@@ -1850,7 +1892,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="41" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A41" s="1" t="s">
         <v>98</v>
       </c>
@@ -1867,7 +1909,7 @@
         <v>99</v>
       </c>
     </row>
-    <row r="42" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A42" s="1" t="s">
         <v>100</v>
       </c>
@@ -1881,7 +1923,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="43" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A43" s="1" t="s">
         <v>101</v>
       </c>
@@ -1898,7 +1940,7 @@
         <v>103</v>
       </c>
     </row>
-    <row r="44" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A44" s="1" t="s">
         <v>101</v>
       </c>
@@ -1915,7 +1957,7 @@
         <v>103</v>
       </c>
     </row>
-    <row r="45" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A45" s="2" t="s">
         <v>105</v>
       </c>
@@ -1929,7 +1971,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="46" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A46" s="1" t="s">
         <v>106</v>
       </c>
@@ -1944,7 +1986,7 @@
       </c>
       <c r="H46" s="9"/>
     </row>
-    <row r="47" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A47" s="1" t="s">
         <v>110</v>
       </c>
@@ -1958,7 +2000,7 @@
         <v>109</v>
       </c>
     </row>
-    <row r="48" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A48" s="1" t="s">
         <v>111</v>
       </c>
@@ -1972,7 +2014,7 @@
         <v>112</v>
       </c>
     </row>
-    <row r="49" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A49" s="1" t="s">
         <v>114</v>
       </c>
@@ -1986,7 +2028,7 @@
         <v>113</v>
       </c>
     </row>
-    <row r="50" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A50" s="1" t="s">
         <v>117</v>
       </c>
@@ -2001,7 +2043,7 @@
       </c>
       <c r="H50" s="9"/>
     </row>
-    <row r="51" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A51" s="1" t="s">
         <v>120</v>
       </c>
@@ -2015,7 +2057,7 @@
         <v>118</v>
       </c>
     </row>
-    <row r="52" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A52" s="1" t="s">
         <v>120</v>
       </c>
@@ -2029,7 +2071,7 @@
         <v>119</v>
       </c>
     </row>
-    <row r="53" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="53" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A53" s="1" t="s">
         <v>57</v>
       </c>
@@ -2043,7 +2085,7 @@
         <v>121</v>
       </c>
     </row>
-    <row r="54" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="54" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A54" s="2" t="s">
         <v>122</v>
       </c>
@@ -2057,7 +2099,7 @@
         <v>123</v>
       </c>
     </row>
-    <row r="55" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="55" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A55" s="2" t="s">
         <v>124</v>
       </c>
@@ -2071,7 +2113,7 @@
         <v>123</v>
       </c>
     </row>
-    <row r="56" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="56" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A56" s="2" t="s">
         <v>125</v>
       </c>
@@ -2085,7 +2127,7 @@
         <v>123</v>
       </c>
     </row>
-    <row r="57" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="57" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A57" s="2" t="s">
         <v>127</v>
       </c>
@@ -2102,7 +2144,7 @@
         <v>128</v>
       </c>
     </row>
-    <row r="58" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="58" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A58" s="2" t="s">
         <v>129</v>
       </c>
@@ -2116,7 +2158,7 @@
         <v>123</v>
       </c>
     </row>
-    <row r="59" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="59" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A59" s="2" t="s">
         <v>130</v>
       </c>
@@ -2130,7 +2172,7 @@
         <v>123</v>
       </c>
     </row>
-    <row r="60" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="60" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A60" s="2" t="s">
         <v>131</v>
       </c>
@@ -2144,7 +2186,7 @@
         <v>123</v>
       </c>
     </row>
-    <row r="61" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="61" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A61" s="2" t="s">
         <v>133</v>
       </c>
@@ -2161,7 +2203,7 @@
         <v>134</v>
       </c>
     </row>
-    <row r="62" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="62" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A62" s="2" t="s">
         <v>131</v>
       </c>
@@ -2175,7 +2217,7 @@
         <v>123</v>
       </c>
     </row>
-    <row r="63" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="63" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A63" s="2" t="s">
         <v>98</v>
       </c>
@@ -2192,7 +2234,7 @@
         <v>135</v>
       </c>
     </row>
-    <row r="64" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="64" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A64" s="2" t="s">
         <v>136</v>
       </c>
@@ -2206,7 +2248,7 @@
         <v>123</v>
       </c>
     </row>
-    <row r="65" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="65" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A65" s="2" t="s">
         <v>137</v>
       </c>
@@ -2220,7 +2262,7 @@
         <v>123</v>
       </c>
     </row>
-    <row r="66" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="66" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A66" s="2" t="s">
         <v>138</v>
       </c>
@@ -2234,7 +2276,7 @@
         <v>123</v>
       </c>
     </row>
-    <row r="67" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="67" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A67" s="2" t="s">
         <v>122</v>
       </c>
@@ -2248,7 +2290,7 @@
         <v>123</v>
       </c>
     </row>
-    <row r="68" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="68" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A68" s="2" t="s">
         <v>141</v>
       </c>
@@ -2262,7 +2304,7 @@
         <v>123</v>
       </c>
     </row>
-    <row r="69" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="69" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A69" s="2" t="s">
         <v>143</v>
       </c>
@@ -2276,7 +2318,7 @@
         <v>123</v>
       </c>
     </row>
-    <row r="70" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="70" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A70" s="2" t="s">
         <v>130</v>
       </c>
@@ -2290,7 +2332,7 @@
         <v>123</v>
       </c>
     </row>
-    <row r="71" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="71" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A71" s="2" t="s">
         <v>146</v>
       </c>
@@ -2304,7 +2346,7 @@
         <v>123</v>
       </c>
     </row>
-    <row r="72" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="72" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A72" s="2" t="s">
         <v>148</v>
       </c>
@@ -2318,7 +2360,7 @@
         <v>149</v>
       </c>
     </row>
-    <row r="73" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="73" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A73" s="2" t="s">
         <v>150</v>
       </c>
@@ -2332,7 +2374,7 @@
         <v>151</v>
       </c>
     </row>
-    <row r="74" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="74" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A74" s="2" t="s">
         <v>153</v>
       </c>
@@ -2346,7 +2388,7 @@
         <v>152</v>
       </c>
     </row>
-    <row r="75" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="75" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A75" s="2" t="s">
         <v>111</v>
       </c>
@@ -2363,7 +2405,7 @@
         <v>112</v>
       </c>
     </row>
-    <row r="76" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="76" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A76" s="2" t="s">
         <v>157</v>
       </c>
@@ -2377,7 +2419,7 @@
         <v>156</v>
       </c>
     </row>
-    <row r="77" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="77" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A77" s="2" t="s">
         <v>159</v>
       </c>
@@ -2391,7 +2433,7 @@
         <v>158</v>
       </c>
     </row>
-    <row r="78" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="78" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A78" s="2" t="s">
         <v>160</v>
       </c>
@@ -2405,7 +2447,7 @@
         <v>161</v>
       </c>
     </row>
-    <row r="79" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="79" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A79" s="2" t="s">
         <v>163</v>
       </c>
@@ -2419,7 +2461,7 @@
         <v>162</v>
       </c>
     </row>
-    <row r="80" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="80" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A80" t="s">
         <v>165</v>
       </c>
@@ -2433,7 +2475,7 @@
         <v>164</v>
       </c>
     </row>
-    <row r="81" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="81" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A81" s="2" t="s">
         <v>167</v>
       </c>
@@ -2447,7 +2489,7 @@
         <v>166</v>
       </c>
     </row>
-    <row r="82" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="82" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A82" s="2" t="s">
         <v>138</v>
       </c>
@@ -2461,7 +2503,7 @@
         <v>168</v>
       </c>
     </row>
-    <row r="83" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="83" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A83" s="2" t="s">
         <v>159</v>
       </c>
@@ -2475,7 +2517,7 @@
         <v>169</v>
       </c>
     </row>
-    <row r="84" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="84" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A84" s="2" t="s">
         <v>170</v>
       </c>
@@ -2489,7 +2531,7 @@
         <v>123</v>
       </c>
     </row>
-    <row r="85" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="85" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A85" s="2" t="s">
         <v>171</v>
       </c>
@@ -2503,7 +2545,7 @@
         <v>123</v>
       </c>
     </row>
-    <row r="86" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="86" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A86" s="2" t="s">
         <v>129</v>
       </c>
@@ -2517,7 +2559,7 @@
         <v>123</v>
       </c>
     </row>
-    <row r="87" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="87" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A87" s="2" t="s">
         <v>122</v>
       </c>
@@ -2531,7 +2573,7 @@
         <v>123</v>
       </c>
     </row>
-    <row r="88" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="88" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A88" s="2" t="s">
         <v>172</v>
       </c>
@@ -2545,7 +2587,7 @@
         <v>173</v>
       </c>
     </row>
-    <row r="89" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="89" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A89" s="2" t="s">
         <v>177</v>
       </c>
@@ -2562,7 +2604,7 @@
         <v>9394791981</v>
       </c>
     </row>
-    <row r="90" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="90" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A90" s="2" t="s">
         <v>57</v>
       </c>
@@ -2576,7 +2618,7 @@
         <v>178</v>
       </c>
     </row>
-    <row r="91" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="91" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A91" s="2" t="s">
         <v>143</v>
       </c>
@@ -2593,7 +2635,7 @@
         <v>9270345867</v>
       </c>
     </row>
-    <row r="92" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="92" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A92" s="2" t="s">
         <v>180</v>
       </c>
@@ -2610,7 +2652,7 @@
         <v>639923742220</v>
       </c>
     </row>
-    <row r="93" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="93" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A93" s="2" t="s">
         <v>182</v>
       </c>
@@ -2624,7 +2666,7 @@
         <v>183</v>
       </c>
     </row>
-    <row r="94" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="94" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A94" s="2" t="s">
         <v>131</v>
       </c>
@@ -2638,7 +2680,7 @@
         <v>184</v>
       </c>
     </row>
-    <row r="95" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="95" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A95" s="2" t="s">
         <v>186</v>
       </c>
@@ -2652,7 +2694,7 @@
         <v>185</v>
       </c>
     </row>
-    <row r="96" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="96" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A96" s="2" t="s">
         <v>187</v>
       </c>
@@ -2666,7 +2708,7 @@
         <v>188</v>
       </c>
     </row>
-    <row r="97" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="97" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A97" s="2" t="s">
         <v>189</v>
       </c>
@@ -2677,7 +2719,7 @@
         <v>107</v>
       </c>
     </row>
-    <row r="98" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="98" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A98" s="2" t="s">
         <v>57</v>
       </c>
@@ -2691,7 +2733,7 @@
         <v>190</v>
       </c>
     </row>
-    <row r="99" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="99" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A99" s="2" t="s">
         <v>192</v>
       </c>
@@ -2705,7 +2747,7 @@
         <v>191</v>
       </c>
     </row>
-    <row r="100" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="100" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A100" s="2" t="s">
         <v>194</v>
       </c>
@@ -2722,7 +2764,7 @@
         <v>9695979091</v>
       </c>
     </row>
-    <row r="101" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="101" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A101" s="2" t="s">
         <v>196</v>
       </c>
@@ -2736,7 +2778,7 @@
         <v>195</v>
       </c>
     </row>
-    <row r="102" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="102" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A102" s="2" t="s">
         <v>198</v>
       </c>
@@ -2750,7 +2792,7 @@
         <v>197</v>
       </c>
     </row>
-    <row r="103" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="103" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A103" s="2" t="s">
         <v>192</v>
       </c>
@@ -2764,7 +2806,7 @@
         <v>199</v>
       </c>
     </row>
-    <row r="104" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="104" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A104" s="2" t="s">
         <v>200</v>
       </c>
@@ -2778,7 +2820,7 @@
         <v>201</v>
       </c>
     </row>
-    <row r="105" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="105" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A105" s="2" t="s">
         <v>202</v>
       </c>
@@ -2789,7 +2831,7 @@
         <v>107</v>
       </c>
     </row>
-    <row r="106" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="106" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A106" s="2" t="s">
         <v>203</v>
       </c>
@@ -2803,7 +2845,7 @@
         <v>123</v>
       </c>
     </row>
-    <row r="107" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="107" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A107" s="2" t="s">
         <v>98</v>
       </c>
@@ -2817,7 +2859,7 @@
         <v>123</v>
       </c>
     </row>
-    <row r="108" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="108" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A108" s="2" t="s">
         <v>206</v>
       </c>
@@ -2831,7 +2873,7 @@
         <v>123</v>
       </c>
     </row>
-    <row r="109" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="109" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A109" s="2" t="s">
         <v>206</v>
       </c>
@@ -2845,7 +2887,7 @@
         <v>123</v>
       </c>
     </row>
-    <row r="110" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="110" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A110" s="2" t="s">
         <v>209</v>
       </c>
@@ -2859,7 +2901,7 @@
         <v>123</v>
       </c>
     </row>
-    <row r="111" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="111" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A111" s="2" t="s">
         <v>211</v>
       </c>
@@ -2873,7 +2915,7 @@
         <v>123</v>
       </c>
     </row>
-    <row r="112" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="112" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A112" s="2" t="s">
         <v>137</v>
       </c>
@@ -2887,7 +2929,7 @@
         <v>123</v>
       </c>
     </row>
-    <row r="113" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="113" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A113" s="2" t="s">
         <v>212</v>
       </c>
@@ -2901,7 +2943,7 @@
         <v>123</v>
       </c>
     </row>
-    <row r="114" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="114" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A114" s="2" t="s">
         <v>213</v>
       </c>
@@ -2915,7 +2957,7 @@
         <v>123</v>
       </c>
     </row>
-    <row r="115" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="115" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A115" s="2" t="s">
         <v>215</v>
       </c>
@@ -2929,7 +2971,7 @@
         <v>123</v>
       </c>
     </row>
-    <row r="116" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="116" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A116" s="2" t="s">
         <v>216</v>
       </c>
@@ -2943,7 +2985,7 @@
         <v>123</v>
       </c>
     </row>
-    <row r="117" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="117" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A117" s="2" t="s">
         <v>211</v>
       </c>
@@ -2957,7 +2999,7 @@
         <v>123</v>
       </c>
     </row>
-    <row r="118" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="118" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A118" s="2" t="s">
         <v>170</v>
       </c>
@@ -2974,7 +3016,7 @@
         <v>219</v>
       </c>
     </row>
-    <row r="119" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="119" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A119" s="2" t="s">
         <v>220</v>
       </c>
@@ -2988,7 +3030,7 @@
         <v>123</v>
       </c>
     </row>
-    <row r="120" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="120" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A120" s="2" t="s">
         <v>221</v>
       </c>
@@ -3002,7 +3044,7 @@
         <v>123</v>
       </c>
     </row>
-    <row r="121" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="121" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A121" s="2" t="s">
         <v>223</v>
       </c>
@@ -3016,7 +3058,7 @@
         <v>123</v>
       </c>
     </row>
-    <row r="122" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="122" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A122" s="2" t="s">
         <v>224</v>
       </c>
@@ -3030,7 +3072,7 @@
         <v>123</v>
       </c>
     </row>
-    <row r="123" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="123" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A123" s="2" t="s">
         <v>98</v>
       </c>
@@ -3044,7 +3086,7 @@
         <v>123</v>
       </c>
     </row>
-    <row r="124" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="124" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A124" s="2" t="s">
         <v>213</v>
       </c>
@@ -3058,7 +3100,7 @@
         <v>123</v>
       </c>
     </row>
-    <row r="125" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="125" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A125" s="2" t="s">
         <v>226</v>
       </c>
@@ -3072,7 +3114,7 @@
         <v>123</v>
       </c>
     </row>
-    <row r="126" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="126" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A126" s="2" t="s">
         <v>141</v>
       </c>
@@ -3086,7 +3128,7 @@
         <v>123</v>
       </c>
     </row>
-    <row r="127" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="127" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A127" s="2" t="s">
         <v>227</v>
       </c>
@@ -3100,7 +3142,7 @@
         <v>123</v>
       </c>
     </row>
-    <row r="128" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="128" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A128" s="2" t="s">
         <v>163</v>
       </c>
@@ -3114,7 +3156,7 @@
         <v>123</v>
       </c>
     </row>
-    <row r="129" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="129" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A129" s="2" t="s">
         <v>228</v>
       </c>
@@ -3128,7 +3170,7 @@
         <v>123</v>
       </c>
     </row>
-    <row r="130" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="130" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A130" s="2" t="s">
         <v>229</v>
       </c>
@@ -3142,7 +3184,7 @@
         <v>123</v>
       </c>
     </row>
-    <row r="131" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="131" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A131" s="2" t="s">
         <v>230</v>
       </c>
@@ -3156,7 +3198,7 @@
         <v>123</v>
       </c>
     </row>
-    <row r="132" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="132" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A132" s="2" t="s">
         <v>231</v>
       </c>
@@ -3170,7 +3212,7 @@
         <v>123</v>
       </c>
     </row>
-    <row r="133" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="133" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A133" s="2" t="s">
         <v>233</v>
       </c>
@@ -3184,7 +3226,7 @@
         <v>123</v>
       </c>
     </row>
-    <row r="134" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="134" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A134" s="2" t="s">
         <v>234</v>
       </c>
@@ -3198,7 +3240,7 @@
         <v>123</v>
       </c>
     </row>
-    <row r="135" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="135" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A135" s="2" t="s">
         <v>235</v>
       </c>
@@ -3212,7 +3254,7 @@
         <v>123</v>
       </c>
     </row>
-    <row r="136" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="136" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A136" s="2" t="s">
         <v>236</v>
       </c>
@@ -3224,6 +3266,129 @@
       </c>
       <c r="E136" s="2" t="s">
         <v>123</v>
+      </c>
+    </row>
+    <row r="137" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A137" s="2" t="s">
+        <v>237</v>
+      </c>
+      <c r="C137" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="D137" s="2" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="138" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A138" s="2" t="s">
+        <v>239</v>
+      </c>
+      <c r="C138" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="D138" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="F138" s="10" t="s">
+        <v>238</v>
+      </c>
+    </row>
+    <row r="139" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A139" s="2" t="s">
+        <v>240</v>
+      </c>
+      <c r="C139" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="D139" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="F139" s="2" t="s">
+        <v>241</v>
+      </c>
+    </row>
+    <row r="140" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A140" s="2" t="s">
+        <v>242</v>
+      </c>
+      <c r="C140" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="D140" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="F140" s="2" t="s">
+        <v>243</v>
+      </c>
+    </row>
+    <row r="141" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A141" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="C141" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="D141" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="E141" s="2" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="142" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A142" s="2" t="s">
+        <v>244</v>
+      </c>
+      <c r="C142" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="D142" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="E142" s="2" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="143" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A143" s="2" t="s">
+        <v>245</v>
+      </c>
+      <c r="C143" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="D143" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="E143" s="2" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="144" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A144" s="2" t="s">
+        <v>246</v>
+      </c>
+      <c r="C144" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="D144" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="E144" s="2" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="145" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A145" s="2" t="s">
+        <v>248</v>
+      </c>
+      <c r="C145" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="D145" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="E145" s="2" t="s">
+        <v>247</v>
       </c>
     </row>
   </sheetData>
@@ -3232,32 +3397,33 @@
     <mergeCell ref="G50:H50"/>
   </mergeCells>
   <hyperlinks>
-    <hyperlink ref="G51" r:id="rId1" display="mailto:angeliqu.misa@vxi.com" xr:uid="{F8822347-4DA6-4E1C-A199-2A7D94621AA7}"/>
-    <hyperlink ref="G53" r:id="rId2" display="mailto:daniella.mae.m.bisda@accenture.com" xr:uid="{5736F313-6CD2-4F50-B11A-CAF420139990}"/>
-    <hyperlink ref="F75" r:id="rId3" xr:uid="{1F35D3D0-D2E4-44F7-A294-1D932740061B}"/>
-    <hyperlink ref="G76" r:id="rId4" display="mailto:vcvisda@unionbankph.com" xr:uid="{2B50802A-78DE-45BD-8487-7B04C5C69BCC}"/>
-    <hyperlink ref="G77" r:id="rId5" display="mailto:mhelbert.paredes17@gmail.com" xr:uid="{3A70F298-6A85-485F-B784-E721910E61AD}"/>
-    <hyperlink ref="G78" r:id="rId6" display="mailto:maricvid@amazon.com" xr:uid="{B0781B8C-DB3D-4E3B-BDC9-1B4BFFA4F80F}"/>
-    <hyperlink ref="G79" r:id="rId7" display="mailto:ryan.rivera@telusinternational.com" xr:uid="{6FB8D0A7-3746-4063-ADC1-39039DC75449}"/>
-    <hyperlink ref="G80" r:id="rId8" display="mailto:060290remfelguillenabelandres@gmail.com" xr:uid="{A4145F4D-D6B4-4735-9CFD-6E9D7170DCB7}"/>
-    <hyperlink ref="G82" r:id="rId9" display="mailto:aprilchristine024@gmail.com" xr:uid="{16F6E4B8-B4D2-49BF-98EE-3D097721E81B}"/>
-    <hyperlink ref="G83" r:id="rId10" display="mailto:lyanatorrecampo@gmail.com" xr:uid="{D51965BF-4764-4516-B002-98A2E111999F}"/>
-    <hyperlink ref="G88" r:id="rId11" display="mailto:ljayme@yondu.com" xr:uid="{B8D84DF7-0660-4ABB-B6B3-EC4399E9E1B6}"/>
-    <hyperlink ref="G89" r:id="rId12" display="mailto:miiraaa14@gmail.com" xr:uid="{152360AF-DCC6-4B5C-A953-BE4BE0336D85}"/>
-    <hyperlink ref="G90" r:id="rId13" display="mailto:floriedelsanchez@gmail.com" xr:uid="{7637E896-0CD3-4EB0-98B2-5F6E6BAD95D2}"/>
-    <hyperlink ref="G91" r:id="rId14" display="mailto:iamchristinelopez@yahoo.com" xr:uid="{A09DB61A-7FA6-4FEB-ACA9-712996ABCA45}"/>
-    <hyperlink ref="G92" r:id="rId15" display="mailto:donnatamayodlt@gmail.com" xr:uid="{F1BDD7F7-18B2-4C58-83B3-8C625C90694E}"/>
-    <hyperlink ref="G94" r:id="rId16" display="mailto:jannachristina.liwanag@emerson.com" xr:uid="{3A73A12A-16C8-476F-AFEF-1361A084559A}"/>
-    <hyperlink ref="G95" r:id="rId17" display="mailto:antuazon@hrnetworkph.com" xr:uid="{53C7618E-6977-4B29-BF35-86BAFD22CF7E}"/>
-    <hyperlink ref="G96" r:id="rId18" display="mailto:kqxmc2mcmr@privaterelay.appleid.com" xr:uid="{BCCB1F5B-FA73-43B1-993A-97328E59A748}"/>
-    <hyperlink ref="G98" r:id="rId19" display="mailto:sheanasunga@gmail.com" xr:uid="{696C44F2-33F8-4D1C-85E3-B23516398A3A}"/>
-    <hyperlink ref="G99" r:id="rId20" display="mailto:gabatajohnmartin@gmail.com" xr:uid="{08544EF3-D7EB-402E-AF77-ED725C298C68}"/>
-    <hyperlink ref="G100" r:id="rId21" display="mailto:ncorpuz@enshored.com" xr:uid="{035A0D76-EEC3-4B02-AB1B-9FA0BFEC1ED1}"/>
-    <hyperlink ref="G101" r:id="rId22" display="mailto:krystel.dimalibot@gmail.com" xr:uid="{0536CED5-725F-4C6D-A39D-AD0A28E0182A}"/>
-    <hyperlink ref="G102" r:id="rId23" display="mailto:alessandrian04@gmail.com" xr:uid="{EF7858F4-4749-49F3-832D-C20C07D0160C}"/>
-    <hyperlink ref="G103" r:id="rId24" display="mailto:jgrojas1208@gmail.com" xr:uid="{127D1963-A796-4043-B835-D4E9B5C4BF9E}"/>
-    <hyperlink ref="G104" r:id="rId25" display="mailto:adrianejomeldupo.s@infosys.com" xr:uid="{55DD9FC8-5D3B-4C7F-8283-365B41814C2C}"/>
+    <hyperlink ref="G51" r:id="rId1" display="mailto:angeliqu.misa@vxi.com"/>
+    <hyperlink ref="G53" r:id="rId2" display="mailto:daniella.mae.m.bisda@accenture.com"/>
+    <hyperlink ref="F75" r:id="rId3"/>
+    <hyperlink ref="G76" r:id="rId4" display="mailto:vcvisda@unionbankph.com"/>
+    <hyperlink ref="G77" r:id="rId5" display="mailto:mhelbert.paredes17@gmail.com"/>
+    <hyperlink ref="G78" r:id="rId6" display="mailto:maricvid@amazon.com"/>
+    <hyperlink ref="G79" r:id="rId7" display="mailto:ryan.rivera@telusinternational.com"/>
+    <hyperlink ref="G80" r:id="rId8" display="mailto:060290remfelguillenabelandres@gmail.com"/>
+    <hyperlink ref="G82" r:id="rId9" display="mailto:aprilchristine024@gmail.com"/>
+    <hyperlink ref="G83" r:id="rId10" display="mailto:lyanatorrecampo@gmail.com"/>
+    <hyperlink ref="G88" r:id="rId11" display="mailto:ljayme@yondu.com"/>
+    <hyperlink ref="G89" r:id="rId12" display="mailto:miiraaa14@gmail.com"/>
+    <hyperlink ref="G90" r:id="rId13" display="mailto:floriedelsanchez@gmail.com"/>
+    <hyperlink ref="G91" r:id="rId14" display="mailto:iamchristinelopez@yahoo.com"/>
+    <hyperlink ref="G92" r:id="rId15" display="mailto:donnatamayodlt@gmail.com"/>
+    <hyperlink ref="G94" r:id="rId16" display="mailto:jannachristina.liwanag@emerson.com"/>
+    <hyperlink ref="G95" r:id="rId17" display="mailto:antuazon@hrnetworkph.com"/>
+    <hyperlink ref="G96" r:id="rId18" display="mailto:kqxmc2mcmr@privaterelay.appleid.com"/>
+    <hyperlink ref="G98" r:id="rId19" display="mailto:sheanasunga@gmail.com"/>
+    <hyperlink ref="G99" r:id="rId20" display="mailto:gabatajohnmartin@gmail.com"/>
+    <hyperlink ref="G100" r:id="rId21" display="mailto:ncorpuz@enshored.com"/>
+    <hyperlink ref="G101" r:id="rId22" display="mailto:krystel.dimalibot@gmail.com"/>
+    <hyperlink ref="G102" r:id="rId23" display="mailto:alessandrian04@gmail.com"/>
+    <hyperlink ref="G103" r:id="rId24" display="mailto:jgrojas1208@gmail.com"/>
+    <hyperlink ref="G104" r:id="rId25" display="mailto:adrianejomeldupo.s@infosys.com"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" verticalDpi="300" r:id="rId26"/>
 </worksheet>
 </file>
--- a/documents/job-applications.xlsx
+++ b/documents/job-applications.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="622" uniqueCount="249">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="638" uniqueCount="255">
   <si>
     <t>company</t>
   </si>
@@ -766,6 +766,24 @@
   </si>
   <si>
     <t>WHR Global Consulting</t>
+  </si>
+  <si>
+    <t>Task Us</t>
+  </si>
+  <si>
+    <t>adaca</t>
+  </si>
+  <si>
+    <t>Jobslin</t>
+  </si>
+  <si>
+    <t>Jobsline</t>
+  </si>
+  <si>
+    <t>Blaseek</t>
+  </si>
+  <si>
+    <t>Five9</t>
   </si>
 </sst>
 </file>
@@ -866,10 +884,10 @@
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
@@ -1176,7 +1194,7 @@
   <sheetPr>
     <outlinePr summaryBelow="0"/>
   </sheetPr>
-  <dimension ref="A1:H145"/>
+  <dimension ref="A1:H149"/>
   <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="45.140625" style="2" bestFit="1" customWidth="1"/>
@@ -1981,10 +1999,10 @@
       <c r="D46" s="1" t="s">
         <v>107</v>
       </c>
-      <c r="G46" s="9" t="s">
+      <c r="G46" s="10" t="s">
         <v>108</v>
       </c>
-      <c r="H46" s="9"/>
+      <c r="H46" s="10"/>
     </row>
     <row r="47" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A47" s="1" t="s">
@@ -2038,10 +2056,10 @@
       <c r="D50" s="1" t="s">
         <v>116</v>
       </c>
-      <c r="G50" s="9" t="s">
+      <c r="G50" s="10" t="s">
         <v>115</v>
       </c>
-      <c r="H50" s="9"/>
+      <c r="H50" s="10"/>
     </row>
     <row r="51" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A51" s="1" t="s">
@@ -3289,7 +3307,7 @@
       <c r="D138" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="F138" s="10" t="s">
+      <c r="F138" s="9" t="s">
         <v>238</v>
       </c>
     </row>
@@ -3389,6 +3407,62 @@
       </c>
       <c r="E145" s="2" t="s">
         <v>247</v>
+      </c>
+    </row>
+    <row r="146" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A146" s="2" t="s">
+        <v>249</v>
+      </c>
+      <c r="C146" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="D146" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="E146" s="2" t="s">
+        <v>247</v>
+      </c>
+    </row>
+    <row r="147" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A147" s="2" t="s">
+        <v>250</v>
+      </c>
+      <c r="C147" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="D147" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="E147" s="2" t="s">
+        <v>251</v>
+      </c>
+    </row>
+    <row r="148" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A148" s="2" t="s">
+        <v>253</v>
+      </c>
+      <c r="C148" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="D148" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="E148" s="2" t="s">
+        <v>252</v>
+      </c>
+    </row>
+    <row r="149" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A149" s="2" t="s">
+        <v>254</v>
+      </c>
+      <c r="C149" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="D149" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="E149" s="2" t="s">
+        <v>88</v>
       </c>
     </row>
   </sheetData>

--- a/documents/job-applications.xlsx
+++ b/documents/job-applications.xlsx
@@ -1,15 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="6" lowestEdited="5" rupBuild="14420"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="28429"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Projects\To Github\auto-job-app-sender\documents\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\LARRY\Documents\Scripts\auto-job-app-sender\documents\"/>
     </mc:Choice>
   </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4974CE46-2A42-4A05-A0C4-7AA10DFA7F15}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-105" yWindow="-105" windowWidth="23250" windowHeight="12450"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -19,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="638" uniqueCount="255">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="715" uniqueCount="279">
   <si>
     <t>company</t>
   </si>
@@ -784,13 +785,85 @@
   </si>
   <si>
     <t>Five9</t>
+  </si>
+  <si>
+    <t>Teleperformance</t>
+  </si>
+  <si>
+    <t>aylaranang@gmail.com</t>
+  </si>
+  <si>
+    <t>09173128516 | 09985625835</t>
+  </si>
+  <si>
+    <t>katrinaleyva28@gmail.com</t>
+  </si>
+  <si>
+    <t>Almana</t>
+  </si>
+  <si>
+    <t>ajesta.mitche@yahoo.com</t>
+  </si>
+  <si>
+    <t>geapafin@gmail.com</t>
+  </si>
+  <si>
+    <t>Athena</t>
+  </si>
+  <si>
+    <t>acesabelle@gmail.com</t>
+  </si>
+  <si>
+    <t>jmstopcio@gmail.com</t>
+  </si>
+  <si>
+    <t>zamudiomjoyn@gmail.com</t>
+  </si>
+  <si>
+    <t>Acclime</t>
+  </si>
+  <si>
+    <t>Ubiquity</t>
+  </si>
+  <si>
+    <t>effflores0987@gmail.com</t>
+  </si>
+  <si>
+    <t>Avanade</t>
+  </si>
+  <si>
+    <t>xfusion.io</t>
+  </si>
+  <si>
+    <t>Indeed</t>
+  </si>
+  <si>
+    <t>J-K Network Manpower Services</t>
+  </si>
+  <si>
+    <t>LuxeVision Consulting</t>
+  </si>
+  <si>
+    <t>Bravissimo Resourcing, Inc.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Credit Corp Group Limited </t>
+  </si>
+  <si>
+    <t>Corporate Executive Search, Inc.</t>
+  </si>
+  <si>
+    <t>QIAGEN Manila, Inc.</t>
+  </si>
+  <si>
+    <t>Stark Asia Solutions, Inc.</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
-  <fonts count="6" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="8" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -833,6 +906,17 @@
       <name val="Arial"/>
       <family val="2"/>
     </font>
+    <font>
+      <sz val="8"/>
+      <color theme="1"/>
+      <name val="Segoe UI"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF2D2D2D"/>
+      <name val="Helvetica"/>
+    </font>
   </fonts>
   <fills count="3">
     <fill>
@@ -868,7 +952,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="11">
+  <cellXfs count="13">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
@@ -888,6 +972,8 @@
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
@@ -1190,25 +1276,25 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <sheetPr>
     <outlinePr summaryBelow="0"/>
   </sheetPr>
-  <dimension ref="A1:H149"/>
-  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <dimension ref="A1:H166"/>
+  <sheetFormatPr defaultColWidth="8.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="45.140625" style="2" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="36.42578125" style="2" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="46.42578125" style="2" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="25.42578125" style="2" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="13.5703125" style="2" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="53.140625" style="2" customWidth="1"/>
-    <col min="7" max="7" width="22.7109375" style="2" customWidth="1"/>
-    <col min="8" max="8" width="23.42578125" style="2" customWidth="1"/>
-    <col min="9" max="16384" width="8.85546875" style="2"/>
+    <col min="1" max="1" width="45.109375" style="2" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="36.44140625" style="2" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="46.44140625" style="2" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="25.44140625" style="2" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="13.5546875" style="2" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="53.109375" style="2" customWidth="1"/>
+    <col min="7" max="7" width="22.6640625" style="2" customWidth="1"/>
+    <col min="8" max="8" width="23.44140625" style="2" customWidth="1"/>
+    <col min="9" max="16384" width="8.88671875" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:8" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1234,7 +1320,7 @@
         <v>176</v>
       </c>
     </row>
-    <row r="2" spans="1:8" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:8" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="1" t="s">
         <v>6</v>
       </c>
@@ -1252,7 +1338,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="3" spans="1:8" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:8" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3" s="1" t="s">
         <v>6</v>
       </c>
@@ -1270,7 +1356,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="4" spans="1:8" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:8" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A4" s="1" t="s">
         <v>13</v>
       </c>
@@ -1286,7 +1372,7 @@
       </c>
       <c r="F4" s="1"/>
     </row>
-    <row r="5" spans="1:8" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:8" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A5" s="1" t="s">
         <v>15</v>
       </c>
@@ -1304,7 +1390,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="6" spans="1:8" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:8" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A6" s="1" t="s">
         <v>17</v>
       </c>
@@ -1320,7 +1406,7 @@
       </c>
       <c r="F6" s="1"/>
     </row>
-    <row r="7" spans="1:8" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:8" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A7" s="1" t="s">
         <v>17</v>
       </c>
@@ -1336,7 +1422,7 @@
       </c>
       <c r="F7" s="1"/>
     </row>
-    <row r="8" spans="1:8" ht="33" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:8" ht="33" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A8" s="1" t="s">
         <v>20</v>
       </c>
@@ -1354,7 +1440,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="9" spans="1:8" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:8" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A9" s="1" t="s">
         <v>20</v>
       </c>
@@ -1372,7 +1458,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="10" spans="1:8" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:8" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A10" s="1" t="s">
         <v>24</v>
       </c>
@@ -1390,7 +1476,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="11" spans="1:8" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:8" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A11" s="1" t="s">
         <v>28</v>
       </c>
@@ -1408,7 +1494,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="12" spans="1:8" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:8" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A12" s="1" t="s">
         <v>31</v>
       </c>
@@ -1426,7 +1512,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="13" spans="1:8" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:8" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A13" s="1" t="s">
         <v>34</v>
       </c>
@@ -1444,7 +1530,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="14" spans="1:8" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:8" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A14" s="1" t="s">
         <v>37</v>
       </c>
@@ -1462,7 +1548,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="15" spans="1:8" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:8" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A15" s="1" t="s">
         <v>37</v>
       </c>
@@ -1480,7 +1566,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="16" spans="1:8" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:8" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A16" s="1" t="s">
         <v>42</v>
       </c>
@@ -1498,7 +1584,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="17" spans="1:6" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:6" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A17" s="1" t="s">
         <v>45</v>
       </c>
@@ -1516,7 +1602,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="18" spans="1:6" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:6" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A18" s="3" t="s">
         <v>48</v>
       </c>
@@ -1534,7 +1620,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="19" spans="1:6" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:6" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A19" s="1" t="s">
         <v>51</v>
       </c>
@@ -1552,7 +1638,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="20" spans="1:6" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:6" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A20" s="1" t="s">
         <v>53</v>
       </c>
@@ -1570,7 +1656,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="21" spans="1:6" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:6" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A21" s="1" t="s">
         <v>57</v>
       </c>
@@ -1588,7 +1674,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="22" spans="1:6" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:6" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A22" s="1" t="s">
         <v>57</v>
       </c>
@@ -1606,7 +1692,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="23" spans="1:6" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:6" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A23" s="1" t="s">
         <v>57</v>
       </c>
@@ -1624,7 +1710,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="24" spans="1:6" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:6" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A24" s="1" t="s">
         <v>63</v>
       </c>
@@ -1642,7 +1728,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="25" spans="1:6" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:6" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A25" s="1" t="s">
         <v>66</v>
       </c>
@@ -1660,7 +1746,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="26" spans="1:6" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:6" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A26" s="1" t="s">
         <v>63</v>
       </c>
@@ -1678,7 +1764,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="27" spans="1:6" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:6" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A27" s="1" t="s">
         <v>63</v>
       </c>
@@ -1696,7 +1782,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="28" spans="1:6" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:6" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A28" s="1" t="s">
         <v>71</v>
       </c>
@@ -1714,7 +1800,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="29" spans="1:6" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:6" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A29" s="1" t="s">
         <v>74</v>
       </c>
@@ -1732,7 +1818,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="30" spans="1:6" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:6" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A30" s="1" t="s">
         <v>77</v>
       </c>
@@ -1752,7 +1838,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="31" spans="1:6" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:6" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A31" s="1" t="s">
         <v>77</v>
       </c>
@@ -1772,7 +1858,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="32" spans="1:6" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:6" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A32" s="1" t="s">
         <v>81</v>
       </c>
@@ -1789,7 +1875,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="33" spans="1:8" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:8" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A33" s="1" t="s">
         <v>84</v>
       </c>
@@ -1806,7 +1892,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="34" spans="1:8" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:8" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A34" s="1" t="s">
         <v>84</v>
       </c>
@@ -1820,7 +1906,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="35" spans="1:8" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:8" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A35" s="1" t="s">
         <v>87</v>
       </c>
@@ -1834,7 +1920,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="36" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A36" s="1" t="s">
         <v>89</v>
       </c>
@@ -1851,7 +1937,7 @@
         <v>92</v>
       </c>
     </row>
-    <row r="37" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A37" s="1" t="s">
         <v>93</v>
       </c>
@@ -1868,7 +1954,7 @@
         <v>94</v>
       </c>
     </row>
-    <row r="38" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A38" s="1" t="s">
         <v>95</v>
       </c>
@@ -1882,7 +1968,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="39" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A39" s="1" t="s">
         <v>96</v>
       </c>
@@ -1896,7 +1982,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="40" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A40" s="1" t="s">
         <v>97</v>
       </c>
@@ -1910,7 +1996,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="41" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A41" s="1" t="s">
         <v>98</v>
       </c>
@@ -1927,7 +2013,7 @@
         <v>99</v>
       </c>
     </row>
-    <row r="42" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A42" s="1" t="s">
         <v>100</v>
       </c>
@@ -1941,7 +2027,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="43" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A43" s="1" t="s">
         <v>101</v>
       </c>
@@ -1958,7 +2044,7 @@
         <v>103</v>
       </c>
     </row>
-    <row r="44" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A44" s="1" t="s">
         <v>101</v>
       </c>
@@ -1975,7 +2061,7 @@
         <v>103</v>
       </c>
     </row>
-    <row r="45" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A45" s="2" t="s">
         <v>105</v>
       </c>
@@ -1989,7 +2075,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="46" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A46" s="1" t="s">
         <v>106</v>
       </c>
@@ -2004,7 +2090,7 @@
       </c>
       <c r="H46" s="10"/>
     </row>
-    <row r="47" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A47" s="1" t="s">
         <v>110</v>
       </c>
@@ -2018,7 +2104,7 @@
         <v>109</v>
       </c>
     </row>
-    <row r="48" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A48" s="1" t="s">
         <v>111</v>
       </c>
@@ -2032,7 +2118,7 @@
         <v>112</v>
       </c>
     </row>
-    <row r="49" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A49" s="1" t="s">
         <v>114</v>
       </c>
@@ -2046,7 +2132,7 @@
         <v>113</v>
       </c>
     </row>
-    <row r="50" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A50" s="1" t="s">
         <v>117</v>
       </c>
@@ -2061,7 +2147,7 @@
       </c>
       <c r="H50" s="10"/>
     </row>
-    <row r="51" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A51" s="1" t="s">
         <v>120</v>
       </c>
@@ -2075,7 +2161,7 @@
         <v>118</v>
       </c>
     </row>
-    <row r="52" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A52" s="1" t="s">
         <v>120</v>
       </c>
@@ -2089,7 +2175,7 @@
         <v>119</v>
       </c>
     </row>
-    <row r="53" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A53" s="1" t="s">
         <v>57</v>
       </c>
@@ -2103,7 +2189,7 @@
         <v>121</v>
       </c>
     </row>
-    <row r="54" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A54" s="2" t="s">
         <v>122</v>
       </c>
@@ -2117,7 +2203,7 @@
         <v>123</v>
       </c>
     </row>
-    <row r="55" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A55" s="2" t="s">
         <v>124</v>
       </c>
@@ -2131,7 +2217,7 @@
         <v>123</v>
       </c>
     </row>
-    <row r="56" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A56" s="2" t="s">
         <v>125</v>
       </c>
@@ -2145,7 +2231,7 @@
         <v>123</v>
       </c>
     </row>
-    <row r="57" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A57" s="2" t="s">
         <v>127</v>
       </c>
@@ -2162,7 +2248,7 @@
         <v>128</v>
       </c>
     </row>
-    <row r="58" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A58" s="2" t="s">
         <v>129</v>
       </c>
@@ -2176,7 +2262,7 @@
         <v>123</v>
       </c>
     </row>
-    <row r="59" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A59" s="2" t="s">
         <v>130</v>
       </c>
@@ -2190,7 +2276,7 @@
         <v>123</v>
       </c>
     </row>
-    <row r="60" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A60" s="2" t="s">
         <v>131</v>
       </c>
@@ -2204,7 +2290,7 @@
         <v>123</v>
       </c>
     </row>
-    <row r="61" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A61" s="2" t="s">
         <v>133</v>
       </c>
@@ -2221,7 +2307,7 @@
         <v>134</v>
       </c>
     </row>
-    <row r="62" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A62" s="2" t="s">
         <v>131</v>
       </c>
@@ -2235,7 +2321,7 @@
         <v>123</v>
       </c>
     </row>
-    <row r="63" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A63" s="2" t="s">
         <v>98</v>
       </c>
@@ -2252,7 +2338,7 @@
         <v>135</v>
       </c>
     </row>
-    <row r="64" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A64" s="2" t="s">
         <v>136</v>
       </c>
@@ -2266,7 +2352,7 @@
         <v>123</v>
       </c>
     </row>
-    <row r="65" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A65" s="2" t="s">
         <v>137</v>
       </c>
@@ -2280,7 +2366,7 @@
         <v>123</v>
       </c>
     </row>
-    <row r="66" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A66" s="2" t="s">
         <v>138</v>
       </c>
@@ -2294,7 +2380,7 @@
         <v>123</v>
       </c>
     </row>
-    <row r="67" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A67" s="2" t="s">
         <v>122</v>
       </c>
@@ -2308,7 +2394,7 @@
         <v>123</v>
       </c>
     </row>
-    <row r="68" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A68" s="2" t="s">
         <v>141</v>
       </c>
@@ -2322,7 +2408,7 @@
         <v>123</v>
       </c>
     </row>
-    <row r="69" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A69" s="2" t="s">
         <v>143</v>
       </c>
@@ -2336,7 +2422,7 @@
         <v>123</v>
       </c>
     </row>
-    <row r="70" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A70" s="2" t="s">
         <v>130</v>
       </c>
@@ -2350,7 +2436,7 @@
         <v>123</v>
       </c>
     </row>
-    <row r="71" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A71" s="2" t="s">
         <v>146</v>
       </c>
@@ -2364,7 +2450,7 @@
         <v>123</v>
       </c>
     </row>
-    <row r="72" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A72" s="2" t="s">
         <v>148</v>
       </c>
@@ -2378,7 +2464,7 @@
         <v>149</v>
       </c>
     </row>
-    <row r="73" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A73" s="2" t="s">
         <v>150</v>
       </c>
@@ -2392,7 +2478,7 @@
         <v>151</v>
       </c>
     </row>
-    <row r="74" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A74" s="2" t="s">
         <v>153</v>
       </c>
@@ -2406,7 +2492,7 @@
         <v>152</v>
       </c>
     </row>
-    <row r="75" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A75" s="2" t="s">
         <v>111</v>
       </c>
@@ -2423,7 +2509,7 @@
         <v>112</v>
       </c>
     </row>
-    <row r="76" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A76" s="2" t="s">
         <v>157</v>
       </c>
@@ -2437,7 +2523,7 @@
         <v>156</v>
       </c>
     </row>
-    <row r="77" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A77" s="2" t="s">
         <v>159</v>
       </c>
@@ -2451,7 +2537,7 @@
         <v>158</v>
       </c>
     </row>
-    <row r="78" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A78" s="2" t="s">
         <v>160</v>
       </c>
@@ -2465,7 +2551,7 @@
         <v>161</v>
       </c>
     </row>
-    <row r="79" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="79" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A79" s="2" t="s">
         <v>163</v>
       </c>
@@ -2479,7 +2565,7 @@
         <v>162</v>
       </c>
     </row>
-    <row r="80" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="80" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A80" t="s">
         <v>165</v>
       </c>
@@ -2493,7 +2579,7 @@
         <v>164</v>
       </c>
     </row>
-    <row r="81" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="81" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A81" s="2" t="s">
         <v>167</v>
       </c>
@@ -2507,7 +2593,7 @@
         <v>166</v>
       </c>
     </row>
-    <row r="82" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="82" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A82" s="2" t="s">
         <v>138</v>
       </c>
@@ -2521,7 +2607,7 @@
         <v>168</v>
       </c>
     </row>
-    <row r="83" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="83" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A83" s="2" t="s">
         <v>159</v>
       </c>
@@ -2535,7 +2621,7 @@
         <v>169</v>
       </c>
     </row>
-    <row r="84" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="84" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A84" s="2" t="s">
         <v>170</v>
       </c>
@@ -2549,7 +2635,7 @@
         <v>123</v>
       </c>
     </row>
-    <row r="85" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="85" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A85" s="2" t="s">
         <v>171</v>
       </c>
@@ -2563,7 +2649,7 @@
         <v>123</v>
       </c>
     </row>
-    <row r="86" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="86" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A86" s="2" t="s">
         <v>129</v>
       </c>
@@ -2577,7 +2663,7 @@
         <v>123</v>
       </c>
     </row>
-    <row r="87" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="87" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A87" s="2" t="s">
         <v>122</v>
       </c>
@@ -2591,7 +2677,7 @@
         <v>123</v>
       </c>
     </row>
-    <row r="88" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="88" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A88" s="2" t="s">
         <v>172</v>
       </c>
@@ -2605,7 +2691,7 @@
         <v>173</v>
       </c>
     </row>
-    <row r="89" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="89" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A89" s="2" t="s">
         <v>177</v>
       </c>
@@ -2622,7 +2708,7 @@
         <v>9394791981</v>
       </c>
     </row>
-    <row r="90" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="90" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A90" s="2" t="s">
         <v>57</v>
       </c>
@@ -2636,7 +2722,7 @@
         <v>178</v>
       </c>
     </row>
-    <row r="91" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="91" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A91" s="2" t="s">
         <v>143</v>
       </c>
@@ -2653,7 +2739,7 @@
         <v>9270345867</v>
       </c>
     </row>
-    <row r="92" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="92" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A92" s="2" t="s">
         <v>180</v>
       </c>
@@ -2670,7 +2756,7 @@
         <v>639923742220</v>
       </c>
     </row>
-    <row r="93" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="93" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A93" s="2" t="s">
         <v>182</v>
       </c>
@@ -2684,7 +2770,7 @@
         <v>183</v>
       </c>
     </row>
-    <row r="94" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="94" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A94" s="2" t="s">
         <v>131</v>
       </c>
@@ -2698,7 +2784,7 @@
         <v>184</v>
       </c>
     </row>
-    <row r="95" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="95" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A95" s="2" t="s">
         <v>186</v>
       </c>
@@ -2712,7 +2798,7 @@
         <v>185</v>
       </c>
     </row>
-    <row r="96" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="96" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A96" s="2" t="s">
         <v>187</v>
       </c>
@@ -2726,7 +2812,7 @@
         <v>188</v>
       </c>
     </row>
-    <row r="97" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="97" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A97" s="2" t="s">
         <v>189</v>
       </c>
@@ -2737,7 +2823,7 @@
         <v>107</v>
       </c>
     </row>
-    <row r="98" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="98" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A98" s="2" t="s">
         <v>57</v>
       </c>
@@ -2751,7 +2837,7 @@
         <v>190</v>
       </c>
     </row>
-    <row r="99" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="99" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A99" s="2" t="s">
         <v>192</v>
       </c>
@@ -2765,7 +2851,7 @@
         <v>191</v>
       </c>
     </row>
-    <row r="100" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="100" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A100" s="2" t="s">
         <v>194</v>
       </c>
@@ -2782,7 +2868,7 @@
         <v>9695979091</v>
       </c>
     </row>
-    <row r="101" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="101" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A101" s="2" t="s">
         <v>196</v>
       </c>
@@ -2796,7 +2882,7 @@
         <v>195</v>
       </c>
     </row>
-    <row r="102" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="102" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A102" s="2" t="s">
         <v>198</v>
       </c>
@@ -2810,7 +2896,7 @@
         <v>197</v>
       </c>
     </row>
-    <row r="103" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="103" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A103" s="2" t="s">
         <v>192</v>
       </c>
@@ -2824,7 +2910,7 @@
         <v>199</v>
       </c>
     </row>
-    <row r="104" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="104" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A104" s="2" t="s">
         <v>200</v>
       </c>
@@ -2838,7 +2924,7 @@
         <v>201</v>
       </c>
     </row>
-    <row r="105" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="105" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A105" s="2" t="s">
         <v>202</v>
       </c>
@@ -2849,7 +2935,7 @@
         <v>107</v>
       </c>
     </row>
-    <row r="106" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="106" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A106" s="2" t="s">
         <v>203</v>
       </c>
@@ -2863,7 +2949,7 @@
         <v>123</v>
       </c>
     </row>
-    <row r="107" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="107" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A107" s="2" t="s">
         <v>98</v>
       </c>
@@ -2877,7 +2963,7 @@
         <v>123</v>
       </c>
     </row>
-    <row r="108" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="108" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A108" s="2" t="s">
         <v>206</v>
       </c>
@@ -2891,7 +2977,7 @@
         <v>123</v>
       </c>
     </row>
-    <row r="109" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="109" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A109" s="2" t="s">
         <v>206</v>
       </c>
@@ -2905,7 +2991,7 @@
         <v>123</v>
       </c>
     </row>
-    <row r="110" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="110" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A110" s="2" t="s">
         <v>209</v>
       </c>
@@ -2919,7 +3005,7 @@
         <v>123</v>
       </c>
     </row>
-    <row r="111" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="111" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A111" s="2" t="s">
         <v>211</v>
       </c>
@@ -2933,7 +3019,7 @@
         <v>123</v>
       </c>
     </row>
-    <row r="112" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="112" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A112" s="2" t="s">
         <v>137</v>
       </c>
@@ -2947,7 +3033,7 @@
         <v>123</v>
       </c>
     </row>
-    <row r="113" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="113" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A113" s="2" t="s">
         <v>212</v>
       </c>
@@ -2961,7 +3047,7 @@
         <v>123</v>
       </c>
     </row>
-    <row r="114" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="114" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A114" s="2" t="s">
         <v>213</v>
       </c>
@@ -2975,7 +3061,7 @@
         <v>123</v>
       </c>
     </row>
-    <row r="115" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="115" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A115" s="2" t="s">
         <v>215</v>
       </c>
@@ -2989,7 +3075,7 @@
         <v>123</v>
       </c>
     </row>
-    <row r="116" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="116" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A116" s="2" t="s">
         <v>216</v>
       </c>
@@ -3003,7 +3089,7 @@
         <v>123</v>
       </c>
     </row>
-    <row r="117" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="117" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A117" s="2" t="s">
         <v>211</v>
       </c>
@@ -3017,7 +3103,7 @@
         <v>123</v>
       </c>
     </row>
-    <row r="118" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="118" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A118" s="2" t="s">
         <v>170</v>
       </c>
@@ -3034,7 +3120,7 @@
         <v>219</v>
       </c>
     </row>
-    <row r="119" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="119" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A119" s="2" t="s">
         <v>220</v>
       </c>
@@ -3048,7 +3134,7 @@
         <v>123</v>
       </c>
     </row>
-    <row r="120" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="120" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A120" s="2" t="s">
         <v>221</v>
       </c>
@@ -3062,7 +3148,7 @@
         <v>123</v>
       </c>
     </row>
-    <row r="121" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="121" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A121" s="2" t="s">
         <v>223</v>
       </c>
@@ -3076,7 +3162,7 @@
         <v>123</v>
       </c>
     </row>
-    <row r="122" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="122" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A122" s="2" t="s">
         <v>224</v>
       </c>
@@ -3090,7 +3176,7 @@
         <v>123</v>
       </c>
     </row>
-    <row r="123" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="123" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A123" s="2" t="s">
         <v>98</v>
       </c>
@@ -3104,7 +3190,7 @@
         <v>123</v>
       </c>
     </row>
-    <row r="124" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="124" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A124" s="2" t="s">
         <v>213</v>
       </c>
@@ -3118,7 +3204,7 @@
         <v>123</v>
       </c>
     </row>
-    <row r="125" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="125" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A125" s="2" t="s">
         <v>226</v>
       </c>
@@ -3132,7 +3218,7 @@
         <v>123</v>
       </c>
     </row>
-    <row r="126" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="126" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A126" s="2" t="s">
         <v>141</v>
       </c>
@@ -3146,7 +3232,7 @@
         <v>123</v>
       </c>
     </row>
-    <row r="127" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="127" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A127" s="2" t="s">
         <v>227</v>
       </c>
@@ -3160,7 +3246,7 @@
         <v>123</v>
       </c>
     </row>
-    <row r="128" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="128" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A128" s="2" t="s">
         <v>163</v>
       </c>
@@ -3174,7 +3260,7 @@
         <v>123</v>
       </c>
     </row>
-    <row r="129" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="129" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A129" s="2" t="s">
         <v>228</v>
       </c>
@@ -3188,7 +3274,7 @@
         <v>123</v>
       </c>
     </row>
-    <row r="130" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="130" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A130" s="2" t="s">
         <v>229</v>
       </c>
@@ -3202,7 +3288,7 @@
         <v>123</v>
       </c>
     </row>
-    <row r="131" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="131" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A131" s="2" t="s">
         <v>230</v>
       </c>
@@ -3216,7 +3302,7 @@
         <v>123</v>
       </c>
     </row>
-    <row r="132" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="132" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A132" s="2" t="s">
         <v>231</v>
       </c>
@@ -3230,7 +3316,7 @@
         <v>123</v>
       </c>
     </row>
-    <row r="133" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="133" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A133" s="2" t="s">
         <v>233</v>
       </c>
@@ -3244,7 +3330,7 @@
         <v>123</v>
       </c>
     </row>
-    <row r="134" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="134" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A134" s="2" t="s">
         <v>234</v>
       </c>
@@ -3258,7 +3344,7 @@
         <v>123</v>
       </c>
     </row>
-    <row r="135" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="135" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A135" s="2" t="s">
         <v>235</v>
       </c>
@@ -3272,7 +3358,7 @@
         <v>123</v>
       </c>
     </row>
-    <row r="136" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="136" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A136" s="2" t="s">
         <v>236</v>
       </c>
@@ -3280,13 +3366,13 @@
         <v>69</v>
       </c>
       <c r="D136" s="2" t="s">
-        <v>12</v>
+        <v>26</v>
       </c>
       <c r="E136" s="2" t="s">
         <v>123</v>
       </c>
     </row>
-    <row r="137" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="137" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A137" s="2" t="s">
         <v>237</v>
       </c>
@@ -3297,7 +3383,7 @@
         <v>107</v>
       </c>
     </row>
-    <row r="138" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="138" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A138" s="2" t="s">
         <v>239</v>
       </c>
@@ -3307,11 +3393,11 @@
       <c r="D138" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="F138" s="9" t="s">
+      <c r="G138" s="9" t="s">
         <v>238</v>
       </c>
     </row>
-    <row r="139" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="139" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A139" s="2" t="s">
         <v>240</v>
       </c>
@@ -3321,11 +3407,11 @@
       <c r="D139" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="F139" s="2" t="s">
+      <c r="G139" s="2" t="s">
         <v>241</v>
       </c>
     </row>
-    <row r="140" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="140" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A140" s="2" t="s">
         <v>242</v>
       </c>
@@ -3335,11 +3421,11 @@
       <c r="D140" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="F140" s="2" t="s">
+      <c r="G140" s="2" t="s">
         <v>243</v>
       </c>
     </row>
-    <row r="141" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="141" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A141" s="2" t="s">
         <v>37</v>
       </c>
@@ -3353,7 +3439,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="142" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="142" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A142" s="2" t="s">
         <v>244</v>
       </c>
@@ -3367,7 +3453,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="143" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="143" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A143" s="2" t="s">
         <v>245</v>
       </c>
@@ -3381,7 +3467,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="144" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="144" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A144" s="2" t="s">
         <v>246</v>
       </c>
@@ -3395,7 +3481,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="145" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="145" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A145" s="2" t="s">
         <v>248</v>
       </c>
@@ -3409,7 +3495,7 @@
         <v>247</v>
       </c>
     </row>
-    <row r="146" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="146" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A146" s="2" t="s">
         <v>249</v>
       </c>
@@ -3423,7 +3509,7 @@
         <v>247</v>
       </c>
     </row>
-    <row r="147" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="147" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A147" s="2" t="s">
         <v>250</v>
       </c>
@@ -3437,7 +3523,7 @@
         <v>251</v>
       </c>
     </row>
-    <row r="148" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="148" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A148" s="2" t="s">
         <v>253</v>
       </c>
@@ -3451,7 +3537,7 @@
         <v>252</v>
       </c>
     </row>
-    <row r="149" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="149" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A149" s="2" t="s">
         <v>254</v>
       </c>
@@ -3463,6 +3549,289 @@
       </c>
       <c r="E149" s="2" t="s">
         <v>88</v>
+      </c>
+    </row>
+    <row r="150" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A150" s="2" t="s">
+        <v>255</v>
+      </c>
+      <c r="C150" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="D150" s="2" t="s">
+        <v>107</v>
+      </c>
+      <c r="E150" s="2" t="s">
+        <v>123</v>
+      </c>
+      <c r="G150" s="5" t="s">
+        <v>256</v>
+      </c>
+      <c r="H150" s="11" t="s">
+        <v>257</v>
+      </c>
+    </row>
+    <row r="151" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A151" s="2" t="s">
+        <v>259</v>
+      </c>
+      <c r="C151" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="D151" s="2" t="s">
+        <v>107</v>
+      </c>
+      <c r="E151" s="2" t="s">
+        <v>123</v>
+      </c>
+      <c r="G151" s="5" t="s">
+        <v>258</v>
+      </c>
+      <c r="H151" s="11">
+        <v>9499601153</v>
+      </c>
+    </row>
+    <row r="152" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A152" s="2" t="s">
+        <v>163</v>
+      </c>
+      <c r="C152" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="D152" s="2" t="s">
+        <v>107</v>
+      </c>
+      <c r="E152" s="2" t="s">
+        <v>123</v>
+      </c>
+      <c r="G152" s="5" t="s">
+        <v>260</v>
+      </c>
+    </row>
+    <row r="153" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A153" s="2" t="s">
+        <v>262</v>
+      </c>
+      <c r="C153" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="D153" s="2" t="s">
+        <v>107</v>
+      </c>
+      <c r="E153" s="2" t="s">
+        <v>123</v>
+      </c>
+      <c r="G153" s="5" t="s">
+        <v>261</v>
+      </c>
+      <c r="H153" s="11">
+        <v>9155285209</v>
+      </c>
+    </row>
+    <row r="154" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A154" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="C154" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="D154" s="2" t="s">
+        <v>107</v>
+      </c>
+      <c r="E154" s="2" t="s">
+        <v>123</v>
+      </c>
+      <c r="G154" s="5" t="s">
+        <v>263</v>
+      </c>
+      <c r="H154" s="11">
+        <v>9479868804</v>
+      </c>
+    </row>
+    <row r="155" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A155" s="2" t="s">
+        <v>266</v>
+      </c>
+      <c r="C155" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="D155" s="2" t="s">
+        <v>107</v>
+      </c>
+      <c r="E155" s="2" t="s">
+        <v>123</v>
+      </c>
+      <c r="G155" s="5" t="s">
+        <v>264</v>
+      </c>
+      <c r="H155" s="11">
+        <v>9393224106</v>
+      </c>
+    </row>
+    <row r="156" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A156" s="2" t="s">
+        <v>267</v>
+      </c>
+      <c r="C156" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="D156" s="2" t="s">
+        <v>107</v>
+      </c>
+      <c r="E156" s="2" t="s">
+        <v>123</v>
+      </c>
+      <c r="G156" s="5" t="s">
+        <v>265</v>
+      </c>
+      <c r="H156" s="11">
+        <v>9164259033</v>
+      </c>
+    </row>
+    <row r="157" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A157" s="2" t="s">
+        <v>163</v>
+      </c>
+      <c r="C157" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="D157" s="2" t="s">
+        <v>107</v>
+      </c>
+      <c r="E157" s="2" t="s">
+        <v>123</v>
+      </c>
+      <c r="G157" s="5" t="s">
+        <v>268</v>
+      </c>
+      <c r="H157" s="11">
+        <v>9957467792</v>
+      </c>
+    </row>
+    <row r="158" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A158" s="2" t="s">
+        <v>269</v>
+      </c>
+      <c r="C158" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="D158" s="2" t="s">
+        <v>107</v>
+      </c>
+      <c r="E158" s="2" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="159" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A159" s="2" t="s">
+        <v>270</v>
+      </c>
+      <c r="C159" s="2" t="s">
+        <v>67</v>
+      </c>
+      <c r="D159" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="E159" s="2" t="s">
+        <v>271</v>
+      </c>
+    </row>
+    <row r="160" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A160" s="12" t="s">
+        <v>272</v>
+      </c>
+      <c r="C160" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="D160" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="E160" s="2" t="s">
+        <v>271</v>
+      </c>
+    </row>
+    <row r="161" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A161" s="2" t="s">
+        <v>273</v>
+      </c>
+      <c r="C161" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="D161" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="E161" s="2" t="s">
+        <v>271</v>
+      </c>
+    </row>
+    <row r="162" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A162" s="2" t="s">
+        <v>274</v>
+      </c>
+      <c r="C162" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="D162" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="E162" s="2" t="s">
+        <v>271</v>
+      </c>
+    </row>
+    <row r="163" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A163" s="2" t="s">
+        <v>275</v>
+      </c>
+      <c r="C163" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="D163" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="E163" s="2" t="s">
+        <v>271</v>
+      </c>
+    </row>
+    <row r="164" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A164" s="2" t="s">
+        <v>276</v>
+      </c>
+      <c r="C164" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="D164" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="E164" s="2" t="s">
+        <v>271</v>
+      </c>
+    </row>
+    <row r="165" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A165" s="2" t="s">
+        <v>277</v>
+      </c>
+      <c r="C165" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="D165" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="E165" s="2" t="s">
+        <v>271</v>
+      </c>
+    </row>
+    <row r="166" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A166" s="2" t="s">
+        <v>278</v>
+      </c>
+      <c r="C166" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="D166" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="E166" s="2" t="s">
+        <v>271</v>
       </c>
     </row>
   </sheetData>
@@ -3471,33 +3840,41 @@
     <mergeCell ref="G50:H50"/>
   </mergeCells>
   <hyperlinks>
-    <hyperlink ref="G51" r:id="rId1" display="mailto:angeliqu.misa@vxi.com"/>
-    <hyperlink ref="G53" r:id="rId2" display="mailto:daniella.mae.m.bisda@accenture.com"/>
-    <hyperlink ref="F75" r:id="rId3"/>
-    <hyperlink ref="G76" r:id="rId4" display="mailto:vcvisda@unionbankph.com"/>
-    <hyperlink ref="G77" r:id="rId5" display="mailto:mhelbert.paredes17@gmail.com"/>
-    <hyperlink ref="G78" r:id="rId6" display="mailto:maricvid@amazon.com"/>
-    <hyperlink ref="G79" r:id="rId7" display="mailto:ryan.rivera@telusinternational.com"/>
-    <hyperlink ref="G80" r:id="rId8" display="mailto:060290remfelguillenabelandres@gmail.com"/>
-    <hyperlink ref="G82" r:id="rId9" display="mailto:aprilchristine024@gmail.com"/>
-    <hyperlink ref="G83" r:id="rId10" display="mailto:lyanatorrecampo@gmail.com"/>
-    <hyperlink ref="G88" r:id="rId11" display="mailto:ljayme@yondu.com"/>
-    <hyperlink ref="G89" r:id="rId12" display="mailto:miiraaa14@gmail.com"/>
-    <hyperlink ref="G90" r:id="rId13" display="mailto:floriedelsanchez@gmail.com"/>
-    <hyperlink ref="G91" r:id="rId14" display="mailto:iamchristinelopez@yahoo.com"/>
-    <hyperlink ref="G92" r:id="rId15" display="mailto:donnatamayodlt@gmail.com"/>
-    <hyperlink ref="G94" r:id="rId16" display="mailto:jannachristina.liwanag@emerson.com"/>
-    <hyperlink ref="G95" r:id="rId17" display="mailto:antuazon@hrnetworkph.com"/>
-    <hyperlink ref="G96" r:id="rId18" display="mailto:kqxmc2mcmr@privaterelay.appleid.com"/>
-    <hyperlink ref="G98" r:id="rId19" display="mailto:sheanasunga@gmail.com"/>
-    <hyperlink ref="G99" r:id="rId20" display="mailto:gabatajohnmartin@gmail.com"/>
-    <hyperlink ref="G100" r:id="rId21" display="mailto:ncorpuz@enshored.com"/>
-    <hyperlink ref="G101" r:id="rId22" display="mailto:krystel.dimalibot@gmail.com"/>
-    <hyperlink ref="G102" r:id="rId23" display="mailto:alessandrian04@gmail.com"/>
-    <hyperlink ref="G103" r:id="rId24" display="mailto:jgrojas1208@gmail.com"/>
-    <hyperlink ref="G104" r:id="rId25" display="mailto:adrianejomeldupo.s@infosys.com"/>
+    <hyperlink ref="G51" r:id="rId1" display="mailto:angeliqu.misa@vxi.com" xr:uid="{00000000-0004-0000-0000-000000000000}"/>
+    <hyperlink ref="G53" r:id="rId2" display="mailto:daniella.mae.m.bisda@accenture.com" xr:uid="{00000000-0004-0000-0000-000001000000}"/>
+    <hyperlink ref="F75" r:id="rId3" xr:uid="{00000000-0004-0000-0000-000002000000}"/>
+    <hyperlink ref="G76" r:id="rId4" display="mailto:vcvisda@unionbankph.com" xr:uid="{00000000-0004-0000-0000-000003000000}"/>
+    <hyperlink ref="G77" r:id="rId5" display="mailto:mhelbert.paredes17@gmail.com" xr:uid="{00000000-0004-0000-0000-000004000000}"/>
+    <hyperlink ref="G78" r:id="rId6" display="mailto:maricvid@amazon.com" xr:uid="{00000000-0004-0000-0000-000005000000}"/>
+    <hyperlink ref="G79" r:id="rId7" display="mailto:ryan.rivera@telusinternational.com" xr:uid="{00000000-0004-0000-0000-000006000000}"/>
+    <hyperlink ref="G80" r:id="rId8" display="mailto:060290remfelguillenabelandres@gmail.com" xr:uid="{00000000-0004-0000-0000-000007000000}"/>
+    <hyperlink ref="G82" r:id="rId9" display="mailto:aprilchristine024@gmail.com" xr:uid="{00000000-0004-0000-0000-000008000000}"/>
+    <hyperlink ref="G83" r:id="rId10" display="mailto:lyanatorrecampo@gmail.com" xr:uid="{00000000-0004-0000-0000-000009000000}"/>
+    <hyperlink ref="G88" r:id="rId11" display="mailto:ljayme@yondu.com" xr:uid="{00000000-0004-0000-0000-00000A000000}"/>
+    <hyperlink ref="G89" r:id="rId12" display="mailto:miiraaa14@gmail.com" xr:uid="{00000000-0004-0000-0000-00000B000000}"/>
+    <hyperlink ref="G90" r:id="rId13" display="mailto:floriedelsanchez@gmail.com" xr:uid="{00000000-0004-0000-0000-00000C000000}"/>
+    <hyperlink ref="G91" r:id="rId14" display="mailto:iamchristinelopez@yahoo.com" xr:uid="{00000000-0004-0000-0000-00000D000000}"/>
+    <hyperlink ref="G92" r:id="rId15" display="mailto:donnatamayodlt@gmail.com" xr:uid="{00000000-0004-0000-0000-00000E000000}"/>
+    <hyperlink ref="G94" r:id="rId16" display="mailto:jannachristina.liwanag@emerson.com" xr:uid="{00000000-0004-0000-0000-00000F000000}"/>
+    <hyperlink ref="G95" r:id="rId17" display="mailto:antuazon@hrnetworkph.com" xr:uid="{00000000-0004-0000-0000-000010000000}"/>
+    <hyperlink ref="G96" r:id="rId18" display="mailto:kqxmc2mcmr@privaterelay.appleid.com" xr:uid="{00000000-0004-0000-0000-000011000000}"/>
+    <hyperlink ref="G98" r:id="rId19" display="mailto:sheanasunga@gmail.com" xr:uid="{00000000-0004-0000-0000-000012000000}"/>
+    <hyperlink ref="G99" r:id="rId20" display="mailto:gabatajohnmartin@gmail.com" xr:uid="{00000000-0004-0000-0000-000013000000}"/>
+    <hyperlink ref="G100" r:id="rId21" display="mailto:ncorpuz@enshored.com" xr:uid="{00000000-0004-0000-0000-000014000000}"/>
+    <hyperlink ref="G101" r:id="rId22" display="mailto:krystel.dimalibot@gmail.com" xr:uid="{00000000-0004-0000-0000-000015000000}"/>
+    <hyperlink ref="G102" r:id="rId23" display="mailto:alessandrian04@gmail.com" xr:uid="{00000000-0004-0000-0000-000016000000}"/>
+    <hyperlink ref="G103" r:id="rId24" display="mailto:jgrojas1208@gmail.com" xr:uid="{00000000-0004-0000-0000-000017000000}"/>
+    <hyperlink ref="G104" r:id="rId25" display="mailto:adrianejomeldupo.s@infosys.com" xr:uid="{00000000-0004-0000-0000-000018000000}"/>
+    <hyperlink ref="G150" r:id="rId26" display="mailto:aylaranang@gmail.com" xr:uid="{03572F30-386B-49BA-A886-117B536266DF}"/>
+    <hyperlink ref="G151" r:id="rId27" display="mailto:katrinaleyva28@gmail.com" xr:uid="{D6A725AD-054A-453D-A985-069C06E714F0}"/>
+    <hyperlink ref="G152" r:id="rId28" display="mailto:ajesta.mitche@yahoo.com" xr:uid="{281F7134-C26D-4B20-A18D-4055C242B6E6}"/>
+    <hyperlink ref="G153" r:id="rId29" display="mailto:geapafin@gmail.com" xr:uid="{640CF582-AEBF-422D-BE4E-F436C6CEB398}"/>
+    <hyperlink ref="G154" r:id="rId30" display="mailto:acesabelle@gmail.com" xr:uid="{3CB07AAB-5119-45D0-9500-6E15D6B9F480}"/>
+    <hyperlink ref="G155" r:id="rId31" display="mailto:jmstopcio@gmail.com" xr:uid="{AA8AD871-D894-4A86-9600-415D9BC3EA56}"/>
+    <hyperlink ref="G156" r:id="rId32" display="mailto:zamudiomjoyn@gmail.com" xr:uid="{DADB82FB-1728-471A-88BB-96CD5ABD84A7}"/>
+    <hyperlink ref="G157" r:id="rId33" display="mailto:effflores0987@gmail.com" xr:uid="{0894C386-DBD9-469D-BDAF-EE06C1BC2454}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" verticalDpi="300" r:id="rId26"/>
+  <pageSetup orientation="portrait" verticalDpi="300" r:id="rId34"/>
 </worksheet>
 </file>
--- a/documents/job-applications.xlsx
+++ b/documents/job-applications.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\LARRY\Documents\Scripts\auto-job-app-sender\documents\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4974CE46-2A42-4A05-A0C4-7AA10DFA7F15}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8864CEE0-489A-49D5-86F0-739EDAE97211}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="715" uniqueCount="279">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="777" uniqueCount="303">
   <si>
     <t>company</t>
   </si>
@@ -857,13 +857,85 @@
   </si>
   <si>
     <t>Stark Asia Solutions, Inc.</t>
+  </si>
+  <si>
+    <t>Security Bank Corporation</t>
+  </si>
+  <si>
+    <t>medinaeunice1293@gmail.com</t>
+  </si>
+  <si>
+    <t>dioquino.jennifer@yahoo.com</t>
+  </si>
+  <si>
+    <t>+639999610236 (Mobile)</t>
+  </si>
+  <si>
+    <t>Outsource Accelerator</t>
+  </si>
+  <si>
+    <t>9benema@ph.ibm.com</t>
+  </si>
+  <si>
+    <t>IBM</t>
+  </si>
+  <si>
+    <t>TTEC</t>
+  </si>
+  <si>
+    <t>pauloggutierrez@gmail.com</t>
+  </si>
+  <si>
+    <t>09763632509 (Work)</t>
+  </si>
+  <si>
+    <t>shekinahgraceliwanag@gmail.com</t>
+  </si>
+  <si>
+    <t>Integrated OS</t>
+  </si>
+  <si>
+    <t>himongalaelle@gmail.com</t>
+  </si>
+  <si>
+    <t>Afni, Inc.</t>
+  </si>
+  <si>
+    <t>+639603823696 (Work)</t>
+  </si>
+  <si>
+    <t>Intellipro</t>
+  </si>
+  <si>
+    <t>aylaa.hugo@gmail.com</t>
+  </si>
+  <si>
+    <t>adrianevalderrama@gmail.com</t>
+  </si>
+  <si>
+    <t>Dynamic Careers International Services</t>
+  </si>
+  <si>
+    <t>gabrieljannatricia@gmail.com</t>
+  </si>
+  <si>
+    <t>Aquire BPO</t>
+  </si>
+  <si>
+    <t>emacupang@gmail.com</t>
+  </si>
+  <si>
+    <t>engelbert.acefortin@gmail.com</t>
+  </si>
+  <si>
+    <t>Pro Integrate</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="8" x14ac:knownFonts="1">
+  <fonts count="7" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -903,19 +975,16 @@
     <font>
       <sz val="11"/>
       <color rgb="FF222222"/>
-      <name val="Arial"/>
+      <name val="Calibri"/>
       <family val="2"/>
-    </font>
-    <font>
-      <sz val="8"/>
-      <color theme="1"/>
-      <name val="Segoe UI"/>
-      <family val="2"/>
+      <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
       <color rgb="FF2D2D2D"/>
-      <name val="Helvetica"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="3">
@@ -952,7 +1021,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="13">
+  <cellXfs count="15">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
@@ -963,17 +1032,21 @@
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
@@ -1280,7 +1353,7 @@
   <sheetPr>
     <outlinePr summaryBelow="0"/>
   </sheetPr>
-  <dimension ref="A1:H166"/>
+  <dimension ref="A1:H178"/>
   <sheetFormatPr defaultColWidth="8.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="45.109375" style="2" bestFit="1" customWidth="1"/>
@@ -2085,10 +2158,10 @@
       <c r="D46" s="1" t="s">
         <v>107</v>
       </c>
-      <c r="G46" s="10" t="s">
+      <c r="G46" s="8" t="s">
         <v>108</v>
       </c>
-      <c r="H46" s="10"/>
+      <c r="H46" s="8"/>
     </row>
     <row r="47" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A47" s="1" t="s">
@@ -2142,10 +2215,10 @@
       <c r="D50" s="1" t="s">
         <v>116</v>
       </c>
-      <c r="G50" s="10" t="s">
+      <c r="G50" s="8" t="s">
         <v>115</v>
       </c>
-      <c r="H50" s="10"/>
+      <c r="H50" s="8"/>
     </row>
     <row r="51" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A51" s="1" t="s">
@@ -2502,7 +2575,7 @@
       <c r="D75" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="F75" s="5" t="s">
+      <c r="F75" s="9" t="s">
         <v>155</v>
       </c>
       <c r="G75" s="2" t="s">
@@ -2519,7 +2592,7 @@
       <c r="D76" s="2" t="s">
         <v>107</v>
       </c>
-      <c r="G76" s="5" t="s">
+      <c r="G76" s="9" t="s">
         <v>156</v>
       </c>
     </row>
@@ -2533,7 +2606,7 @@
       <c r="D77" s="2" t="s">
         <v>107</v>
       </c>
-      <c r="G77" s="6" t="s">
+      <c r="G77" s="10" t="s">
         <v>158</v>
       </c>
     </row>
@@ -2547,7 +2620,7 @@
       <c r="D78" s="2" t="s">
         <v>107</v>
       </c>
-      <c r="G78" s="5" t="s">
+      <c r="G78" s="9" t="s">
         <v>161</v>
       </c>
     </row>
@@ -2561,12 +2634,12 @@
       <c r="D79" s="2" t="s">
         <v>107</v>
       </c>
-      <c r="G79" s="5" t="s">
+      <c r="G79" s="9" t="s">
         <v>162</v>
       </c>
     </row>
     <row r="80" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A80" t="s">
+      <c r="A80" s="11" t="s">
         <v>165</v>
       </c>
       <c r="C80" s="2" t="s">
@@ -2575,7 +2648,7 @@
       <c r="D80" s="2" t="s">
         <v>107</v>
       </c>
-      <c r="G80" s="5" t="s">
+      <c r="G80" s="9" t="s">
         <v>164</v>
       </c>
     </row>
@@ -2589,7 +2662,7 @@
       <c r="D81" s="2" t="s">
         <v>107</v>
       </c>
-      <c r="G81" s="7" t="s">
+      <c r="G81" s="6" t="s">
         <v>166</v>
       </c>
     </row>
@@ -2603,7 +2676,7 @@
       <c r="D82" s="2" t="s">
         <v>107</v>
       </c>
-      <c r="G82" s="5" t="s">
+      <c r="G82" s="9" t="s">
         <v>168</v>
       </c>
     </row>
@@ -2617,7 +2690,7 @@
       <c r="D83" s="2" t="s">
         <v>107</v>
       </c>
-      <c r="G83" s="5" t="s">
+      <c r="G83" s="9" t="s">
         <v>169</v>
       </c>
     </row>
@@ -2687,7 +2760,7 @@
       <c r="D88" s="2" t="s">
         <v>107</v>
       </c>
-      <c r="G88" s="5" t="s">
+      <c r="G88" s="9" t="s">
         <v>173</v>
       </c>
     </row>
@@ -2701,10 +2774,10 @@
       <c r="D89" s="2" t="s">
         <v>107</v>
       </c>
-      <c r="G89" s="5" t="s">
+      <c r="G89" s="9" t="s">
         <v>174</v>
       </c>
-      <c r="H89">
+      <c r="H89" s="11">
         <v>9394791981</v>
       </c>
     </row>
@@ -2718,7 +2791,7 @@
       <c r="D90" s="2" t="s">
         <v>107</v>
       </c>
-      <c r="G90" s="5" t="s">
+      <c r="G90" s="9" t="s">
         <v>178</v>
       </c>
     </row>
@@ -2732,10 +2805,10 @@
       <c r="D91" s="2" t="s">
         <v>107</v>
       </c>
-      <c r="G91" s="5" t="s">
+      <c r="G91" s="9" t="s">
         <v>179</v>
       </c>
-      <c r="H91">
+      <c r="H91" s="11">
         <v>9270345867</v>
       </c>
     </row>
@@ -2749,10 +2822,10 @@
       <c r="D92" s="2" t="s">
         <v>107</v>
       </c>
-      <c r="G92" s="5" t="s">
+      <c r="G92" s="9" t="s">
         <v>181</v>
       </c>
-      <c r="H92">
+      <c r="H92" s="11">
         <v>639923742220</v>
       </c>
     </row>
@@ -2766,7 +2839,7 @@
       <c r="D93" s="2" t="s">
         <v>107</v>
       </c>
-      <c r="G93" s="8" t="s">
+      <c r="G93" s="7" t="s">
         <v>183</v>
       </c>
     </row>
@@ -2780,7 +2853,7 @@
       <c r="D94" s="2" t="s">
         <v>107</v>
       </c>
-      <c r="G94" s="5" t="s">
+      <c r="G94" s="9" t="s">
         <v>184</v>
       </c>
     </row>
@@ -2794,7 +2867,7 @@
       <c r="D95" s="2" t="s">
         <v>107</v>
       </c>
-      <c r="G95" s="5" t="s">
+      <c r="G95" s="9" t="s">
         <v>185</v>
       </c>
     </row>
@@ -2808,7 +2881,7 @@
       <c r="D96" s="2" t="s">
         <v>107</v>
       </c>
-      <c r="G96" s="5" t="s">
+      <c r="G96" s="9" t="s">
         <v>188</v>
       </c>
     </row>
@@ -2833,7 +2906,7 @@
       <c r="D98" s="2" t="s">
         <v>107</v>
       </c>
-      <c r="G98" s="5" t="s">
+      <c r="G98" s="9" t="s">
         <v>190</v>
       </c>
     </row>
@@ -2847,7 +2920,7 @@
       <c r="D99" s="2" t="s">
         <v>107</v>
       </c>
-      <c r="G99" s="5" t="s">
+      <c r="G99" s="9" t="s">
         <v>191</v>
       </c>
     </row>
@@ -2861,10 +2934,10 @@
       <c r="D100" s="2" t="s">
         <v>107</v>
       </c>
-      <c r="G100" s="5" t="s">
+      <c r="G100" s="9" t="s">
         <v>193</v>
       </c>
-      <c r="H100">
+      <c r="H100" s="11">
         <v>9695979091</v>
       </c>
     </row>
@@ -2878,7 +2951,7 @@
       <c r="D101" s="2" t="s">
         <v>107</v>
       </c>
-      <c r="G101" s="5" t="s">
+      <c r="G101" s="9" t="s">
         <v>195</v>
       </c>
     </row>
@@ -2892,7 +2965,7 @@
       <c r="D102" s="2" t="s">
         <v>107</v>
       </c>
-      <c r="G102" s="5" t="s">
+      <c r="G102" s="9" t="s">
         <v>197</v>
       </c>
     </row>
@@ -2906,7 +2979,7 @@
       <c r="D103" s="2" t="s">
         <v>107</v>
       </c>
-      <c r="G103" s="5" t="s">
+      <c r="G103" s="9" t="s">
         <v>199</v>
       </c>
     </row>
@@ -2920,7 +2993,7 @@
       <c r="D104" s="2" t="s">
         <v>107</v>
       </c>
-      <c r="G104" s="5" t="s">
+      <c r="G104" s="9" t="s">
         <v>201</v>
       </c>
     </row>
@@ -3393,7 +3466,7 @@
       <c r="D138" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="G138" s="9" t="s">
+      <c r="G138" s="12" t="s">
         <v>238</v>
       </c>
     </row>
@@ -3564,7 +3637,7 @@
       <c r="E150" s="2" t="s">
         <v>123</v>
       </c>
-      <c r="G150" s="5" t="s">
+      <c r="G150" s="9" t="s">
         <v>256</v>
       </c>
       <c r="H150" s="11" t="s">
@@ -3584,7 +3657,7 @@
       <c r="E151" s="2" t="s">
         <v>123</v>
       </c>
-      <c r="G151" s="5" t="s">
+      <c r="G151" s="9" t="s">
         <v>258</v>
       </c>
       <c r="H151" s="11">
@@ -3604,7 +3677,7 @@
       <c r="E152" s="2" t="s">
         <v>123</v>
       </c>
-      <c r="G152" s="5" t="s">
+      <c r="G152" s="9" t="s">
         <v>260</v>
       </c>
     </row>
@@ -3621,7 +3694,7 @@
       <c r="E153" s="2" t="s">
         <v>123</v>
       </c>
-      <c r="G153" s="5" t="s">
+      <c r="G153" s="9" t="s">
         <v>261</v>
       </c>
       <c r="H153" s="11">
@@ -3641,7 +3714,7 @@
       <c r="E154" s="2" t="s">
         <v>123</v>
       </c>
-      <c r="G154" s="5" t="s">
+      <c r="G154" s="9" t="s">
         <v>263</v>
       </c>
       <c r="H154" s="11">
@@ -3661,7 +3734,7 @@
       <c r="E155" s="2" t="s">
         <v>123</v>
       </c>
-      <c r="G155" s="5" t="s">
+      <c r="G155" s="9" t="s">
         <v>264</v>
       </c>
       <c r="H155" s="11">
@@ -3681,7 +3754,7 @@
       <c r="E156" s="2" t="s">
         <v>123</v>
       </c>
-      <c r="G156" s="5" t="s">
+      <c r="G156" s="9" t="s">
         <v>265</v>
       </c>
       <c r="H156" s="11">
@@ -3701,7 +3774,7 @@
       <c r="E157" s="2" t="s">
         <v>123</v>
       </c>
-      <c r="G157" s="5" t="s">
+      <c r="G157" s="9" t="s">
         <v>268</v>
       </c>
       <c r="H157" s="11">
@@ -3737,7 +3810,7 @@
       </c>
     </row>
     <row r="160" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A160" s="12" t="s">
+      <c r="A160" s="13" t="s">
         <v>272</v>
       </c>
       <c r="C160" s="2" t="s">
@@ -3750,7 +3823,7 @@
         <v>271</v>
       </c>
     </row>
-    <row r="161" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="161" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A161" s="2" t="s">
         <v>273</v>
       </c>
@@ -3764,7 +3837,7 @@
         <v>271</v>
       </c>
     </row>
-    <row r="162" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="162" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A162" s="2" t="s">
         <v>274</v>
       </c>
@@ -3778,7 +3851,7 @@
         <v>271</v>
       </c>
     </row>
-    <row r="163" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="163" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A163" s="2" t="s">
         <v>275</v>
       </c>
@@ -3792,7 +3865,7 @@
         <v>271</v>
       </c>
     </row>
-    <row r="164" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="164" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A164" s="2" t="s">
         <v>276</v>
       </c>
@@ -3806,7 +3879,7 @@
         <v>271</v>
       </c>
     </row>
-    <row r="165" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="165" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A165" s="2" t="s">
         <v>277</v>
       </c>
@@ -3820,7 +3893,7 @@
         <v>271</v>
       </c>
     </row>
-    <row r="166" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="166" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A166" s="2" t="s">
         <v>278</v>
       </c>
@@ -3832,6 +3905,219 @@
       </c>
       <c r="E166" s="2" t="s">
         <v>271</v>
+      </c>
+    </row>
+    <row r="167" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A167" s="2" t="s">
+        <v>279</v>
+      </c>
+      <c r="C167" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="D167" s="2" t="s">
+        <v>107</v>
+      </c>
+      <c r="E167" s="2" t="s">
+        <v>123</v>
+      </c>
+      <c r="G167" s="9" t="s">
+        <v>280</v>
+      </c>
+    </row>
+    <row r="168" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A168" s="2" t="s">
+        <v>283</v>
+      </c>
+      <c r="C168" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="D168" s="2" t="s">
+        <v>107</v>
+      </c>
+      <c r="E168" s="2" t="s">
+        <v>123</v>
+      </c>
+      <c r="G168" s="9" t="s">
+        <v>281</v>
+      </c>
+      <c r="H168" s="14" t="s">
+        <v>282</v>
+      </c>
+    </row>
+    <row r="169" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A169" s="2" t="s">
+        <v>285</v>
+      </c>
+      <c r="C169" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="D169" s="2" t="s">
+        <v>107</v>
+      </c>
+      <c r="E169" s="2" t="s">
+        <v>123</v>
+      </c>
+      <c r="G169" s="9" t="s">
+        <v>284</v>
+      </c>
+    </row>
+    <row r="170" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A170" s="2" t="s">
+        <v>286</v>
+      </c>
+      <c r="C170" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="D170" s="2" t="s">
+        <v>107</v>
+      </c>
+      <c r="E170" s="2" t="s">
+        <v>123</v>
+      </c>
+      <c r="G170" s="9" t="s">
+        <v>287</v>
+      </c>
+    </row>
+    <row r="171" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A171" s="2" t="s">
+        <v>290</v>
+      </c>
+      <c r="C171" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="D171" s="2" t="s">
+        <v>107</v>
+      </c>
+      <c r="E171" s="2" t="s">
+        <v>123</v>
+      </c>
+      <c r="G171" s="9" t="s">
+        <v>289</v>
+      </c>
+      <c r="H171" s="14" t="s">
+        <v>288</v>
+      </c>
+    </row>
+    <row r="172" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A172" s="2" t="s">
+        <v>292</v>
+      </c>
+      <c r="C172" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="D172" s="2" t="s">
+        <v>107</v>
+      </c>
+      <c r="E172" s="2" t="s">
+        <v>123</v>
+      </c>
+      <c r="G172" s="9" t="s">
+        <v>291</v>
+      </c>
+      <c r="H172" s="14">
+        <v>9239962602</v>
+      </c>
+    </row>
+    <row r="173" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A173" s="2" t="s">
+        <v>294</v>
+      </c>
+      <c r="C173" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="D173" s="2" t="s">
+        <v>107</v>
+      </c>
+      <c r="E173" s="2" t="s">
+        <v>123</v>
+      </c>
+      <c r="H173" s="14" t="s">
+        <v>293</v>
+      </c>
+    </row>
+    <row r="174" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A174" s="2" t="s">
+        <v>285</v>
+      </c>
+      <c r="C174" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="D174" s="2" t="s">
+        <v>107</v>
+      </c>
+      <c r="E174" s="2" t="s">
+        <v>123</v>
+      </c>
+      <c r="G174" s="9" t="s">
+        <v>295</v>
+      </c>
+    </row>
+    <row r="175" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A175" s="11" t="s">
+        <v>297</v>
+      </c>
+      <c r="C175" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="D175" s="2" t="s">
+        <v>107</v>
+      </c>
+      <c r="E175" s="2" t="s">
+        <v>123</v>
+      </c>
+      <c r="G175" s="9" t="s">
+        <v>296</v>
+      </c>
+    </row>
+    <row r="176" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A176" s="2" t="s">
+        <v>299</v>
+      </c>
+      <c r="C176" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="D176" s="2" t="s">
+        <v>107</v>
+      </c>
+      <c r="E176" s="2" t="s">
+        <v>123</v>
+      </c>
+      <c r="G176" s="5" t="s">
+        <v>298</v>
+      </c>
+    </row>
+    <row r="177" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A177" s="2" t="s">
+        <v>138</v>
+      </c>
+      <c r="C177" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="D177" s="2" t="s">
+        <v>107</v>
+      </c>
+      <c r="E177" s="2" t="s">
+        <v>123</v>
+      </c>
+      <c r="G177" s="5" t="s">
+        <v>300</v>
+      </c>
+    </row>
+    <row r="178" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A178" s="2" t="s">
+        <v>302</v>
+      </c>
+      <c r="C178" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="D178" s="2" t="s">
+        <v>107</v>
+      </c>
+      <c r="E178" s="2" t="s">
+        <v>123</v>
+      </c>
+      <c r="G178" s="5" t="s">
+        <v>301</v>
       </c>
     </row>
   </sheetData>
@@ -3873,8 +4159,19 @@
     <hyperlink ref="G155" r:id="rId31" display="mailto:jmstopcio@gmail.com" xr:uid="{AA8AD871-D894-4A86-9600-415D9BC3EA56}"/>
     <hyperlink ref="G156" r:id="rId32" display="mailto:zamudiomjoyn@gmail.com" xr:uid="{DADB82FB-1728-471A-88BB-96CD5ABD84A7}"/>
     <hyperlink ref="G157" r:id="rId33" display="mailto:effflores0987@gmail.com" xr:uid="{0894C386-DBD9-469D-BDAF-EE06C1BC2454}"/>
+    <hyperlink ref="G167" r:id="rId34" display="mailto:medinaeunice1293@gmail.com" xr:uid="{57CF7B2C-B71F-42D1-A9FB-6DFFBC6F6EC5}"/>
+    <hyperlink ref="G168" r:id="rId35" display="mailto:dioquino.jennifer@yahoo.com" xr:uid="{4D21E71A-F23D-4475-A8FE-AE6A064871F5}"/>
+    <hyperlink ref="G169" r:id="rId36" display="mailto:9benema@ph.ibm.com" xr:uid="{1F0B0803-7D58-4AAC-9E32-5877F6D061C8}"/>
+    <hyperlink ref="G170" r:id="rId37" display="mailto:pauloggutierrez@gmail.com" xr:uid="{FE68110B-4FE5-46BF-91E3-32742FA74988}"/>
+    <hyperlink ref="G171" r:id="rId38" display="mailto:shekinahgraceliwanag@gmail.com" xr:uid="{C0125AA5-0D1C-420C-81DF-04F068B38AC3}"/>
+    <hyperlink ref="G172" r:id="rId39" display="mailto:himongalaelle@gmail.com" xr:uid="{5998E394-113C-482C-9127-2BF26A5B59B8}"/>
+    <hyperlink ref="G174" r:id="rId40" display="mailto:aylaa.hugo@gmail.com" xr:uid="{BAF3F7F6-F3AF-47A9-9B9A-F625C3B6E1A7}"/>
+    <hyperlink ref="G175" r:id="rId41" display="mailto:adrianevalderrama@gmail.com" xr:uid="{A94C6215-87C6-4ACC-8E31-37897D5BD037}"/>
+    <hyperlink ref="G176" r:id="rId42" display="mailto:gabrieljannatricia@gmail.com" xr:uid="{D28F0502-1BFE-495F-9F24-2D80A162CCA5}"/>
+    <hyperlink ref="G177" r:id="rId43" display="mailto:emacupang@gmail.com" xr:uid="{2ED56E74-9E8B-4C1F-80CF-B2224CF02624}"/>
+    <hyperlink ref="G178" r:id="rId44" display="mailto:engelbert.acefortin@gmail.com" xr:uid="{25F2B952-2A6A-40BD-89B1-951CDCA3955D}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" verticalDpi="300" r:id="rId34"/>
+  <pageSetup orientation="portrait" verticalDpi="300" r:id="rId45"/>
 </worksheet>
 </file>
--- a/documents/job-applications.xlsx
+++ b/documents/job-applications.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="28429"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="28526"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\LARRY\Documents\Scripts\auto-job-app-sender\documents\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8864CEE0-489A-49D5-86F0-739EDAE97211}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7C100EA7-BA30-43C0-8D48-36FBF299BC5C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,14 +20,11 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="777" uniqueCount="303">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="785" uniqueCount="306">
   <si>
     <t>company</t>
   </si>
   <si>
-    <t>email</t>
-  </si>
-  <si>
     <t>role</t>
   </si>
   <si>
@@ -929,13 +926,25 @@
   </si>
   <si>
     <t>Pro Integrate</t>
+  </si>
+  <si>
+    <t>Octal Philippines, Inc.</t>
+  </si>
+  <si>
+    <t>Viber</t>
+  </si>
+  <si>
+    <t>service (basta anything that's IT consulting, Healthcare, Finance and tech, Morning shift, 9-5, in Makati, Quezon, or Taguig, 30000php base, ok sa akin)</t>
+  </si>
+  <si>
+    <t>Lightweight Solutions</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="7" x14ac:knownFonts="1">
+  <fonts count="8" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -982,6 +991,13 @@
     <font>
       <sz val="11"/>
       <color rgb="FF2D2D2D"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -1034,18 +1050,20 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -1353,7 +1371,7 @@
   <sheetPr>
     <outlinePr summaryBelow="0"/>
   </sheetPr>
-  <dimension ref="A1:H178"/>
+  <dimension ref="A1:H180"/>
   <sheetFormatPr defaultColWidth="8.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="45.109375" style="2" bestFit="1" customWidth="1"/>
@@ -1372,2752 +1390,2780 @@
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
+        <v>304</v>
+      </c>
+      <c r="C1" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="D1" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="E1" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="F1" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="1" t="s">
-        <v>5</v>
-      </c>
       <c r="G1" s="1" t="s">
+        <v>174</v>
+      </c>
+      <c r="H1" s="2" t="s">
         <v>175</v>
-      </c>
-      <c r="H1" s="2" t="s">
-        <v>176</v>
       </c>
     </row>
     <row r="2" spans="1:8" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="1" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B2" s="1"/>
       <c r="C2" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="D2" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="D2" s="1" t="s">
+      <c r="E2" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="E2" s="1" t="s">
+      <c r="F2" s="1" t="s">
         <v>9</v>
-      </c>
-      <c r="F2" s="1" t="s">
-        <v>10</v>
       </c>
     </row>
     <row r="3" spans="1:8" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3" s="1" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B3" s="1"/>
       <c r="C3" s="1" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="E3" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="F3" s="1" t="s">
         <v>9</v>
-      </c>
-      <c r="F3" s="1" t="s">
-        <v>10</v>
       </c>
     </row>
     <row r="4" spans="1:8" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A4" s="1" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B4" s="1"/>
       <c r="C4" s="1" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="F4" s="1"/>
     </row>
     <row r="5" spans="1:8" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A5" s="1" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B5" s="1"/>
       <c r="C5" s="1" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="E5" s="1" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="F5" s="1" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
     </row>
     <row r="6" spans="1:8" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A6" s="1" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B6" s="1"/>
       <c r="C6" s="1" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="E6" s="1" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="F6" s="1"/>
     </row>
     <row r="7" spans="1:8" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A7" s="1" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B7" s="1"/>
       <c r="C7" s="1" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="E7" s="1" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="F7" s="1"/>
     </row>
     <row r="8" spans="1:8" ht="33" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A8" s="1" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="B8" s="1"/>
       <c r="C8" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="D8" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="E8" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="F8" s="1" t="s">
         <v>21</v>
-      </c>
-      <c r="D8" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="E8" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="F8" s="1" t="s">
-        <v>22</v>
       </c>
     </row>
     <row r="9" spans="1:8" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A9" s="1" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="B9" s="1"/>
       <c r="C9" s="3" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="E9" s="1" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="F9" s="1" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="10" spans="1:8" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A10" s="1" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B10" s="1"/>
       <c r="C10" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="D10" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="D10" s="1" t="s">
+      <c r="E10" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="F10" s="1" t="s">
         <v>26</v>
-      </c>
-      <c r="E10" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="F10" s="1" t="s">
-        <v>27</v>
       </c>
     </row>
     <row r="11" spans="1:8" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A11" s="1" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="B11" s="1"/>
       <c r="C11" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="D11" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="E11" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="F11" s="1" t="s">
         <v>29</v>
-      </c>
-      <c r="D11" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="E11" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="F11" s="1" t="s">
-        <v>30</v>
       </c>
     </row>
     <row r="12" spans="1:8" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A12" s="1" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="B12" s="1"/>
       <c r="C12" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="D12" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="E12" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="F12" s="1" t="s">
         <v>32</v>
-      </c>
-      <c r="D12" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="E12" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="F12" s="1" t="s">
-        <v>33</v>
       </c>
     </row>
     <row r="13" spans="1:8" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A13" s="1" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B13" s="1"/>
       <c r="C13" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="D13" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="E13" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="F13" s="1" t="s">
         <v>35</v>
-      </c>
-      <c r="D13" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="E13" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="F13" s="1" t="s">
-        <v>36</v>
       </c>
     </row>
     <row r="14" spans="1:8" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A14" s="1" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="B14" s="1"/>
       <c r="C14" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="D14" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="E14" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="D14" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="E14" s="1" t="s">
+      <c r="F14" s="1" t="s">
         <v>39</v>
-      </c>
-      <c r="F14" s="1" t="s">
-        <v>40</v>
       </c>
     </row>
     <row r="15" spans="1:8" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A15" s="1" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="B15" s="1"/>
       <c r="C15" s="1" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="D15" s="1" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="E15" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="F15" s="1" t="s">
         <v>39</v>
-      </c>
-      <c r="F15" s="1" t="s">
-        <v>40</v>
       </c>
     </row>
     <row r="16" spans="1:8" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A16" s="1" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="B16" s="1"/>
       <c r="C16" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="D16" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="E16" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="F16" s="1" t="s">
         <v>43</v>
-      </c>
-      <c r="D16" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="E16" s="1" t="s">
-        <v>39</v>
-      </c>
-      <c r="F16" s="1" t="s">
-        <v>44</v>
       </c>
     </row>
     <row r="17" spans="1:6" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A17" s="1" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="B17" s="1"/>
       <c r="C17" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="D17" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="E17" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="F17" s="1" t="s">
         <v>46</v>
-      </c>
-      <c r="D17" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="E17" s="1" t="s">
-        <v>39</v>
-      </c>
-      <c r="F17" s="1" t="s">
-        <v>47</v>
       </c>
     </row>
     <row r="18" spans="1:6" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A18" s="3" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="B18" s="1"/>
       <c r="C18" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="D18" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="E18" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="F18" s="1" t="s">
         <v>49</v>
       </c>
-      <c r="D18" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="E18" s="1" t="s">
-        <v>39</v>
-      </c>
-      <c r="F18" s="1" t="s">
+    </row>
+    <row r="19" spans="1:6" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A19" s="12" t="s">
         <v>50</v>
-      </c>
-    </row>
-    <row r="19" spans="1:6" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A19" s="1" t="s">
-        <v>51</v>
       </c>
       <c r="B19" s="1"/>
       <c r="C19" s="1" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="D19" s="1" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="E19" s="1" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="F19" s="1" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
     </row>
     <row r="20" spans="1:6" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A20" s="1" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="B20" s="1"/>
       <c r="C20" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="D20" s="1" t="s">
         <v>54</v>
       </c>
-      <c r="D20" s="1" t="s">
+      <c r="E20" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="F20" s="1" t="s">
         <v>55</v>
-      </c>
-      <c r="E20" s="1" t="s">
-        <v>39</v>
-      </c>
-      <c r="F20" s="1" t="s">
-        <v>56</v>
       </c>
     </row>
     <row r="21" spans="1:6" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A21" s="1" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="B21" s="1"/>
       <c r="C21" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="D21" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="E21" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="F21" s="1" t="s">
         <v>58</v>
-      </c>
-      <c r="D21" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="E21" s="1" t="s">
-        <v>39</v>
-      </c>
-      <c r="F21" s="1" t="s">
-        <v>59</v>
       </c>
     </row>
     <row r="22" spans="1:6" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A22" s="1" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="B22" s="1"/>
       <c r="C22" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="D22" s="1" t="s">
         <v>60</v>
       </c>
-      <c r="D22" s="1" t="s">
-        <v>61</v>
-      </c>
       <c r="E22" s="1" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="F22" s="1" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
     </row>
     <row r="23" spans="1:6" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A23" s="1" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="B23" s="1"/>
       <c r="C23" s="1" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="D23" s="1" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="E23" s="1" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="F23" s="1" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
     </row>
     <row r="24" spans="1:6" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A24" s="1" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="B24" s="1"/>
       <c r="C24" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="D24" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="E24" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="F24" s="1" t="s">
         <v>64</v>
-      </c>
-      <c r="D24" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="E24" s="1" t="s">
-        <v>39</v>
-      </c>
-      <c r="F24" s="1" t="s">
-        <v>65</v>
       </c>
     </row>
     <row r="25" spans="1:6" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A25" s="1" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="B25" s="1"/>
       <c r="C25" s="1" t="s">
+        <v>66</v>
+      </c>
+      <c r="D25" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="E25" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="F25" s="1" t="s">
         <v>67</v>
-      </c>
-      <c r="D25" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="E25" s="1" t="s">
-        <v>39</v>
-      </c>
-      <c r="F25" s="1" t="s">
-        <v>68</v>
       </c>
     </row>
     <row r="26" spans="1:6" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A26" s="1" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="B26" s="1"/>
       <c r="C26" s="1" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="D26" s="1" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="E26" s="1" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="F26" s="1" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
     </row>
     <row r="27" spans="1:6" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A27" s="1" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="B27" s="1"/>
       <c r="C27" s="1" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="D27" s="1" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="E27" s="1" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="F27" s="1" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
     </row>
     <row r="28" spans="1:6" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A28" s="1" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="B28" s="1"/>
       <c r="C28" s="1" t="s">
+        <v>71</v>
+      </c>
+      <c r="D28" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="E28" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="F28" s="1" t="s">
         <v>72</v>
-      </c>
-      <c r="D28" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="E28" s="1" t="s">
-        <v>39</v>
-      </c>
-      <c r="F28" s="1" t="s">
-        <v>73</v>
       </c>
     </row>
     <row r="29" spans="1:6" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A29" s="1" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="B29" s="1"/>
       <c r="C29" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="D29" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="E29" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="F29" s="1" t="s">
         <v>75</v>
       </c>
-      <c r="D29" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="E29" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="F29" s="1" t="s">
+    </row>
+    <row r="30" spans="1:6" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A30" s="12" t="s">
         <v>76</v>
       </c>
-    </row>
-    <row r="30" spans="1:6" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A30" s="1" t="s">
+      <c r="B30" s="1" t="s">
         <v>77</v>
       </c>
-      <c r="B30" s="1" t="s">
+      <c r="C30" s="1" t="s">
+        <v>68</v>
+      </c>
+      <c r="D30" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="E30" s="1" t="s">
+        <v>76</v>
+      </c>
+      <c r="F30" s="1" t="s">
         <v>78</v>
-      </c>
-      <c r="C30" s="1" t="s">
-        <v>69</v>
-      </c>
-      <c r="D30" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="E30" s="1" t="s">
-        <v>77</v>
-      </c>
-      <c r="F30" s="1" t="s">
-        <v>79</v>
       </c>
     </row>
     <row r="31" spans="1:6" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A31" s="1" t="s">
+        <v>76</v>
+      </c>
+      <c r="B31" s="1" t="s">
         <v>77</v>
       </c>
-      <c r="B31" s="1" t="s">
+      <c r="C31" s="1" t="s">
+        <v>79</v>
+      </c>
+      <c r="D31" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="E31" s="1" t="s">
+        <v>76</v>
+      </c>
+      <c r="F31" s="1" t="s">
         <v>78</v>
-      </c>
-      <c r="C31" s="1" t="s">
-        <v>80</v>
-      </c>
-      <c r="D31" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="E31" s="1" t="s">
-        <v>77</v>
-      </c>
-      <c r="F31" s="1" t="s">
-        <v>79</v>
       </c>
     </row>
     <row r="32" spans="1:6" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A32" s="1" t="s">
+        <v>80</v>
+      </c>
+      <c r="C32" s="1" t="s">
         <v>81</v>
       </c>
-      <c r="C32" s="1" t="s">
+      <c r="D32" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="E32" s="1" t="s">
+        <v>80</v>
+      </c>
+      <c r="F32" s="2" t="s">
         <v>82</v>
-      </c>
-      <c r="D32" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="E32" s="1" t="s">
-        <v>81</v>
-      </c>
-      <c r="F32" s="2" t="s">
-        <v>83</v>
       </c>
     </row>
     <row r="33" spans="1:8" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A33" s="1" t="s">
+        <v>83</v>
+      </c>
+      <c r="C33" s="1" t="s">
+        <v>68</v>
+      </c>
+      <c r="D33" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="E33" s="1" t="s">
+        <v>83</v>
+      </c>
+      <c r="F33" s="2" t="s">
         <v>84</v>
-      </c>
-      <c r="C33" s="1" t="s">
-        <v>69</v>
-      </c>
-      <c r="D33" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="E33" s="1" t="s">
-        <v>84</v>
-      </c>
-      <c r="F33" s="2" t="s">
-        <v>85</v>
       </c>
     </row>
     <row r="34" spans="1:8" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A34" s="1" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="C34" s="1" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="D34" s="1" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="E34" s="1" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
     </row>
     <row r="35" spans="1:8" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A35" s="1" t="s">
+        <v>86</v>
+      </c>
+      <c r="C35" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="D35" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="E35" s="1" t="s">
         <v>87</v>
       </c>
-      <c r="C35" s="1" t="s">
-        <v>46</v>
-      </c>
-      <c r="D35" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="E35" s="1" t="s">
+    </row>
+    <row r="36" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A36" s="12" t="s">
         <v>88</v>
       </c>
-    </row>
-    <row r="36" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A36" s="1" t="s">
+      <c r="C36" s="1" t="s">
         <v>89</v>
       </c>
-      <c r="C36" s="1" t="s">
+      <c r="D36" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="E36" s="1" t="s">
         <v>90</v>
       </c>
-      <c r="D36" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="E36" s="1" t="s">
+      <c r="F36" s="2" t="s">
         <v>91</v>
       </c>
-      <c r="F36" s="2" t="s">
+    </row>
+    <row r="37" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A37" s="12" t="s">
         <v>92</v>
       </c>
-    </row>
-    <row r="37" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A37" s="1" t="s">
+      <c r="C37" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="D37" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="E37" s="1" t="s">
+        <v>90</v>
+      </c>
+      <c r="F37" s="2" t="s">
         <v>93</v>
-      </c>
-      <c r="C37" s="1" t="s">
-        <v>41</v>
-      </c>
-      <c r="D37" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="E37" s="1" t="s">
-        <v>91</v>
-      </c>
-      <c r="F37" s="2" t="s">
-        <v>94</v>
       </c>
     </row>
     <row r="38" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A38" s="1" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="C38" s="1" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="D38" s="1" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="E38" s="1" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
     </row>
     <row r="39" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A39" s="1" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="C39" s="1" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="D39" s="1" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="E39" s="1" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
     </row>
     <row r="40" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A40" s="1" t="s">
+        <v>96</v>
+      </c>
+      <c r="C40" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="D40" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="E40" s="1" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="41" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A41" s="12" t="s">
         <v>97</v>
       </c>
-      <c r="C40" s="1" t="s">
-        <v>41</v>
-      </c>
-      <c r="D40" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="E40" s="1" t="s">
-        <v>88</v>
-      </c>
-    </row>
-    <row r="41" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A41" s="1" t="s">
+      <c r="C41" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="D41" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="E41" s="1" t="s">
+        <v>87</v>
+      </c>
+      <c r="F41" s="2" t="s">
         <v>98</v>
       </c>
-      <c r="C41" s="1" t="s">
-        <v>41</v>
-      </c>
-      <c r="D41" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="E41" s="1" t="s">
-        <v>88</v>
-      </c>
-      <c r="F41" s="2" t="s">
+    </row>
+    <row r="42" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A42" s="12" t="s">
         <v>99</v>
       </c>
-    </row>
-    <row r="42" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A42" s="1" t="s">
+      <c r="C42" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="D42" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="E42" s="1" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="43" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A43" s="12" t="s">
         <v>100</v>
       </c>
-      <c r="C42" s="1" t="s">
-        <v>41</v>
-      </c>
-      <c r="D42" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="E42" s="1" t="s">
-        <v>88</v>
-      </c>
-    </row>
-    <row r="43" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A43" s="1" t="s">
+      <c r="C43" s="1" t="s">
         <v>101</v>
       </c>
-      <c r="C43" s="1" t="s">
+      <c r="D43" s="1" t="s">
+        <v>144</v>
+      </c>
+      <c r="E43" s="1" t="s">
+        <v>87</v>
+      </c>
+      <c r="F43" s="2" t="s">
         <v>102</v>
-      </c>
-      <c r="D43" s="1" t="s">
-        <v>145</v>
-      </c>
-      <c r="E43" s="1" t="s">
-        <v>88</v>
-      </c>
-      <c r="F43" s="2" t="s">
-        <v>103</v>
       </c>
     </row>
     <row r="44" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A44" s="1" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="C44" s="1" t="s">
+        <v>103</v>
+      </c>
+      <c r="D44" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="E44" s="1" t="s">
+        <v>87</v>
+      </c>
+      <c r="F44" s="2" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="45" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A45" s="13" t="s">
         <v>104</v>
       </c>
-      <c r="D44" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="E44" s="1" t="s">
-        <v>88</v>
-      </c>
-      <c r="F44" s="2" t="s">
-        <v>103</v>
-      </c>
-    </row>
-    <row r="45" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A45" s="2" t="s">
+      <c r="C45" s="1" t="s">
+        <v>68</v>
+      </c>
+      <c r="D45" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="E45" s="1" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="46" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A46" s="12" t="s">
         <v>105</v>
       </c>
-      <c r="C45" s="1" t="s">
-        <v>69</v>
-      </c>
-      <c r="D45" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="E45" s="1" t="s">
-        <v>88</v>
-      </c>
-    </row>
-    <row r="46" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A46" s="1" t="s">
-        <v>106</v>
-      </c>
       <c r="C46" s="1" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="D46" s="1" t="s">
+        <v>106</v>
+      </c>
+      <c r="G46" s="14" t="s">
         <v>107</v>
       </c>
-      <c r="G46" s="8" t="s">
-        <v>108</v>
-      </c>
-      <c r="H46" s="8"/>
+      <c r="H46" s="14"/>
     </row>
     <row r="47" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A47" s="1" t="s">
+        <v>109</v>
+      </c>
+      <c r="C47" s="1" t="s">
+        <v>68</v>
+      </c>
+      <c r="D47" s="1" t="s">
+        <v>106</v>
+      </c>
+      <c r="G47" s="2" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="48" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A48" s="12" t="s">
         <v>110</v>
       </c>
-      <c r="C47" s="1" t="s">
-        <v>69</v>
-      </c>
-      <c r="D47" s="1" t="s">
-        <v>107</v>
-      </c>
-      <c r="G47" s="2" t="s">
-        <v>109</v>
-      </c>
-    </row>
-    <row r="48" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A48" s="1" t="s">
+      <c r="C48" s="1" t="s">
+        <v>68</v>
+      </c>
+      <c r="D48" s="1" t="s">
+        <v>106</v>
+      </c>
+      <c r="G48" s="2" t="s">
         <v>111</v>
-      </c>
-      <c r="C48" s="1" t="s">
-        <v>69</v>
-      </c>
-      <c r="D48" s="1" t="s">
-        <v>107</v>
-      </c>
-      <c r="G48" s="2" t="s">
-        <v>112</v>
       </c>
     </row>
     <row r="49" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A49" s="1" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="C49" s="1" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="D49" s="1" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="G49" s="2" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
     </row>
     <row r="50" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A50" s="1" t="s">
+        <v>116</v>
+      </c>
+      <c r="C50" s="1" t="s">
+        <v>68</v>
+      </c>
+      <c r="D50" s="1" t="s">
+        <v>115</v>
+      </c>
+      <c r="G50" s="14" t="s">
+        <v>114</v>
+      </c>
+      <c r="H50" s="14"/>
+    </row>
+    <row r="51" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A51" s="12" t="s">
+        <v>119</v>
+      </c>
+      <c r="C51" s="1" t="s">
+        <v>68</v>
+      </c>
+      <c r="D51" s="1" t="s">
+        <v>106</v>
+      </c>
+      <c r="G51" s="4" t="s">
         <v>117</v>
-      </c>
-      <c r="C50" s="1" t="s">
-        <v>69</v>
-      </c>
-      <c r="D50" s="1" t="s">
-        <v>116</v>
-      </c>
-      <c r="G50" s="8" t="s">
-        <v>115</v>
-      </c>
-      <c r="H50" s="8"/>
-    </row>
-    <row r="51" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A51" s="1" t="s">
-        <v>120</v>
-      </c>
-      <c r="C51" s="1" t="s">
-        <v>69</v>
-      </c>
-      <c r="D51" s="1" t="s">
-        <v>107</v>
-      </c>
-      <c r="G51" s="4" t="s">
-        <v>118</v>
       </c>
     </row>
     <row r="52" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A52" s="1" t="s">
+        <v>119</v>
+      </c>
+      <c r="C52" s="1" t="s">
+        <v>68</v>
+      </c>
+      <c r="D52" s="1" t="s">
+        <v>106</v>
+      </c>
+      <c r="G52" s="2" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="53" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A53" s="12" t="s">
+        <v>56</v>
+      </c>
+      <c r="C53" s="1" t="s">
+        <v>68</v>
+      </c>
+      <c r="D53" s="1" t="s">
+        <v>106</v>
+      </c>
+      <c r="G53" s="4" t="s">
         <v>120</v>
       </c>
-      <c r="C52" s="1" t="s">
-        <v>69</v>
-      </c>
-      <c r="D52" s="1" t="s">
-        <v>107</v>
-      </c>
-      <c r="G52" s="2" t="s">
-        <v>119</v>
-      </c>
-    </row>
-    <row r="53" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A53" s="1" t="s">
-        <v>57</v>
-      </c>
-      <c r="C53" s="1" t="s">
-        <v>69</v>
-      </c>
-      <c r="D53" s="1" t="s">
-        <v>107</v>
-      </c>
-      <c r="G53" s="4" t="s">
+    </row>
+    <row r="54" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A54" s="13" t="s">
         <v>121</v>
       </c>
-    </row>
-    <row r="54" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A54" s="2" t="s">
-        <v>122</v>
-      </c>
       <c r="C54" s="2" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="D54" s="2" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="E54" s="2" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
     </row>
     <row r="55" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A55" s="2" t="s">
+        <v>123</v>
+      </c>
+      <c r="C55" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="D55" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="E55" s="2" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="56" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A56" s="13" t="s">
         <v>124</v>
       </c>
-      <c r="C55" s="2" t="s">
-        <v>69</v>
-      </c>
-      <c r="D55" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="E55" s="2" t="s">
-        <v>123</v>
-      </c>
-    </row>
-    <row r="56" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A56" s="2" t="s">
+      <c r="C56" s="2" t="s">
         <v>125</v>
       </c>
-      <c r="C56" s="2" t="s">
+      <c r="D56" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="E56" s="2" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="57" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A57" s="13" t="s">
         <v>126</v>
       </c>
-      <c r="D56" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="E56" s="2" t="s">
-        <v>123</v>
-      </c>
-    </row>
-    <row r="57" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A57" s="2" t="s">
+      <c r="C57" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="D57" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="E57" s="2" t="s">
+        <v>122</v>
+      </c>
+      <c r="F57" s="2" t="s">
         <v>127</v>
       </c>
-      <c r="C57" s="2" t="s">
-        <v>69</v>
-      </c>
-      <c r="D57" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="E57" s="2" t="s">
-        <v>123</v>
-      </c>
-      <c r="F57" s="2" t="s">
+    </row>
+    <row r="58" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A58" s="13" t="s">
         <v>128</v>
       </c>
-    </row>
-    <row r="58" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A58" s="2" t="s">
+      <c r="C58" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="D58" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="E58" s="2" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="59" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A59" s="13" t="s">
         <v>129</v>
       </c>
-      <c r="C58" s="2" t="s">
-        <v>69</v>
-      </c>
-      <c r="D58" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="E58" s="2" t="s">
-        <v>123</v>
-      </c>
-    </row>
-    <row r="59" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A59" s="2" t="s">
+      <c r="C59" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="D59" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="E59" s="2" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="60" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A60" s="13" t="s">
         <v>130</v>
       </c>
-      <c r="C59" s="2" t="s">
-        <v>46</v>
-      </c>
-      <c r="D59" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="E59" s="2" t="s">
-        <v>123</v>
-      </c>
-    </row>
-    <row r="60" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A60" s="2" t="s">
+      <c r="C60" s="2" t="s">
         <v>131</v>
       </c>
-      <c r="C60" s="2" t="s">
+      <c r="D60" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="E60" s="2" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="61" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A61" s="13" t="s">
         <v>132</v>
       </c>
-      <c r="D60" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="E60" s="2" t="s">
-        <v>123</v>
-      </c>
-    </row>
-    <row r="61" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A61" s="2" t="s">
+      <c r="C61" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="D61" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="E61" s="2" t="s">
+        <v>122</v>
+      </c>
+      <c r="F61" s="2" t="s">
         <v>133</v>
       </c>
-      <c r="C61" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="D61" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="E61" s="2" t="s">
-        <v>123</v>
-      </c>
-      <c r="F61" s="2" t="s">
-        <v>134</v>
-      </c>
     </row>
     <row r="62" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A62" s="2" t="s">
-        <v>131</v>
+      <c r="A62" s="13" t="s">
+        <v>130</v>
       </c>
       <c r="C62" s="2" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="D62" s="2" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="E62" s="2" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
     </row>
     <row r="63" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A63" s="2" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="C63" s="2" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="D63" s="2" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="E63" s="2" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="F63" s="2" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
     </row>
     <row r="64" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A64" s="2" t="s">
+        <v>135</v>
+      </c>
+      <c r="C64" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="D64" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="E64" s="2" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="65" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A65" s="13" t="s">
         <v>136</v>
       </c>
-      <c r="C64" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="D64" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="E64" s="2" t="s">
-        <v>123</v>
-      </c>
-    </row>
-    <row r="65" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A65" s="2" t="s">
+      <c r="C65" s="2" t="s">
+        <v>85</v>
+      </c>
+      <c r="D65" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="E65" s="2" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="66" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A66" s="13" t="s">
         <v>137</v>
       </c>
-      <c r="C65" s="2" t="s">
-        <v>86</v>
-      </c>
-      <c r="D65" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="E65" s="2" t="s">
-        <v>123</v>
-      </c>
-    </row>
-    <row r="66" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A66" s="2" t="s">
+      <c r="C66" s="2" t="s">
         <v>138</v>
       </c>
-      <c r="C66" s="2" t="s">
-        <v>139</v>
-      </c>
       <c r="D66" s="2" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="E66" s="2" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
     </row>
     <row r="67" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A67" s="2" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="C67" s="2" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="D67" s="2" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="E67" s="2" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
     </row>
     <row r="68" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A68" s="2" t="s">
+        <v>140</v>
+      </c>
+      <c r="C68" s="2" t="s">
         <v>141</v>
       </c>
-      <c r="C68" s="2" t="s">
+      <c r="D68" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="E68" s="2" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="69" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A69" s="13" t="s">
         <v>142</v>
       </c>
-      <c r="D68" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="E68" s="2" t="s">
-        <v>123</v>
-      </c>
-    </row>
-    <row r="69" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A69" s="2" t="s">
-        <v>143</v>
-      </c>
       <c r="C69" s="2" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="D69" s="2" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="E69" s="2" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
     </row>
     <row r="70" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A70" s="2" t="s">
-        <v>130</v>
+      <c r="A70" s="13" t="s">
+        <v>129</v>
       </c>
       <c r="C70" s="2" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="D70" s="2" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="E70" s="2" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
     </row>
     <row r="71" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A71" s="2" t="s">
+        <v>145</v>
+      </c>
+      <c r="C71" s="2" t="s">
         <v>146</v>
       </c>
-      <c r="C71" s="2" t="s">
+      <c r="D71" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="E71" s="2" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="72" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A72" s="13" t="s">
         <v>147</v>
       </c>
-      <c r="D71" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="E71" s="2" t="s">
-        <v>123</v>
-      </c>
-    </row>
-    <row r="72" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A72" s="2" t="s">
+      <c r="C72" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="D72" s="2" t="s">
+        <v>106</v>
+      </c>
+      <c r="G72" s="2" t="s">
         <v>148</v>
       </c>
-      <c r="C72" s="2" t="s">
-        <v>69</v>
-      </c>
-      <c r="D72" s="2" t="s">
-        <v>107</v>
-      </c>
-      <c r="G72" s="2" t="s">
+    </row>
+    <row r="73" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A73" s="13" t="s">
         <v>149</v>
       </c>
-    </row>
-    <row r="73" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A73" s="2" t="s">
+      <c r="C73" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="D73" s="2" t="s">
+        <v>106</v>
+      </c>
+      <c r="G73" s="2" t="s">
         <v>150</v>
-      </c>
-      <c r="C73" s="2" t="s">
-        <v>69</v>
-      </c>
-      <c r="D73" s="2" t="s">
-        <v>107</v>
-      </c>
-      <c r="G73" s="2" t="s">
-        <v>151</v>
       </c>
     </row>
     <row r="74" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A74" s="2" t="s">
+        <v>152</v>
+      </c>
+      <c r="C74" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="D74" s="2" t="s">
+        <v>106</v>
+      </c>
+      <c r="G74" s="2" t="s">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="75" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A75" s="13" t="s">
+        <v>110</v>
+      </c>
+      <c r="C75" s="2" t="s">
         <v>153</v>
       </c>
-      <c r="C74" s="2" t="s">
-        <v>69</v>
-      </c>
-      <c r="D74" s="2" t="s">
-        <v>107</v>
-      </c>
-      <c r="G74" s="2" t="s">
-        <v>152</v>
-      </c>
-    </row>
-    <row r="75" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A75" s="2" t="s">
+      <c r="D75" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="F75" s="5" t="s">
+        <v>154</v>
+      </c>
+      <c r="G75" s="2" t="s">
         <v>111</v>
       </c>
-      <c r="C75" s="2" t="s">
-        <v>154</v>
-      </c>
-      <c r="D75" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="F75" s="9" t="s">
+    </row>
+    <row r="76" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A76" s="13" t="s">
+        <v>156</v>
+      </c>
+      <c r="C76" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="D76" s="2" t="s">
+        <v>106</v>
+      </c>
+      <c r="G76" s="5" t="s">
         <v>155</v>
-      </c>
-      <c r="G75" s="2" t="s">
-        <v>112</v>
-      </c>
-    </row>
-    <row r="76" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A76" s="2" t="s">
-        <v>157</v>
-      </c>
-      <c r="C76" s="2" t="s">
-        <v>69</v>
-      </c>
-      <c r="D76" s="2" t="s">
-        <v>107</v>
-      </c>
-      <c r="G76" s="9" t="s">
-        <v>156</v>
       </c>
     </row>
     <row r="77" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A77" s="2" t="s">
+        <v>158</v>
+      </c>
+      <c r="C77" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="D77" s="2" t="s">
+        <v>106</v>
+      </c>
+      <c r="G77" s="8" t="s">
+        <v>157</v>
+      </c>
+    </row>
+    <row r="78" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A78" s="13" t="s">
         <v>159</v>
       </c>
-      <c r="C77" s="2" t="s">
-        <v>69</v>
-      </c>
-      <c r="D77" s="2" t="s">
-        <v>107</v>
-      </c>
-      <c r="G77" s="10" t="s">
-        <v>158</v>
-      </c>
-    </row>
-    <row r="78" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A78" s="2" t="s">
+      <c r="C78" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="D78" s="2" t="s">
+        <v>106</v>
+      </c>
+      <c r="G78" s="5" t="s">
         <v>160</v>
       </c>
-      <c r="C78" s="2" t="s">
-        <v>69</v>
-      </c>
-      <c r="D78" s="2" t="s">
-        <v>107</v>
-      </c>
-      <c r="G78" s="9" t="s">
+    </row>
+    <row r="79" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A79" s="13" t="s">
+        <v>162</v>
+      </c>
+      <c r="C79" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="D79" s="2" t="s">
+        <v>106</v>
+      </c>
+      <c r="G79" s="5" t="s">
         <v>161</v>
       </c>
     </row>
-    <row r="79" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A79" s="2" t="s">
+    <row r="80" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A80" t="s">
+        <v>164</v>
+      </c>
+      <c r="C80" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="D80" s="2" t="s">
+        <v>106</v>
+      </c>
+      <c r="G80" s="5" t="s">
         <v>163</v>
-      </c>
-      <c r="C79" s="2" t="s">
-        <v>69</v>
-      </c>
-      <c r="D79" s="2" t="s">
-        <v>107</v>
-      </c>
-      <c r="G79" s="9" t="s">
-        <v>162</v>
-      </c>
-    </row>
-    <row r="80" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A80" s="11" t="s">
-        <v>165</v>
-      </c>
-      <c r="C80" s="2" t="s">
-        <v>69</v>
-      </c>
-      <c r="D80" s="2" t="s">
-        <v>107</v>
-      </c>
-      <c r="G80" s="9" t="s">
-        <v>164</v>
       </c>
     </row>
     <row r="81" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A81" s="2" t="s">
+        <v>166</v>
+      </c>
+      <c r="C81" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="D81" s="2" t="s">
+        <v>106</v>
+      </c>
+      <c r="G81" s="6" t="s">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="82" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A82" s="13" t="s">
+        <v>137</v>
+      </c>
+      <c r="C82" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="D82" s="2" t="s">
+        <v>106</v>
+      </c>
+      <c r="G82" s="5" t="s">
         <v>167</v>
-      </c>
-      <c r="C81" s="2" t="s">
-        <v>69</v>
-      </c>
-      <c r="D81" s="2" t="s">
-        <v>107</v>
-      </c>
-      <c r="G81" s="6" t="s">
-        <v>166</v>
-      </c>
-    </row>
-    <row r="82" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A82" s="2" t="s">
-        <v>138</v>
-      </c>
-      <c r="C82" s="2" t="s">
-        <v>69</v>
-      </c>
-      <c r="D82" s="2" t="s">
-        <v>107</v>
-      </c>
-      <c r="G82" s="9" t="s">
-        <v>168</v>
       </c>
     </row>
     <row r="83" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A83" s="2" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="C83" s="2" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="D83" s="2" t="s">
-        <v>107</v>
-      </c>
-      <c r="G83" s="9" t="s">
+        <v>106</v>
+      </c>
+      <c r="G83" s="5" t="s">
+        <v>168</v>
+      </c>
+    </row>
+    <row r="84" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A84" s="13" t="s">
         <v>169</v>
       </c>
-    </row>
-    <row r="84" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A84" s="2" t="s">
-        <v>170</v>
-      </c>
       <c r="C84" s="2" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="D84" s="2" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="E84" s="2" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
     </row>
     <row r="85" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A85" s="2" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="C85" s="2" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="D85" s="2" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="E85" s="2" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
     </row>
     <row r="86" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A86" s="2" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="C86" s="2" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="D86" s="2" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="E86" s="2" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
     </row>
     <row r="87" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A87" s="2" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="C87" s="2" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="D87" s="2" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="E87" s="2" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
     </row>
     <row r="88" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A88" s="2" t="s">
+        <v>171</v>
+      </c>
+      <c r="C88" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="D88" s="2" t="s">
+        <v>106</v>
+      </c>
+      <c r="G88" s="5" t="s">
         <v>172</v>
       </c>
-      <c r="C88" s="2" t="s">
-        <v>69</v>
-      </c>
-      <c r="D88" s="2" t="s">
-        <v>107</v>
-      </c>
-      <c r="G88" s="9" t="s">
+    </row>
+    <row r="89" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A89" s="13" t="s">
+        <v>176</v>
+      </c>
+      <c r="C89" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="D89" s="2" t="s">
+        <v>106</v>
+      </c>
+      <c r="G89" s="5" t="s">
         <v>173</v>
       </c>
-    </row>
-    <row r="89" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A89" s="2" t="s">
+      <c r="H89">
+        <v>9394791981</v>
+      </c>
+    </row>
+    <row r="90" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A90" s="13" t="s">
+        <v>56</v>
+      </c>
+      <c r="C90" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="D90" s="2" t="s">
+        <v>106</v>
+      </c>
+      <c r="G90" s="5" t="s">
         <v>177</v>
-      </c>
-      <c r="C89" s="2" t="s">
-        <v>69</v>
-      </c>
-      <c r="D89" s="2" t="s">
-        <v>107</v>
-      </c>
-      <c r="G89" s="9" t="s">
-        <v>174</v>
-      </c>
-      <c r="H89" s="11">
-        <v>9394791981</v>
-      </c>
-    </row>
-    <row r="90" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A90" s="2" t="s">
-        <v>57</v>
-      </c>
-      <c r="C90" s="2" t="s">
-        <v>69</v>
-      </c>
-      <c r="D90" s="2" t="s">
-        <v>107</v>
-      </c>
-      <c r="G90" s="9" t="s">
-        <v>178</v>
       </c>
     </row>
     <row r="91" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A91" s="2" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="C91" s="2" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="D91" s="2" t="s">
-        <v>107</v>
-      </c>
-      <c r="G91" s="9" t="s">
-        <v>179</v>
-      </c>
-      <c r="H91" s="11">
+        <v>106</v>
+      </c>
+      <c r="G91" s="5" t="s">
+        <v>178</v>
+      </c>
+      <c r="H91">
         <v>9270345867</v>
       </c>
     </row>
     <row r="92" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A92" s="2" t="s">
+        <v>179</v>
+      </c>
+      <c r="C92" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="D92" s="2" t="s">
+        <v>106</v>
+      </c>
+      <c r="G92" s="5" t="s">
         <v>180</v>
       </c>
-      <c r="C92" s="2" t="s">
-        <v>69</v>
-      </c>
-      <c r="D92" s="2" t="s">
-        <v>107</v>
-      </c>
-      <c r="G92" s="9" t="s">
-        <v>181</v>
-      </c>
-      <c r="H92" s="11">
+      <c r="H92">
         <v>639923742220</v>
       </c>
     </row>
     <row r="93" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A93" s="2" t="s">
+        <v>181</v>
+      </c>
+      <c r="C93" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="D93" s="2" t="s">
+        <v>106</v>
+      </c>
+      <c r="G93" s="7" t="s">
         <v>182</v>
-      </c>
-      <c r="C93" s="2" t="s">
-        <v>69</v>
-      </c>
-      <c r="D93" s="2" t="s">
-        <v>107</v>
-      </c>
-      <c r="G93" s="7" t="s">
-        <v>183</v>
       </c>
     </row>
     <row r="94" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A94" s="2" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="C94" s="2" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="D94" s="2" t="s">
-        <v>107</v>
-      </c>
-      <c r="G94" s="9" t="s">
-        <v>184</v>
+        <v>106</v>
+      </c>
+      <c r="G94" s="5" t="s">
+        <v>183</v>
       </c>
     </row>
     <row r="95" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A95" s="2" t="s">
+        <v>185</v>
+      </c>
+      <c r="C95" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="D95" s="2" t="s">
+        <v>106</v>
+      </c>
+      <c r="G95" s="5" t="s">
+        <v>184</v>
+      </c>
+    </row>
+    <row r="96" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A96" s="13" t="s">
         <v>186</v>
       </c>
-      <c r="C95" s="2" t="s">
-        <v>69</v>
-      </c>
-      <c r="D95" s="2" t="s">
-        <v>107</v>
-      </c>
-      <c r="G95" s="9" t="s">
-        <v>185</v>
-      </c>
-    </row>
-    <row r="96" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A96" s="2" t="s">
+      <c r="C96" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="D96" s="2" t="s">
+        <v>106</v>
+      </c>
+      <c r="G96" s="5" t="s">
         <v>187</v>
       </c>
-      <c r="C96" s="2" t="s">
-        <v>69</v>
-      </c>
-      <c r="D96" s="2" t="s">
-        <v>107</v>
-      </c>
-      <c r="G96" s="9" t="s">
+    </row>
+    <row r="97" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A97" s="13" t="s">
         <v>188</v>
       </c>
-    </row>
-    <row r="97" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A97" s="2" t="s">
+      <c r="C97" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="D97" s="2" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="98" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A98" s="13" t="s">
+        <v>56</v>
+      </c>
+      <c r="C98" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="D98" s="2" t="s">
+        <v>106</v>
+      </c>
+      <c r="G98" s="5" t="s">
         <v>189</v>
       </c>
-      <c r="C97" s="2" t="s">
-        <v>69</v>
-      </c>
-      <c r="D97" s="2" t="s">
-        <v>107</v>
-      </c>
-    </row>
-    <row r="98" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A98" s="2" t="s">
-        <v>57</v>
-      </c>
-      <c r="C98" s="2" t="s">
-        <v>69</v>
-      </c>
-      <c r="D98" s="2" t="s">
-        <v>107</v>
-      </c>
-      <c r="G98" s="9" t="s">
+    </row>
+    <row r="99" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A99" s="13" t="s">
+        <v>191</v>
+      </c>
+      <c r="C99" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="D99" s="2" t="s">
+        <v>106</v>
+      </c>
+      <c r="G99" s="5" t="s">
         <v>190</v>
-      </c>
-    </row>
-    <row r="99" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A99" s="2" t="s">
-        <v>192</v>
-      </c>
-      <c r="C99" s="2" t="s">
-        <v>69</v>
-      </c>
-      <c r="D99" s="2" t="s">
-        <v>107</v>
-      </c>
-      <c r="G99" s="9" t="s">
-        <v>191</v>
       </c>
     </row>
     <row r="100" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A100" s="2" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="C100" s="2" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="D100" s="2" t="s">
-        <v>107</v>
-      </c>
-      <c r="G100" s="9" t="s">
-        <v>193</v>
-      </c>
-      <c r="H100" s="11">
+        <v>106</v>
+      </c>
+      <c r="G100" s="5" t="s">
+        <v>192</v>
+      </c>
+      <c r="H100">
         <v>9695979091</v>
       </c>
     </row>
     <row r="101" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A101" s="2" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="C101" s="2" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="D101" s="2" t="s">
-        <v>107</v>
-      </c>
-      <c r="G101" s="9" t="s">
-        <v>195</v>
+        <v>106</v>
+      </c>
+      <c r="G101" s="5" t="s">
+        <v>194</v>
       </c>
     </row>
     <row r="102" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A102" s="2" t="s">
+        <v>197</v>
+      </c>
+      <c r="C102" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="D102" s="2" t="s">
+        <v>106</v>
+      </c>
+      <c r="G102" s="5" t="s">
+        <v>196</v>
+      </c>
+    </row>
+    <row r="103" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A103" s="13" t="s">
+        <v>191</v>
+      </c>
+      <c r="C103" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="D103" s="2" t="s">
+        <v>106</v>
+      </c>
+      <c r="G103" s="5" t="s">
         <v>198</v>
       </c>
-      <c r="C102" s="2" t="s">
-        <v>69</v>
-      </c>
-      <c r="D102" s="2" t="s">
-        <v>107</v>
-      </c>
-      <c r="G102" s="9" t="s">
-        <v>197</v>
-      </c>
-    </row>
-    <row r="103" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A103" s="2" t="s">
-        <v>192</v>
-      </c>
-      <c r="C103" s="2" t="s">
-        <v>69</v>
-      </c>
-      <c r="D103" s="2" t="s">
-        <v>107</v>
-      </c>
-      <c r="G103" s="9" t="s">
+    </row>
+    <row r="104" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A104" s="13" t="s">
         <v>199</v>
       </c>
-    </row>
-    <row r="104" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A104" s="2" t="s">
+      <c r="C104" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="D104" s="2" t="s">
+        <v>106</v>
+      </c>
+      <c r="G104" s="5" t="s">
         <v>200</v>
       </c>
-      <c r="C104" s="2" t="s">
-        <v>69</v>
-      </c>
-      <c r="D104" s="2" t="s">
-        <v>107</v>
-      </c>
-      <c r="G104" s="9" t="s">
+    </row>
+    <row r="105" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A105" s="13" t="s">
         <v>201</v>
       </c>
-    </row>
-    <row r="105" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A105" s="2" t="s">
-        <v>202</v>
-      </c>
       <c r="C105" s="2" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="D105" s="2" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
     </row>
     <row r="106" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A106" s="2" t="s">
+        <v>202</v>
+      </c>
+      <c r="C106" s="2" t="s">
         <v>203</v>
       </c>
-      <c r="C106" s="2" t="s">
-        <v>204</v>
-      </c>
       <c r="D106" s="2" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="E106" s="2" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
     </row>
     <row r="107" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A107" s="2" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="C107" s="2" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="D107" s="2" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="E107" s="2" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
     </row>
     <row r="108" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A108" s="2" t="s">
+        <v>205</v>
+      </c>
+      <c r="C108" s="2" t="s">
         <v>206</v>
       </c>
-      <c r="C108" s="2" t="s">
-        <v>207</v>
-      </c>
       <c r="D108" s="2" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="E108" s="2" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
     </row>
     <row r="109" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A109" s="2" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="C109" s="2" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="D109" s="2" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="E109" s="2" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
     </row>
     <row r="110" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A110" s="2" t="s">
+        <v>208</v>
+      </c>
+      <c r="C110" s="2" t="s">
         <v>209</v>
       </c>
-      <c r="C110" s="2" t="s">
-        <v>210</v>
-      </c>
       <c r="D110" s="2" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="E110" s="2" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
     </row>
     <row r="111" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A111" s="2" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="C111" s="2" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="D111" s="2" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="E111" s="2" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
     </row>
     <row r="112" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A112" s="2" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="C112" s="2" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="D112" s="2" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="E112" s="2" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
     </row>
     <row r="113" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A113" s="2" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="C113" s="2" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="D113" s="2" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="E113" s="2" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
     </row>
     <row r="114" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A114" s="2" t="s">
+        <v>212</v>
+      </c>
+      <c r="C114" s="2" t="s">
         <v>213</v>
       </c>
-      <c r="C114" s="2" t="s">
-        <v>214</v>
-      </c>
       <c r="D114" s="2" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="E114" s="2" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
     </row>
     <row r="115" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A115" s="2" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="C115" s="2" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="D115" s="2" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="E115" s="2" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
     </row>
     <row r="116" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A116" s="2" t="s">
+        <v>215</v>
+      </c>
+      <c r="C116" s="2" t="s">
         <v>216</v>
       </c>
-      <c r="C116" s="2" t="s">
-        <v>217</v>
-      </c>
       <c r="D116" s="2" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="E116" s="2" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
     </row>
     <row r="117" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A117" s="2" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="C117" s="2" t="s">
+        <v>217</v>
+      </c>
+      <c r="D117" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="E117" s="2" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="118" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A118" s="13" t="s">
+        <v>169</v>
+      </c>
+      <c r="C118" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="D118" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="E118" s="2" t="s">
+        <v>122</v>
+      </c>
+      <c r="G118" s="2" t="s">
         <v>218</v>
-      </c>
-      <c r="D117" s="2" t="s">
-        <v>26</v>
-      </c>
-      <c r="E117" s="2" t="s">
-        <v>123</v>
-      </c>
-    </row>
-    <row r="118" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A118" s="2" t="s">
-        <v>170</v>
-      </c>
-      <c r="C118" s="2" t="s">
-        <v>69</v>
-      </c>
-      <c r="D118" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="E118" s="2" t="s">
-        <v>123</v>
-      </c>
-      <c r="G118" s="2" t="s">
-        <v>219</v>
       </c>
     </row>
     <row r="119" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A119" s="2" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="C119" s="2" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="D119" s="2" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="E119" s="2" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
     </row>
     <row r="120" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A120" s="2" t="s">
+        <v>220</v>
+      </c>
+      <c r="C120" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="D120" s="2" t="s">
         <v>221</v>
       </c>
-      <c r="C120" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="D120" s="2" t="s">
-        <v>222</v>
-      </c>
       <c r="E120" s="2" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
     </row>
     <row r="121" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A121" s="2" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="C121" s="2" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D121" s="2" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="E121" s="2" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
     </row>
     <row r="122" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A122" s="2" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="C122" s="2" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="D122" s="2" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="E122" s="2" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
     </row>
     <row r="123" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A123" s="2" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="C123" s="2" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="D123" s="2" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="E123" s="2" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
     </row>
     <row r="124" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A124" s="2" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="C124" s="2" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="D124" s="2" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="E124" s="2" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
     </row>
     <row r="125" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A125" s="2" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="C125" s="2" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="D125" s="2" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="E125" s="2" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
     </row>
     <row r="126" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A126" s="2" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="C126" s="2" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="D126" s="2" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="E126" s="2" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
     </row>
     <row r="127" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A127" s="2" t="s">
+        <v>226</v>
+      </c>
+      <c r="C127" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="D127" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="E127" s="2" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="128" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A128" s="13" t="s">
+        <v>162</v>
+      </c>
+      <c r="C128" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="D128" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="E128" s="2" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="129" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A129" s="13" t="s">
         <v>227</v>
       </c>
-      <c r="C127" s="2" t="s">
-        <v>69</v>
-      </c>
-      <c r="D127" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="E127" s="2" t="s">
-        <v>123</v>
-      </c>
-    </row>
-    <row r="128" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A128" s="2" t="s">
-        <v>163</v>
-      </c>
-      <c r="C128" s="2" t="s">
-        <v>69</v>
-      </c>
-      <c r="D128" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="E128" s="2" t="s">
-        <v>123</v>
-      </c>
-    </row>
-    <row r="129" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A129" s="2" t="s">
-        <v>228</v>
-      </c>
       <c r="C129" s="2" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="D129" s="2" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="E129" s="2" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
     </row>
     <row r="130" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A130" s="2" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="C130" s="2" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="D130" s="2" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="E130" s="2" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
     </row>
     <row r="131" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A131" s="2" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="C131" s="2" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="D131" s="2" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="E131" s="2" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
     </row>
     <row r="132" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A132" s="2" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="C132" s="2" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="D132" s="2" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="E132" s="2" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
     </row>
     <row r="133" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A133" s="2" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="C133" s="2" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="D133" s="2" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="E133" s="2" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
     </row>
     <row r="134" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A134" s="2" t="s">
+        <v>233</v>
+      </c>
+      <c r="C134" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="D134" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="E134" s="2" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="135" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A135" s="13" t="s">
         <v>234</v>
       </c>
-      <c r="C134" s="2" t="s">
-        <v>69</v>
-      </c>
-      <c r="D134" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="E134" s="2" t="s">
-        <v>123</v>
-      </c>
-    </row>
-    <row r="135" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A135" s="2" t="s">
-        <v>235</v>
-      </c>
       <c r="C135" s="2" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="D135" s="2" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="E135" s="2" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
     </row>
     <row r="136" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A136" s="2" t="s">
+        <v>235</v>
+      </c>
+      <c r="C136" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="D136" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="E136" s="2" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="137" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A137" s="13" t="s">
         <v>236</v>
       </c>
-      <c r="C136" s="2" t="s">
-        <v>69</v>
-      </c>
-      <c r="D136" s="2" t="s">
-        <v>26</v>
-      </c>
-      <c r="E136" s="2" t="s">
-        <v>123</v>
-      </c>
-    </row>
-    <row r="137" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A137" s="2" t="s">
+      <c r="C137" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="D137" s="2" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="138" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A138" s="13" t="s">
+        <v>238</v>
+      </c>
+      <c r="C138" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="D138" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="G138" s="9" t="s">
         <v>237</v>
       </c>
-      <c r="C137" s="2" t="s">
-        <v>69</v>
-      </c>
-      <c r="D137" s="2" t="s">
-        <v>107</v>
-      </c>
-    </row>
-    <row r="138" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A138" s="2" t="s">
+    </row>
+    <row r="139" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A139" s="13" t="s">
         <v>239</v>
       </c>
-      <c r="C138" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="D138" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="G138" s="12" t="s">
-        <v>238</v>
-      </c>
-    </row>
-    <row r="139" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A139" s="2" t="s">
+      <c r="C139" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="D139" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="G139" s="2" t="s">
         <v>240</v>
       </c>
-      <c r="C139" s="2" t="s">
-        <v>69</v>
-      </c>
-      <c r="D139" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="G139" s="2" t="s">
+    </row>
+    <row r="140" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A140" s="13" t="s">
         <v>241</v>
       </c>
-    </row>
-    <row r="140" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A140" s="2" t="s">
+      <c r="C140" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="D140" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="G140" s="2" t="s">
         <v>242</v>
-      </c>
-      <c r="C140" s="2" t="s">
-        <v>69</v>
-      </c>
-      <c r="D140" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="G140" s="2" t="s">
-        <v>243</v>
       </c>
     </row>
     <row r="141" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A141" s="2" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="C141" s="2" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="D141" s="2" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="E141" s="2" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
     </row>
     <row r="142" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A142" s="2" t="s">
+        <v>243</v>
+      </c>
+      <c r="C142" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="D142" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="E142" s="2" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="143" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A143" s="13" t="s">
         <v>244</v>
       </c>
-      <c r="C142" s="2" t="s">
-        <v>69</v>
-      </c>
-      <c r="D142" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="E142" s="2" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="143" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A143" s="2" t="s">
+      <c r="C143" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="D143" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="E143" s="2" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="144" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A144" s="13" t="s">
         <v>245</v>
       </c>
-      <c r="C143" s="2" t="s">
-        <v>69</v>
-      </c>
-      <c r="D143" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="E143" s="2" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="144" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A144" s="2" t="s">
-        <v>246</v>
-      </c>
       <c r="C144" s="2" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="D144" s="2" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="E144" s="2" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
     </row>
     <row r="145" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A145" s="2" t="s">
+        <v>247</v>
+      </c>
+      <c r="C145" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="D145" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="E145" s="2" t="s">
+        <v>246</v>
+      </c>
+    </row>
+    <row r="146" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A146" s="13" t="s">
         <v>248</v>
       </c>
-      <c r="C145" s="2" t="s">
-        <v>69</v>
-      </c>
-      <c r="D145" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="E145" s="2" t="s">
-        <v>247</v>
-      </c>
-    </row>
-    <row r="146" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A146" s="2" t="s">
-        <v>249</v>
-      </c>
       <c r="C146" s="2" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="D146" s="2" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="E146" s="2" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
     </row>
     <row r="147" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A147" s="2" t="s">
+        <v>249</v>
+      </c>
+      <c r="C147" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="D147" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="E147" s="2" t="s">
         <v>250</v>
-      </c>
-      <c r="C147" s="2" t="s">
-        <v>69</v>
-      </c>
-      <c r="D147" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="E147" s="2" t="s">
-        <v>251</v>
       </c>
     </row>
     <row r="148" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A148" s="2" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="C148" s="2" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="D148" s="2" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="E148" s="2" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
     </row>
     <row r="149" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A149" s="2" t="s">
+        <v>253</v>
+      </c>
+      <c r="C149" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="D149" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="E149" s="2" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="150" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A150" s="13" t="s">
         <v>254</v>
       </c>
-      <c r="C149" s="2" t="s">
-        <v>69</v>
-      </c>
-      <c r="D149" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="E149" s="2" t="s">
-        <v>88</v>
-      </c>
-    </row>
-    <row r="150" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A150" s="2" t="s">
+      <c r="C150" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="D150" s="2" t="s">
+        <v>106</v>
+      </c>
+      <c r="E150" s="2" t="s">
+        <v>122</v>
+      </c>
+      <c r="G150" s="5" t="s">
         <v>255</v>
       </c>
-      <c r="C150" s="2" t="s">
-        <v>69</v>
-      </c>
-      <c r="D150" s="2" t="s">
-        <v>107</v>
-      </c>
-      <c r="E150" s="2" t="s">
-        <v>123</v>
-      </c>
-      <c r="G150" s="9" t="s">
+      <c r="H150" t="s">
         <v>256</v>
-      </c>
-      <c r="H150" s="11" t="s">
-        <v>257</v>
       </c>
     </row>
     <row r="151" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A151" s="2" t="s">
+        <v>258</v>
+      </c>
+      <c r="C151" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="D151" s="2" t="s">
+        <v>106</v>
+      </c>
+      <c r="E151" s="2" t="s">
+        <v>122</v>
+      </c>
+      <c r="G151" s="5" t="s">
+        <v>257</v>
+      </c>
+      <c r="H151">
+        <v>9499601153</v>
+      </c>
+    </row>
+    <row r="152" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A152" s="13" t="s">
+        <v>162</v>
+      </c>
+      <c r="C152" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="D152" s="2" t="s">
+        <v>106</v>
+      </c>
+      <c r="E152" s="2" t="s">
+        <v>122</v>
+      </c>
+      <c r="G152" s="5" t="s">
         <v>259</v>
       </c>
-      <c r="C151" s="2" t="s">
-        <v>69</v>
-      </c>
-      <c r="D151" s="2" t="s">
-        <v>107</v>
-      </c>
-      <c r="E151" s="2" t="s">
-        <v>123</v>
-      </c>
-      <c r="G151" s="9" t="s">
-        <v>258</v>
-      </c>
-      <c r="H151" s="11">
-        <v>9499601153</v>
-      </c>
-    </row>
-    <row r="152" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A152" s="2" t="s">
-        <v>163</v>
-      </c>
-      <c r="C152" s="2" t="s">
-        <v>69</v>
-      </c>
-      <c r="D152" s="2" t="s">
-        <v>107</v>
-      </c>
-      <c r="E152" s="2" t="s">
-        <v>123</v>
-      </c>
-      <c r="G152" s="9" t="s">
+    </row>
+    <row r="153" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A153" s="13" t="s">
+        <v>261</v>
+      </c>
+      <c r="C153" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="D153" s="2" t="s">
+        <v>106</v>
+      </c>
+      <c r="E153" s="2" t="s">
+        <v>122</v>
+      </c>
+      <c r="G153" s="5" t="s">
         <v>260</v>
       </c>
-    </row>
-    <row r="153" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A153" s="2" t="s">
+      <c r="H153">
+        <v>9155285209</v>
+      </c>
+    </row>
+    <row r="154" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A154" s="13" t="s">
+        <v>56</v>
+      </c>
+      <c r="C154" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="D154" s="2" t="s">
+        <v>106</v>
+      </c>
+      <c r="E154" s="2" t="s">
+        <v>122</v>
+      </c>
+      <c r="G154" s="5" t="s">
         <v>262</v>
       </c>
-      <c r="C153" s="2" t="s">
-        <v>69</v>
-      </c>
-      <c r="D153" s="2" t="s">
-        <v>107</v>
-      </c>
-      <c r="E153" s="2" t="s">
-        <v>123</v>
-      </c>
-      <c r="G153" s="9" t="s">
-        <v>261</v>
-      </c>
-      <c r="H153" s="11">
-        <v>9155285209</v>
-      </c>
-    </row>
-    <row r="154" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A154" s="2" t="s">
-        <v>57</v>
-      </c>
-      <c r="C154" s="2" t="s">
-        <v>69</v>
-      </c>
-      <c r="D154" s="2" t="s">
-        <v>107</v>
-      </c>
-      <c r="E154" s="2" t="s">
-        <v>123</v>
-      </c>
-      <c r="G154" s="9" t="s">
+      <c r="H154">
+        <v>9479868804</v>
+      </c>
+    </row>
+    <row r="155" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A155" s="13" t="s">
+        <v>265</v>
+      </c>
+      <c r="C155" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="D155" s="2" t="s">
+        <v>106</v>
+      </c>
+      <c r="E155" s="2" t="s">
+        <v>122</v>
+      </c>
+      <c r="G155" s="5" t="s">
         <v>263</v>
       </c>
-      <c r="H154" s="11">
-        <v>9479868804</v>
-      </c>
-    </row>
-    <row r="155" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A155" s="2" t="s">
+      <c r="H155">
+        <v>9393224106</v>
+      </c>
+    </row>
+    <row r="156" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A156" s="13" t="s">
         <v>266</v>
       </c>
-      <c r="C155" s="2" t="s">
-        <v>69</v>
-      </c>
-      <c r="D155" s="2" t="s">
-        <v>107</v>
-      </c>
-      <c r="E155" s="2" t="s">
-        <v>123</v>
-      </c>
-      <c r="G155" s="9" t="s">
+      <c r="C156" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="D156" s="2" t="s">
+        <v>106</v>
+      </c>
+      <c r="E156" s="2" t="s">
+        <v>122</v>
+      </c>
+      <c r="G156" s="5" t="s">
         <v>264</v>
       </c>
-      <c r="H155" s="11">
-        <v>9393224106</v>
-      </c>
-    </row>
-    <row r="156" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A156" s="2" t="s">
+      <c r="H156">
+        <v>9164259033</v>
+      </c>
+    </row>
+    <row r="157" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A157" s="13" t="s">
+        <v>162</v>
+      </c>
+      <c r="C157" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="D157" s="2" t="s">
+        <v>106</v>
+      </c>
+      <c r="E157" s="2" t="s">
+        <v>122</v>
+      </c>
+      <c r="G157" s="5" t="s">
         <v>267</v>
       </c>
-      <c r="C156" s="2" t="s">
-        <v>69</v>
-      </c>
-      <c r="D156" s="2" t="s">
-        <v>107</v>
-      </c>
-      <c r="E156" s="2" t="s">
-        <v>123</v>
-      </c>
-      <c r="G156" s="9" t="s">
-        <v>265</v>
-      </c>
-      <c r="H156" s="11">
-        <v>9164259033</v>
-      </c>
-    </row>
-    <row r="157" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A157" s="2" t="s">
-        <v>163</v>
-      </c>
-      <c r="C157" s="2" t="s">
-        <v>69</v>
-      </c>
-      <c r="D157" s="2" t="s">
-        <v>107</v>
-      </c>
-      <c r="E157" s="2" t="s">
-        <v>123</v>
-      </c>
-      <c r="G157" s="9" t="s">
-        <v>268</v>
-      </c>
-      <c r="H157" s="11">
+      <c r="H157">
         <v>9957467792</v>
       </c>
     </row>
     <row r="158" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A158" s="2" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="C158" s="2" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="D158" s="2" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="E158" s="2" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
     </row>
     <row r="159" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A159" s="2" t="s">
+        <v>269</v>
+      </c>
+      <c r="C159" s="2" t="s">
+        <v>66</v>
+      </c>
+      <c r="D159" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="E159" s="2" t="s">
         <v>270</v>
       </c>
-      <c r="C159" s="2" t="s">
-        <v>67</v>
-      </c>
-      <c r="D159" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="E159" s="2" t="s">
+    </row>
+    <row r="160" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A160" s="10" t="s">
         <v>271</v>
       </c>
-    </row>
-    <row r="160" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A160" s="13" t="s">
-        <v>272</v>
-      </c>
       <c r="C160" s="2" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="D160" s="2" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="E160" s="2" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
     </row>
     <row r="161" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A161" s="2" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="C161" s="2" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="D161" s="2" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="E161" s="2" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
     </row>
     <row r="162" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A162" s="2" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="C162" s="2" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="D162" s="2" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="E162" s="2" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
     </row>
     <row r="163" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A163" s="2" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="C163" s="2" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="D163" s="2" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="E163" s="2" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
     </row>
     <row r="164" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A164" s="2" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="C164" s="2" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="D164" s="2" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="E164" s="2" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
     </row>
     <row r="165" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A165" s="2" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="C165" s="2" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D165" s="2" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="E165" s="2" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
     </row>
     <row r="166" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A166" s="2" t="s">
+        <v>277</v>
+      </c>
+      <c r="C166" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="D166" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="E166" s="2" t="s">
+        <v>270</v>
+      </c>
+    </row>
+    <row r="167" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A167" s="13" t="s">
         <v>278</v>
       </c>
-      <c r="C166" s="2" t="s">
-        <v>41</v>
-      </c>
-      <c r="D166" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="E166" s="2" t="s">
-        <v>271</v>
-      </c>
-    </row>
-    <row r="167" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A167" s="2" t="s">
+      <c r="C167" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="D167" s="2" t="s">
+        <v>106</v>
+      </c>
+      <c r="E167" s="2" t="s">
+        <v>122</v>
+      </c>
+      <c r="G167" s="5" t="s">
         <v>279</v>
-      </c>
-      <c r="C167" s="2" t="s">
-        <v>69</v>
-      </c>
-      <c r="D167" s="2" t="s">
-        <v>107</v>
-      </c>
-      <c r="E167" s="2" t="s">
-        <v>123</v>
-      </c>
-      <c r="G167" s="9" t="s">
-        <v>280</v>
       </c>
     </row>
     <row r="168" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A168" s="2" t="s">
+        <v>282</v>
+      </c>
+      <c r="C168" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="D168" s="2" t="s">
+        <v>106</v>
+      </c>
+      <c r="E168" s="2" t="s">
+        <v>122</v>
+      </c>
+      <c r="G168" s="5" t="s">
+        <v>280</v>
+      </c>
+      <c r="H168" s="11" t="s">
+        <v>281</v>
+      </c>
+    </row>
+    <row r="169" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A169" s="13" t="s">
+        <v>284</v>
+      </c>
+      <c r="C169" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="D169" s="2" t="s">
+        <v>106</v>
+      </c>
+      <c r="E169" s="2" t="s">
+        <v>122</v>
+      </c>
+      <c r="G169" s="5" t="s">
         <v>283</v>
       </c>
-      <c r="C168" s="2" t="s">
-        <v>69</v>
-      </c>
-      <c r="D168" s="2" t="s">
-        <v>107</v>
-      </c>
-      <c r="E168" s="2" t="s">
-        <v>123</v>
-      </c>
-      <c r="G168" s="9" t="s">
-        <v>281</v>
-      </c>
-      <c r="H168" s="14" t="s">
-        <v>282</v>
-      </c>
-    </row>
-    <row r="169" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A169" s="2" t="s">
+    </row>
+    <row r="170" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A170" s="13" t="s">
         <v>285</v>
       </c>
-      <c r="C169" s="2" t="s">
-        <v>69</v>
-      </c>
-      <c r="D169" s="2" t="s">
-        <v>107</v>
-      </c>
-      <c r="E169" s="2" t="s">
-        <v>123</v>
-      </c>
-      <c r="G169" s="9" t="s">
-        <v>284</v>
-      </c>
-    </row>
-    <row r="170" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A170" s="2" t="s">
+      <c r="C170" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="D170" s="2" t="s">
+        <v>106</v>
+      </c>
+      <c r="E170" s="2" t="s">
+        <v>122</v>
+      </c>
+      <c r="G170" s="5" t="s">
         <v>286</v>
       </c>
-      <c r="C170" s="2" t="s">
-        <v>69</v>
-      </c>
-      <c r="D170" s="2" t="s">
-        <v>107</v>
-      </c>
-      <c r="E170" s="2" t="s">
-        <v>123</v>
-      </c>
-      <c r="G170" s="9" t="s">
+    </row>
+    <row r="171" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A171" s="13" t="s">
+        <v>289</v>
+      </c>
+      <c r="C171" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="D171" s="2" t="s">
+        <v>106</v>
+      </c>
+      <c r="E171" s="2" t="s">
+        <v>122</v>
+      </c>
+      <c r="G171" s="5" t="s">
+        <v>288</v>
+      </c>
+      <c r="H171" s="11" t="s">
         <v>287</v>
-      </c>
-    </row>
-    <row r="171" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A171" s="2" t="s">
-        <v>290</v>
-      </c>
-      <c r="C171" s="2" t="s">
-        <v>69</v>
-      </c>
-      <c r="D171" s="2" t="s">
-        <v>107</v>
-      </c>
-      <c r="E171" s="2" t="s">
-        <v>123</v>
-      </c>
-      <c r="G171" s="9" t="s">
-        <v>289</v>
-      </c>
-      <c r="H171" s="14" t="s">
-        <v>288</v>
       </c>
     </row>
     <row r="172" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A172" s="2" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="C172" s="2" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="D172" s="2" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="E172" s="2" t="s">
-        <v>123</v>
-      </c>
-      <c r="G172" s="9" t="s">
-        <v>291</v>
-      </c>
-      <c r="H172" s="14">
+        <v>122</v>
+      </c>
+      <c r="G172" s="5" t="s">
+        <v>290</v>
+      </c>
+      <c r="H172" s="11">
         <v>9239962602</v>
       </c>
     </row>
     <row r="173" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A173" s="2" t="s">
+        <v>293</v>
+      </c>
+      <c r="C173" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="D173" s="2" t="s">
+        <v>106</v>
+      </c>
+      <c r="E173" s="2" t="s">
+        <v>122</v>
+      </c>
+      <c r="H173" s="11" t="s">
+        <v>292</v>
+      </c>
+    </row>
+    <row r="174" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A174" s="13" t="s">
+        <v>284</v>
+      </c>
+      <c r="C174" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="D174" s="2" t="s">
+        <v>106</v>
+      </c>
+      <c r="E174" s="2" t="s">
+        <v>122</v>
+      </c>
+      <c r="G174" s="5" t="s">
         <v>294</v>
       </c>
-      <c r="C173" s="2" t="s">
-        <v>69</v>
-      </c>
-      <c r="D173" s="2" t="s">
-        <v>107</v>
-      </c>
-      <c r="E173" s="2" t="s">
-        <v>123</v>
-      </c>
-      <c r="H173" s="14" t="s">
-        <v>293</v>
-      </c>
-    </row>
-    <row r="174" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A174" s="2" t="s">
-        <v>285</v>
-      </c>
-      <c r="C174" s="2" t="s">
-        <v>69</v>
-      </c>
-      <c r="D174" s="2" t="s">
-        <v>107</v>
-      </c>
-      <c r="E174" s="2" t="s">
-        <v>123</v>
-      </c>
-      <c r="G174" s="9" t="s">
+    </row>
+    <row r="175" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A175" t="s">
+        <v>296</v>
+      </c>
+      <c r="C175" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="D175" s="2" t="s">
+        <v>106</v>
+      </c>
+      <c r="E175" s="2" t="s">
+        <v>122</v>
+      </c>
+      <c r="G175" s="5" t="s">
         <v>295</v>
-      </c>
-    </row>
-    <row r="175" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A175" s="11" t="s">
-        <v>297</v>
-      </c>
-      <c r="C175" s="2" t="s">
-        <v>69</v>
-      </c>
-      <c r="D175" s="2" t="s">
-        <v>107</v>
-      </c>
-      <c r="E175" s="2" t="s">
-        <v>123</v>
-      </c>
-      <c r="G175" s="9" t="s">
-        <v>296</v>
       </c>
     </row>
     <row r="176" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A176" s="2" t="s">
+        <v>298</v>
+      </c>
+      <c r="C176" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="D176" s="2" t="s">
+        <v>106</v>
+      </c>
+      <c r="E176" s="2" t="s">
+        <v>122</v>
+      </c>
+      <c r="G176" s="5" t="s">
+        <v>297</v>
+      </c>
+    </row>
+    <row r="177" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A177" s="13" t="s">
+        <v>137</v>
+      </c>
+      <c r="C177" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="D177" s="2" t="s">
+        <v>106</v>
+      </c>
+      <c r="E177" s="2" t="s">
+        <v>122</v>
+      </c>
+      <c r="G177" s="5" t="s">
         <v>299</v>
-      </c>
-      <c r="C176" s="2" t="s">
-        <v>69</v>
-      </c>
-      <c r="D176" s="2" t="s">
-        <v>107</v>
-      </c>
-      <c r="E176" s="2" t="s">
-        <v>123</v>
-      </c>
-      <c r="G176" s="5" t="s">
-        <v>298</v>
-      </c>
-    </row>
-    <row r="177" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A177" s="2" t="s">
-        <v>138</v>
-      </c>
-      <c r="C177" s="2" t="s">
-        <v>69</v>
-      </c>
-      <c r="D177" s="2" t="s">
-        <v>107</v>
-      </c>
-      <c r="E177" s="2" t="s">
-        <v>123</v>
-      </c>
-      <c r="G177" s="5" t="s">
-        <v>300</v>
       </c>
     </row>
     <row r="178" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A178" s="2" t="s">
+        <v>301</v>
+      </c>
+      <c r="C178" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="D178" s="2" t="s">
+        <v>106</v>
+      </c>
+      <c r="E178" s="2" t="s">
+        <v>122</v>
+      </c>
+      <c r="G178" s="5" t="s">
+        <v>300</v>
+      </c>
+    </row>
+    <row r="179" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A179" s="13" t="s">
         <v>302</v>
       </c>
-      <c r="C178" s="2" t="s">
-        <v>69</v>
-      </c>
-      <c r="D178" s="2" t="s">
-        <v>107</v>
-      </c>
-      <c r="E178" s="2" t="s">
-        <v>123</v>
-      </c>
-      <c r="G178" s="5" t="s">
-        <v>301</v>
+      <c r="C179" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="D179" s="2" t="s">
+        <v>106</v>
+      </c>
+      <c r="E179" s="2" t="s">
+        <v>303</v>
+      </c>
+    </row>
+    <row r="180" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A180" s="2" t="s">
+        <v>305</v>
+      </c>
+      <c r="C180" s="2" t="s">
+        <v>131</v>
+      </c>
+      <c r="D180" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="E180" s="2" t="s">
+        <v>270</v>
       </c>
     </row>
   </sheetData>
